--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1166,7 +1166,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125876692</v>
+        <v>125876721</v>
       </c>
       <c r="B6" t="n">
         <v>98216</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723027</v>
+        <v>723053</v>
       </c>
       <c r="R6" t="n">
-        <v>6380801</v>
+        <v>6380859</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125876827</v>
+        <v>125876694</v>
       </c>
       <c r="B7" t="n">
         <v>98216</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723188</v>
+        <v>723040</v>
       </c>
       <c r="R7" t="n">
-        <v>6380756</v>
+        <v>6380808</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125876721</v>
+        <v>125876692</v>
       </c>
       <c r="B8" t="n">
         <v>98216</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723053</v>
+        <v>723027</v>
       </c>
       <c r="R8" t="n">
-        <v>6380859</v>
+        <v>6380801</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125876694</v>
+        <v>125876827</v>
       </c>
       <c r="B9" t="n">
         <v>98216</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723040</v>
+        <v>723188</v>
       </c>
       <c r="R9" t="n">
-        <v>6380808</v>
+        <v>6380756</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125876696</v>
+        <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98216</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723042</v>
+        <v>722965</v>
       </c>
       <c r="R16" t="n">
-        <v>6380816</v>
+        <v>6380842</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125876732</v>
+        <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98216</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723148</v>
+        <v>722962</v>
       </c>
       <c r="R17" t="n">
-        <v>6380883</v>
+        <v>6380832</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876818</v>
+        <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98216</v>
+        <v>98347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723210</v>
+        <v>723014</v>
       </c>
       <c r="R18" t="n">
-        <v>6380786</v>
+        <v>6380862</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2643,11 +2643,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876794</v>
+        <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98216</v>
+        <v>98346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,26 +2685,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2728,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723296</v>
+        <v>723342</v>
       </c>
       <c r="R19" t="n">
-        <v>6380797</v>
+        <v>6380826</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2795,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876678</v>
+        <v>125876672</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,26 +2801,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2844,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>722965</v>
+        <v>722989</v>
       </c>
       <c r="R20" t="n">
-        <v>6380842</v>
+        <v>6380861</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876680</v>
+        <v>125876769</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>98358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,26 +2917,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219864</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2951,7 +2946,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2960,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>722962</v>
+        <v>723375</v>
       </c>
       <c r="R21" t="n">
-        <v>6380832</v>
+        <v>6380878</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3027,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876670</v>
+        <v>125876696</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98216</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,26 +3033,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3076,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723014</v>
+        <v>723042</v>
       </c>
       <c r="R22" t="n">
-        <v>6380862</v>
+        <v>6380816</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3143,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876774</v>
+        <v>125876732</v>
       </c>
       <c r="B23" t="n">
-        <v>98346</v>
+        <v>98216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,26 +3149,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3192,13 +3187,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723342</v>
+        <v>723148</v>
       </c>
       <c r="R23" t="n">
-        <v>6380826</v>
+        <v>6380883</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876672</v>
+        <v>125876818</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,26 +3265,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>722989</v>
+        <v>723210</v>
       </c>
       <c r="R24" t="n">
-        <v>6380861</v>
+        <v>6380786</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3344,6 +3339,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876769</v>
+        <v>125876794</v>
       </c>
       <c r="B25" t="n">
-        <v>98358</v>
+        <v>98216</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723375</v>
+        <v>723296</v>
       </c>
       <c r="R25" t="n">
-        <v>6380878</v>
+        <v>6380797</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876712</v>
+        <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98346</v>
+        <v>98216</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R31" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,6 +4146,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876805</v>
+        <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,26 +4193,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R32" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4262,11 +4267,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876806</v>
+        <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98216</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876683</v>
+        <v>125876781</v>
       </c>
       <c r="B93" t="n">
-        <v>98216</v>
+        <v>98242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R93" t="n">
-        <v>6380820</v>
+        <v>6380811</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876781</v>
+        <v>125876683</v>
       </c>
       <c r="B94" t="n">
-        <v>98242</v>
+        <v>98216</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723343</v>
+        <v>722977</v>
       </c>
       <c r="R94" t="n">
-        <v>6380811</v>
+        <v>6380820</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -13424,37 +13424,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876811</v>
+        <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>107195</v>
+        <v>98216</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13462,16 +13462,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723234</v>
+        <v>723022</v>
       </c>
       <c r="R112" t="n">
-        <v>6380772</v>
+        <v>6380875</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13535,10 +13540,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98346</v>
+        <v>98216</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13546,26 +13551,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13584,10 +13589,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R113" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13651,37 +13656,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876664</v>
+        <v>125876811</v>
       </c>
       <c r="B114" t="n">
-        <v>98216</v>
+        <v>107195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13689,21 +13694,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723022</v>
+        <v>723234</v>
       </c>
       <c r="R114" t="n">
-        <v>6380875</v>
+        <v>6380772</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,10 +13767,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876782</v>
+        <v>125876765</v>
       </c>
       <c r="B115" t="n">
-        <v>98216</v>
+        <v>98346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13778,26 +13778,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723338</v>
+        <v>723369</v>
       </c>
       <c r="R115" t="n">
-        <v>6380799</v>
+        <v>6380880</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125876721</v>
+        <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723053</v>
+        <v>723027</v>
       </c>
       <c r="R6" t="n">
-        <v>6380859</v>
+        <v>6380801</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125876694</v>
+        <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723040</v>
+        <v>723188</v>
       </c>
       <c r="R7" t="n">
-        <v>6380808</v>
+        <v>6380756</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125876692</v>
+        <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723027</v>
+        <v>723053</v>
       </c>
       <c r="R8" t="n">
-        <v>6380801</v>
+        <v>6380859</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125876827</v>
+        <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723188</v>
+        <v>723040</v>
       </c>
       <c r="R9" t="n">
-        <v>6380756</v>
+        <v>6380808</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876817</v>
+        <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,26 +1641,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723210</v>
+        <v>722989</v>
       </c>
       <c r="R10" t="n">
-        <v>6380786</v>
+        <v>6380861</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876703</v>
+        <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723050</v>
+        <v>723343</v>
       </c>
       <c r="R11" t="n">
-        <v>6380829</v>
+        <v>6380811</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876749</v>
+        <v>125876817</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723321</v>
+        <v>723210</v>
       </c>
       <c r="R12" t="n">
-        <v>6380856</v>
+        <v>6380786</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876673</v>
+        <v>125876703</v>
       </c>
       <c r="B13" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>722989</v>
+        <v>723050</v>
       </c>
       <c r="R13" t="n">
-        <v>6380861</v>
+        <v>6380829</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876780</v>
+        <v>125876749</v>
       </c>
       <c r="B14" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723343</v>
+        <v>723321</v>
       </c>
       <c r="R14" t="n">
-        <v>6380811</v>
+        <v>6380856</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876691</v>
       </c>
       <c r="B15" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125876672</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876769</v>
+        <v>125876732</v>
       </c>
       <c r="B21" t="n">
-        <v>98358</v>
+        <v>98223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723375</v>
+        <v>723148</v>
       </c>
       <c r="R21" t="n">
-        <v>6380878</v>
+        <v>6380883</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876696</v>
+        <v>125876794</v>
       </c>
       <c r="B22" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723042</v>
+        <v>723296</v>
       </c>
       <c r="R22" t="n">
-        <v>6380816</v>
+        <v>6380797</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876732</v>
+        <v>125876769</v>
       </c>
       <c r="B23" t="n">
-        <v>98216</v>
+        <v>98365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R23" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876818</v>
+        <v>125876696</v>
       </c>
       <c r="B24" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723210</v>
+        <v>723042</v>
       </c>
       <c r="R24" t="n">
-        <v>6380786</v>
+        <v>6380816</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3339,11 +3339,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876794</v>
+        <v>125876818</v>
       </c>
       <c r="B25" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3400,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3424,10 +3419,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723296</v>
+        <v>723210</v>
       </c>
       <c r="R25" t="n">
-        <v>6380797</v>
+        <v>6380786</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3460,6 +3455,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876768</v>
+        <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>107195</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,16 +3529,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723375</v>
+        <v>723038</v>
       </c>
       <c r="R26" t="n">
-        <v>6380878</v>
+        <v>6380861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3602,10 +3607,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876656</v>
+        <v>125876731</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723038</v>
+        <v>723148</v>
       </c>
       <c r="R27" t="n">
-        <v>6380861</v>
+        <v>6380883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3718,37 +3723,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>107195</v>
+        <v>98359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3756,16 +3761,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R28" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3829,37 +3839,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876731</v>
+        <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3867,21 +3877,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R29" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3945,37 +3950,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3983,21 +3988,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R30" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876806</v>
+        <v>125876712</v>
       </c>
       <c r="B31" t="n">
-        <v>98216</v>
+        <v>98353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R31" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,11 +4146,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,10 +4177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876712</v>
+        <v>125876805</v>
       </c>
       <c r="B32" t="n">
-        <v>98346</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4193,26 +4188,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R32" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,6 +4262,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876805</v>
+        <v>125876806</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876663</v>
+        <v>125876682</v>
       </c>
       <c r="B34" t="n">
-        <v>98242</v>
+        <v>98359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723022</v>
+        <v>722977</v>
       </c>
       <c r="R34" t="n">
-        <v>6380875</v>
+        <v>6380820</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4535,37 +4535,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876813</v>
+        <v>125876698</v>
       </c>
       <c r="B35" t="n">
-        <v>107195</v>
+        <v>98359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4573,16 +4573,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723238</v>
+        <v>723026</v>
       </c>
       <c r="R35" t="n">
-        <v>6380770</v>
+        <v>6380845</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4646,37 +4651,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876682</v>
+        <v>125876813</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4684,21 +4689,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>722977</v>
+        <v>723238</v>
       </c>
       <c r="R36" t="n">
-        <v>6380820</v>
+        <v>6380770</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876698</v>
+        <v>125876778</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,26 +4773,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,13 +4811,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723026</v>
+        <v>723355</v>
       </c>
       <c r="R37" t="n">
-        <v>6380845</v>
+        <v>6380807</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876778</v>
+        <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723355</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6380807</v>
+        <v>6380856</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876752</v>
+        <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98216</v>
+        <v>98249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723321</v>
+        <v>723022</v>
       </c>
       <c r="R39" t="n">
-        <v>6380856</v>
+        <v>6380875</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876803</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,24 +5960,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723244</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380753</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6033,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B48" t="n">
-        <v>98302</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,21 +6044,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6078,7 +6073,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6087,13 +6082,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R48" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,32 +6149,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876803</v>
+        <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>107195</v>
+        <v>98309</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6192,16 +6187,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723244</v>
+        <v>723172</v>
       </c>
       <c r="R49" t="n">
-        <v>6380753</v>
+        <v>6380881</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6265,10 +6265,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876705</v>
+        <v>125876743</v>
       </c>
       <c r="B50" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6314,13 +6314,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723064</v>
+        <v>723221</v>
       </c>
       <c r="R50" t="n">
-        <v>6380825</v>
+        <v>6380864</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876743</v>
+        <v>125876814</v>
       </c>
       <c r="B51" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723221</v>
+        <v>723228</v>
       </c>
       <c r="R51" t="n">
-        <v>6380864</v>
+        <v>6380782</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876814</v>
+        <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723228</v>
+        <v>723064</v>
       </c>
       <c r="R52" t="n">
-        <v>6380782</v>
+        <v>6380825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,37 +6613,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876761</v>
+        <v>125876723</v>
       </c>
       <c r="B53" t="n">
-        <v>107195</v>
+        <v>98223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6651,16 +6651,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723360</v>
+        <v>723093</v>
       </c>
       <c r="R53" t="n">
-        <v>6380851</v>
+        <v>6380849</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6724,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876714</v>
+        <v>125876736</v>
       </c>
       <c r="B54" t="n">
-        <v>98302</v>
+        <v>98223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6735,21 +6740,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6764,7 +6769,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6773,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723098</v>
+        <v>723172</v>
       </c>
       <c r="R54" t="n">
-        <v>6380819</v>
+        <v>6380881</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6840,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876681</v>
+        <v>125876686</v>
       </c>
       <c r="B55" t="n">
-        <v>98347</v>
+        <v>98223</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6851,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6889,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>722977</v>
+        <v>723006</v>
       </c>
       <c r="R55" t="n">
-        <v>6380820</v>
+        <v>6380816</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6956,37 +6961,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876786</v>
+        <v>125876677</v>
       </c>
       <c r="B56" t="n">
-        <v>107195</v>
+        <v>98223</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6994,16 +6999,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723329</v>
+        <v>722956</v>
       </c>
       <c r="R56" t="n">
-        <v>6380785</v>
+        <v>6380853</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7067,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876723</v>
+        <v>125876738</v>
       </c>
       <c r="B57" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7097,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7116,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723093</v>
+        <v>723157</v>
       </c>
       <c r="R57" t="n">
-        <v>6380849</v>
+        <v>6380881</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7183,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876661</v>
+        <v>125876761</v>
       </c>
       <c r="B58" t="n">
-        <v>109137</v>
+        <v>107202</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7194,26 +7204,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7221,21 +7231,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723022</v>
+        <v>723360</v>
       </c>
       <c r="R58" t="n">
-        <v>6380875</v>
+        <v>6380851</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7299,37 +7304,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876722</v>
+        <v>125876786</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7337,21 +7342,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723061</v>
+        <v>723329</v>
       </c>
       <c r="R59" t="n">
-        <v>6380859</v>
+        <v>6380785</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876826</v>
+        <v>125876714</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>98309</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7426,26 +7426,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723188</v>
+        <v>723098</v>
       </c>
       <c r="R60" t="n">
-        <v>6380756</v>
+        <v>6380819</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7500,11 +7500,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7536,10 +7531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876736</v>
+        <v>125876681</v>
       </c>
       <c r="B61" t="n">
-        <v>98216</v>
+        <v>98354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,26 +7542,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7585,10 +7580,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723172</v>
+        <v>722977</v>
       </c>
       <c r="R61" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7652,10 +7647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876686</v>
+        <v>125876722</v>
       </c>
       <c r="B62" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7663,26 +7658,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7701,10 +7696,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723006</v>
+        <v>723061</v>
       </c>
       <c r="R62" t="n">
-        <v>6380816</v>
+        <v>6380859</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7768,10 +7763,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876677</v>
+        <v>125876739</v>
       </c>
       <c r="B63" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7798,7 +7793,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7817,10 +7812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>722956</v>
+        <v>723173</v>
       </c>
       <c r="R63" t="n">
-        <v>6380853</v>
+        <v>6380850</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7884,10 +7879,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876739</v>
+        <v>125876826</v>
       </c>
       <c r="B64" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,26 +7890,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723173</v>
+        <v>723188</v>
       </c>
       <c r="R64" t="n">
-        <v>6380850</v>
+        <v>6380756</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7969,6 +7964,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8000,37 +8000,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876738</v>
+        <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>98216</v>
+        <v>109144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723157</v>
+        <v>723022</v>
       </c>
       <c r="R65" t="n">
-        <v>6380881</v>
+        <v>6380875</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125876785</v>
+        <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98216</v>
+        <v>98354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8127,26 +8127,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8232,10 +8232,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876784</v>
+        <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8243,26 +8243,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723343</v>
+        <v>723040</v>
       </c>
       <c r="R67" t="n">
-        <v>6380788</v>
+        <v>6380808</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876695</v>
+        <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723040</v>
+        <v>723296</v>
       </c>
       <c r="R68" t="n">
-        <v>6380808</v>
+        <v>6380797</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876793</v>
+        <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>98354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8475,26 +8475,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723296</v>
+        <v>723022</v>
       </c>
       <c r="R69" t="n">
-        <v>6380797</v>
+        <v>6380875</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876665</v>
+        <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98347</v>
+        <v>98223</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723022</v>
+        <v>723343</v>
       </c>
       <c r="R70" t="n">
-        <v>6380875</v>
+        <v>6380788</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,45 +8928,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876921</v>
+        <v>125876910</v>
       </c>
       <c r="B73" t="n">
-        <v>5492</v>
+        <v>95934</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723364</v>
+        <v>723027</v>
       </c>
       <c r="R73" t="n">
-        <v>6380813</v>
+        <v>6380801</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,11 +9008,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9030,62 +9034,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876741</v>
+        <v>125876921</v>
       </c>
       <c r="B74" t="n">
-        <v>98216</v>
+        <v>5492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219769</v>
+        <v>101410</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723189</v>
+        <v>723364</v>
       </c>
       <c r="R74" t="n">
-        <v>6380869</v>
+        <v>6380813</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9117,6 +9107,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9125,11 +9120,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9146,10 +9136,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876717</v>
+        <v>125876741</v>
       </c>
       <c r="B75" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9176,7 +9166,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9195,10 +9185,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723080</v>
+        <v>723189</v>
       </c>
       <c r="R75" t="n">
-        <v>6380837</v>
+        <v>6380869</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9231,11 +9221,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9267,10 +9252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876776</v>
+        <v>125876716</v>
       </c>
       <c r="B76" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9278,26 +9263,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9316,13 +9301,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R76" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9352,6 +9337,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9383,10 +9373,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876729</v>
+        <v>125876828</v>
       </c>
       <c r="B77" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,26 +9384,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9428,14 +9418,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723135</v>
+        <v>723173</v>
       </c>
       <c r="R77" t="n">
-        <v>6380877</v>
+        <v>6380765</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9481,7 +9471,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9499,10 +9489,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876715</v>
+        <v>125876658</v>
       </c>
       <c r="B78" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9529,7 +9519,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9548,10 +9538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723098</v>
+        <v>723022</v>
       </c>
       <c r="R78" t="n">
-        <v>6380819</v>
+        <v>6380859</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9615,10 +9605,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876910</v>
+        <v>125876717</v>
       </c>
       <c r="B79" t="n">
-        <v>95927</v>
+        <v>98223</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9626,31 +9616,36 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2180</v>
+        <v>219769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9659,13 +9654,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723027</v>
+        <v>723080</v>
       </c>
       <c r="R79" t="n">
-        <v>6380801</v>
+        <v>6380837</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9697,6 +9692,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9705,6 +9705,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9721,10 +9726,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876658</v>
+        <v>125876776</v>
       </c>
       <c r="B80" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9756,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9770,13 +9775,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723022</v>
+        <v>723342</v>
       </c>
       <c r="R80" t="n">
-        <v>6380859</v>
+        <v>6380826</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9837,45 +9842,59 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876757</v>
+        <v>125876729</v>
       </c>
       <c r="B81" t="n">
-        <v>103766</v>
+        <v>98223</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723360</v>
+        <v>723135</v>
       </c>
       <c r="R81" t="n">
-        <v>6380851</v>
+        <v>6380877</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9939,10 +9958,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876716</v>
+        <v>125876715</v>
       </c>
       <c r="B82" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9950,26 +9969,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9988,13 +10007,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723080</v>
+        <v>723098</v>
       </c>
       <c r="R82" t="n">
-        <v>6380837</v>
+        <v>6380819</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10024,11 +10043,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10060,59 +10074,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876828</v>
+        <v>125876757</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>103773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219864</v>
+        <v>220164</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723173</v>
+        <v>723360</v>
       </c>
       <c r="R83" t="n">
-        <v>6380765</v>
+        <v>6380851</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10179,7 +10179,7 @@
         <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98242</v>
+        <v>98249</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876727</v>
+        <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,26 +10535,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10576,10 +10576,10 @@
         <v>723123</v>
       </c>
       <c r="R87" t="n">
-        <v>6380868</v>
+        <v>6380848</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876754</v>
+        <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10689,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R88" t="n">
-        <v>6380853</v>
+        <v>6380868</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10725,11 +10725,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10761,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876666</v>
+        <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98346</v>
+        <v>98359</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10772,26 +10767,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10810,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723022</v>
+        <v>723344</v>
       </c>
       <c r="R89" t="n">
-        <v>6380875</v>
+        <v>6380853</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10846,6 +10841,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10877,10 +10877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876724</v>
+        <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98216</v>
+        <v>98353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10888,26 +10888,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10926,10 +10926,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723123</v>
+        <v>723022</v>
       </c>
       <c r="R90" t="n">
-        <v>6380848</v>
+        <v>6380875</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876781</v>
       </c>
       <c r="B93" t="n">
-        <v>98242</v>
+        <v>98249</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876683</v>
       </c>
       <c r="B94" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11457,59 +11457,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876707</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>98216</v>
+        <v>57648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723077</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11544,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11573,10 +11568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876820</v>
+        <v>125876669</v>
       </c>
       <c r="B96" t="n">
-        <v>98216</v>
+        <v>98353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11584,26 +11579,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11622,10 +11617,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723194</v>
+        <v>723014</v>
       </c>
       <c r="R96" t="n">
-        <v>6380741</v>
+        <v>6380862</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11689,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876772</v>
+        <v>125876820</v>
       </c>
       <c r="B97" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11719,7 +11714,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11738,10 +11733,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723364</v>
+        <v>723194</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11774,11 +11769,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11810,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876697</v>
+        <v>125876719</v>
       </c>
       <c r="B98" t="n">
-        <v>98216</v>
+        <v>98359</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11821,21 +11811,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11859,13 +11849,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723031</v>
+        <v>723068</v>
       </c>
       <c r="R98" t="n">
-        <v>6380827</v>
+        <v>6380835</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11926,10 +11916,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876788</v>
+        <v>125876707</v>
       </c>
       <c r="B99" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11956,7 +11946,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11975,10 +11965,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723320</v>
+        <v>723077</v>
       </c>
       <c r="R99" t="n">
-        <v>6380799</v>
+        <v>6380813</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12042,54 +12032,59 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876945</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>57648</v>
+        <v>98223</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>219769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723296</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380797</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12126,7 +12121,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Födosökshack i murken tall.</t>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12137,6 +12132,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12153,37 +12153,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876740</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>107195</v>
+        <v>98223</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12191,16 +12191,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723183</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380860</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,10 +12269,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876669</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98346</v>
+        <v>98223</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12280,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,10 +12318,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723014</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380862</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12380,37 +12385,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>98352</v>
+        <v>107202</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12418,24 +12423,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876745</v>
+        <v>125876685</v>
       </c>
       <c r="B104" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723252</v>
+        <v>722988</v>
       </c>
       <c r="R104" t="n">
-        <v>6380854</v>
+        <v>6380785</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876777</v>
+        <v>125876675</v>
       </c>
       <c r="B105" t="n">
-        <v>98352</v>
+        <v>98223</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12623,26 +12623,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,13 +12661,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723355</v>
+        <v>722934</v>
       </c>
       <c r="R105" t="n">
-        <v>6380807</v>
+        <v>6380847</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876706</v>
+        <v>125876777</v>
       </c>
       <c r="B106" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723064</v>
+        <v>723355</v>
       </c>
       <c r="R106" t="n">
-        <v>6380825</v>
+        <v>6380807</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876702</v>
+        <v>125876706</v>
       </c>
       <c r="B107" t="n">
-        <v>98346</v>
+        <v>98359</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723038</v>
+        <v>723064</v>
       </c>
       <c r="R107" t="n">
-        <v>6380832</v>
+        <v>6380825</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876755</v>
+        <v>125876702</v>
       </c>
       <c r="B108" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,10 +13009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723344</v>
+        <v>723038</v>
       </c>
       <c r="R108" t="n">
-        <v>6380853</v>
+        <v>6380832</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876685</v>
+        <v>125876755</v>
       </c>
       <c r="B109" t="n">
-        <v>98216</v>
+        <v>98354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>722988</v>
+        <v>723344</v>
       </c>
       <c r="R109" t="n">
-        <v>6380785</v>
+        <v>6380853</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876675</v>
+        <v>125876745</v>
       </c>
       <c r="B110" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>722934</v>
+        <v>723252</v>
       </c>
       <c r="R110" t="n">
-        <v>6380847</v>
+        <v>6380854</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>125876699</v>
       </c>
       <c r="B111" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13424,10 +13424,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876664</v>
+        <v>125876765</v>
       </c>
       <c r="B112" t="n">
-        <v>98216</v>
+        <v>98353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,21 +13435,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723022</v>
+        <v>723369</v>
       </c>
       <c r="R112" t="n">
-        <v>6380875</v>
+        <v>6380880</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,37 +13540,37 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876782</v>
+        <v>125876811</v>
       </c>
       <c r="B113" t="n">
-        <v>98216</v>
+        <v>107202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13578,21 +13578,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723338</v>
+        <v>723234</v>
       </c>
       <c r="R113" t="n">
-        <v>6380799</v>
+        <v>6380772</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,37 +13651,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876811</v>
+        <v>125876664</v>
       </c>
       <c r="B114" t="n">
-        <v>107195</v>
+        <v>98223</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13694,16 +13689,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723234</v>
+        <v>723022</v>
       </c>
       <c r="R114" t="n">
-        <v>6380772</v>
+        <v>6380875</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,10 +13767,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B115" t="n">
-        <v>98346</v>
+        <v>98223</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13778,26 +13778,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R115" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,45 +13883,59 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876819</v>
+        <v>125876659</v>
       </c>
       <c r="B116" t="n">
-        <v>109137</v>
+        <v>98249</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723194</v>
+        <v>723022</v>
       </c>
       <c r="R116" t="n">
-        <v>6380741</v>
+        <v>6380869</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13988,7 +14002,7 @@
         <v>125876676</v>
       </c>
       <c r="B117" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14104,7 +14118,7 @@
         <v>125876709</v>
       </c>
       <c r="B118" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14217,59 +14231,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876674</v>
+        <v>125876819</v>
       </c>
       <c r="B119" t="n">
-        <v>98216</v>
+        <v>109144</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>722924</v>
+        <v>723194</v>
       </c>
       <c r="R119" t="n">
-        <v>6380847</v>
+        <v>6380741</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876823</v>
+        <v>125876674</v>
       </c>
       <c r="B120" t="n">
-        <v>110404</v>
+        <v>98223</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14344,34 +14344,48 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219711</v>
+        <v>219769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723189</v>
+        <v>722924</v>
       </c>
       <c r="R120" t="n">
-        <v>6380746</v>
+        <v>6380847</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14435,10 +14449,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876659</v>
+        <v>125876823</v>
       </c>
       <c r="B121" t="n">
-        <v>98242</v>
+        <v>110411</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14446,48 +14460,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>223591</v>
+        <v>219711</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R121" t="n">
-        <v>6380869</v>
+        <v>6380746</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14551,10 +14551,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876690</v>
+        <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>98216</v>
+        <v>98365</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14562,26 +14562,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14589,21 +14589,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723004</v>
+        <v>723098</v>
       </c>
       <c r="R122" t="n">
-        <v>6380791</v>
+        <v>6380819</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14667,10 +14662,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876763</v>
+        <v>125876690</v>
       </c>
       <c r="B123" t="n">
-        <v>98216</v>
+        <v>98223</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14697,7 +14692,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14716,10 +14711,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723370</v>
+        <v>723004</v>
       </c>
       <c r="R123" t="n">
-        <v>6380863</v>
+        <v>6380791</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14783,10 +14778,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876710</v>
+        <v>125876767</v>
       </c>
       <c r="B124" t="n">
-        <v>98358</v>
+        <v>98359</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14794,26 +14789,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>219864</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14821,16 +14816,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723098</v>
+        <v>723375</v>
       </c>
       <c r="R124" t="n">
-        <v>6380819</v>
+        <v>6380878</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,32 +14894,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876792</v>
+        <v>125876766</v>
       </c>
       <c r="B125" t="n">
-        <v>107195</v>
+        <v>98359</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -14932,16 +14932,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723296</v>
+        <v>723369</v>
       </c>
       <c r="R125" t="n">
-        <v>6380797</v>
+        <v>6380880</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,27 +15010,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876767</v>
+        <v>125876667</v>
       </c>
       <c r="B126" t="n">
-        <v>98352</v>
+        <v>109144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -15035,7 +15040,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15054,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723375</v>
+        <v>723014</v>
       </c>
       <c r="R126" t="n">
-        <v>6380878</v>
+        <v>6380862</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,27 +15126,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876766</v>
+        <v>125876718</v>
       </c>
       <c r="B127" t="n">
-        <v>98352</v>
+        <v>109144</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15151,7 +15156,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15170,10 +15175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723369</v>
+        <v>723068</v>
       </c>
       <c r="R127" t="n">
-        <v>6380880</v>
+        <v>6380835</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,32 +15242,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876667</v>
+        <v>125876763</v>
       </c>
       <c r="B128" t="n">
-        <v>109137</v>
+        <v>98223</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15286,10 +15291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723014</v>
+        <v>723370</v>
       </c>
       <c r="R128" t="n">
-        <v>6380862</v>
+        <v>6380863</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,10 +15358,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876718</v>
+        <v>125876792</v>
       </c>
       <c r="B129" t="n">
-        <v>109137</v>
+        <v>107202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15364,26 +15369,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15391,21 +15396,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723068</v>
+        <v>723296</v>
       </c>
       <c r="R129" t="n">
-        <v>6380835</v>
+        <v>6380797</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,7 +1630,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876673</v>
+        <v>125876780</v>
       </c>
       <c r="B10" t="n">
         <v>98223</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722989</v>
+        <v>723343</v>
       </c>
       <c r="R10" t="n">
-        <v>6380861</v>
+        <v>6380811</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876780</v>
+        <v>125876673</v>
       </c>
       <c r="B11" t="n">
         <v>98223</v>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723343</v>
+        <v>722989</v>
       </c>
       <c r="R11" t="n">
-        <v>6380811</v>
+        <v>6380861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -4651,37 +4651,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876813</v>
+        <v>125876778</v>
       </c>
       <c r="B36" t="n">
-        <v>107202</v>
+        <v>98223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4689,19 +4689,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723238</v>
+        <v>723355</v>
       </c>
       <c r="R36" t="n">
-        <v>6380770</v>
+        <v>6380807</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876778</v>
+        <v>125876752</v>
       </c>
       <c r="B37" t="n">
         <v>98223</v>
@@ -4792,7 +4797,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,13 +4816,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723355</v>
+        <v>723321</v>
       </c>
       <c r="R37" t="n">
-        <v>6380807</v>
+        <v>6380856</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4878,37 +4883,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876752</v>
+        <v>125876813</v>
       </c>
       <c r="B38" t="n">
-        <v>98223</v>
+        <v>107202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4916,21 +4921,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723238</v>
       </c>
       <c r="R38" t="n">
-        <v>6380856</v>
+        <v>6380770</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876723</v>
+        <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98223</v>
+        <v>98309</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6624,26 +6624,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723093</v>
+        <v>723098</v>
       </c>
       <c r="R53" t="n">
-        <v>6380849</v>
+        <v>6380819</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876736</v>
+        <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98223</v>
+        <v>98354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723172</v>
+        <v>722977</v>
       </c>
       <c r="R54" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876686</v>
+        <v>125876722</v>
       </c>
       <c r="B55" t="n">
-        <v>98223</v>
+        <v>98359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6856,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723006</v>
+        <v>723061</v>
       </c>
       <c r="R55" t="n">
-        <v>6380816</v>
+        <v>6380859</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876677</v>
+        <v>125876739</v>
       </c>
       <c r="B56" t="n">
         <v>98223</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>722956</v>
+        <v>723173</v>
       </c>
       <c r="R56" t="n">
-        <v>6380853</v>
+        <v>6380850</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876738</v>
+        <v>125876826</v>
       </c>
       <c r="B57" t="n">
-        <v>98223</v>
+        <v>98359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7088,26 +7088,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723157</v>
+        <v>723188</v>
       </c>
       <c r="R57" t="n">
-        <v>6380881</v>
+        <v>6380756</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7162,6 +7162,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7193,10 +7198,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876761</v>
+        <v>125876661</v>
       </c>
       <c r="B58" t="n">
-        <v>107202</v>
+        <v>109144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,26 +7209,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7231,16 +7236,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723360</v>
+        <v>723022</v>
       </c>
       <c r="R58" t="n">
-        <v>6380851</v>
+        <v>6380875</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7304,37 +7314,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876786</v>
+        <v>125876723</v>
       </c>
       <c r="B59" t="n">
-        <v>107202</v>
+        <v>98223</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7342,16 +7352,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723329</v>
+        <v>723093</v>
       </c>
       <c r="R59" t="n">
-        <v>6380785</v>
+        <v>6380849</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7415,10 +7430,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876714</v>
+        <v>125876736</v>
       </c>
       <c r="B60" t="n">
-        <v>98309</v>
+        <v>98223</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7426,21 +7441,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7455,7 +7470,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7464,10 +7479,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723098</v>
+        <v>723172</v>
       </c>
       <c r="R60" t="n">
-        <v>6380819</v>
+        <v>6380881</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7531,10 +7546,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876681</v>
+        <v>125876686</v>
       </c>
       <c r="B61" t="n">
-        <v>98354</v>
+        <v>98223</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7542,26 +7557,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7580,10 +7595,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>722977</v>
+        <v>723006</v>
       </c>
       <c r="R61" t="n">
-        <v>6380820</v>
+        <v>6380816</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7647,10 +7662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876722</v>
+        <v>125876677</v>
       </c>
       <c r="B62" t="n">
-        <v>98359</v>
+        <v>98223</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7658,21 +7673,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7696,10 +7711,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723061</v>
+        <v>722956</v>
       </c>
       <c r="R62" t="n">
-        <v>6380859</v>
+        <v>6380853</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7763,7 +7778,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876739</v>
+        <v>125876738</v>
       </c>
       <c r="B63" t="n">
         <v>98223</v>
@@ -7812,10 +7827,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723173</v>
+        <v>723157</v>
       </c>
       <c r="R63" t="n">
-        <v>6380850</v>
+        <v>6380881</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7879,37 +7894,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876826</v>
+        <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>98359</v>
+        <v>107202</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7917,21 +7932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723188</v>
+        <v>723360</v>
       </c>
       <c r="R64" t="n">
-        <v>6380756</v>
+        <v>6380851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7964,11 +7974,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8000,10 +8005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876661</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>109144</v>
+        <v>107202</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8011,26 +8016,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8038,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723022</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380875</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -9489,59 +9489,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876658</v>
+        <v>125876757</v>
       </c>
       <c r="B78" t="n">
-        <v>98223</v>
+        <v>103773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723022</v>
+        <v>723360</v>
       </c>
       <c r="R78" t="n">
-        <v>6380859</v>
+        <v>6380851</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9605,7 +9591,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876717</v>
+        <v>125876658</v>
       </c>
       <c r="B79" t="n">
         <v>98223</v>
@@ -9635,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9654,10 +9640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R79" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9690,11 +9676,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9726,7 +9707,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876776</v>
+        <v>125876717</v>
       </c>
       <c r="B80" t="n">
         <v>98223</v>
@@ -9756,7 +9737,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9775,13 +9756,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R80" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9811,6 +9792,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9842,7 +9828,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876729</v>
+        <v>125876776</v>
       </c>
       <c r="B81" t="n">
         <v>98223</v>
@@ -9872,7 +9858,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9891,13 +9877,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723135</v>
+        <v>723342</v>
       </c>
       <c r="R81" t="n">
-        <v>6380877</v>
+        <v>6380826</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9958,7 +9944,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876715</v>
+        <v>125876729</v>
       </c>
       <c r="B82" t="n">
         <v>98223</v>
@@ -9988,7 +9974,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10007,10 +9993,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723098</v>
+        <v>723135</v>
       </c>
       <c r="R82" t="n">
-        <v>6380819</v>
+        <v>6380877</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10074,45 +10060,59 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876757</v>
+        <v>125876715</v>
       </c>
       <c r="B83" t="n">
-        <v>103773</v>
+        <v>98223</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R83" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876744</v>
+        <v>125876781</v>
       </c>
       <c r="B92" t="n">
-        <v>98359</v>
+        <v>98249</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723252</v>
+        <v>723343</v>
       </c>
       <c r="R92" t="n">
-        <v>6380854</v>
+        <v>6380811</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876781</v>
+        <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98249</v>
+        <v>98359</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,21 +11236,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723343</v>
+        <v>723252</v>
       </c>
       <c r="R93" t="n">
-        <v>6380811</v>
+        <v>6380854</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -13424,10 +13424,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876765</v>
+        <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98353</v>
+        <v>98223</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,21 +13435,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723369</v>
+        <v>723022</v>
       </c>
       <c r="R112" t="n">
-        <v>6380880</v>
+        <v>6380875</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,37 +13540,37 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876811</v>
+        <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>107202</v>
+        <v>98223</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13578,16 +13578,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723234</v>
+        <v>723338</v>
       </c>
       <c r="R113" t="n">
-        <v>6380772</v>
+        <v>6380799</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13651,10 +13656,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876664</v>
+        <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98223</v>
+        <v>98353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13662,21 +13667,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13700,10 +13705,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723022</v>
+        <v>723369</v>
       </c>
       <c r="R114" t="n">
-        <v>6380875</v>
+        <v>6380880</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,37 +13772,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876782</v>
+        <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>98223</v>
+        <v>107202</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13805,21 +13810,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723338</v>
+        <v>723234</v>
       </c>
       <c r="R115" t="n">
-        <v>6380799</v>
+        <v>6380772</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876659</v>
+        <v>125876676</v>
       </c>
       <c r="B116" t="n">
-        <v>98249</v>
+        <v>98354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723022</v>
+        <v>722956</v>
       </c>
       <c r="R116" t="n">
-        <v>6380869</v>
+        <v>6380853</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B117" t="n">
-        <v>98354</v>
+        <v>98359</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,26 +14010,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R117" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14115,10 +14115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876709</v>
+        <v>125876674</v>
       </c>
       <c r="B118" t="n">
-        <v>98359</v>
+        <v>98223</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14126,26 +14126,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>723074</v>
+        <v>722924</v>
       </c>
       <c r="R118" t="n">
-        <v>6380823</v>
+        <v>6380847</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14231,27 +14231,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876819</v>
+        <v>125876823</v>
       </c>
       <c r="B119" t="n">
-        <v>109144</v>
+        <v>110411</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723194</v>
+        <v>723189</v>
       </c>
       <c r="R119" t="n">
-        <v>6380741</v>
+        <v>6380746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876674</v>
+        <v>125876659</v>
       </c>
       <c r="B120" t="n">
-        <v>98223</v>
+        <v>98249</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14344,26 +14344,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14382,10 +14382,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>722924</v>
+        <v>723022</v>
       </c>
       <c r="R120" t="n">
-        <v>6380847</v>
+        <v>6380869</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14449,27 +14449,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876823</v>
+        <v>125876819</v>
       </c>
       <c r="B121" t="n">
-        <v>110411</v>
+        <v>109144</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -14484,10 +14484,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723189</v>
+        <v>723194</v>
       </c>
       <c r="R121" t="n">
-        <v>6380746</v>
+        <v>6380741</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -15467,6 +15467,3589 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>126004016</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>723457</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6380869</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>126003980</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>723365</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6380795</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>126003999</v>
+      </c>
+      <c r="B132" t="n">
+        <v>109144</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>723516</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6380880</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>126003997</v>
+      </c>
+      <c r="B133" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>723483</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6380826</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>126004010</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>723469</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6380865</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>126004004</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>723496</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6380865</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>126003992</v>
+      </c>
+      <c r="B136" t="n">
+        <v>109144</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>723458</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6380818</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>126003974</v>
+      </c>
+      <c r="B137" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>723349</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6380791</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>126003993</v>
+      </c>
+      <c r="B138" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>723470</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6380822</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>126003995</v>
+      </c>
+      <c r="B139" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>723470</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6380826</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>126003978</v>
+      </c>
+      <c r="B140" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>723349</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6380791</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>126003972</v>
+      </c>
+      <c r="B141" t="n">
+        <v>103773</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>723461</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6380842</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126003986</v>
+      </c>
+      <c r="B142" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>723379</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6380799</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>126003970</v>
+      </c>
+      <c r="B143" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>723221</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6380844</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>126004003</v>
+      </c>
+      <c r="B144" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>723512</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6380870</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>126003998</v>
+      </c>
+      <c r="B145" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>723508</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6380857</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>126003971</v>
+      </c>
+      <c r="B146" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>723257</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6380842</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>126003989</v>
+      </c>
+      <c r="B147" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>723395</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6380817</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>126003976</v>
+      </c>
+      <c r="B148" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>723349</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6380791</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>126004013</v>
+      </c>
+      <c r="B149" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>723461</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6380878</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>126004076</v>
+      </c>
+      <c r="B150" t="n">
+        <v>5492</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>723369</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6380814</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>126004012</v>
+      </c>
+      <c r="B151" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>723461</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6380878</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>126003987</v>
+      </c>
+      <c r="B152" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>723390</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6380799</v>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>126003988</v>
+      </c>
+      <c r="B153" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>723390</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6380809</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>126004002</v>
+      </c>
+      <c r="B154" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>723516</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6380880</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>126003996</v>
+      </c>
+      <c r="B155" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>723479</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6380833</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>126004014</v>
+      </c>
+      <c r="B156" t="n">
+        <v>98354</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>723461</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6380878</v>
+      </c>
+      <c r="S156" t="n">
+        <v>5</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>126003990</v>
+      </c>
+      <c r="B157" t="n">
+        <v>99006</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>723426</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6380811</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Agmyrkant.</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>126004000</v>
+      </c>
+      <c r="B158" t="n">
+        <v>98309</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>723516</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6380880</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>126003973</v>
+      </c>
+      <c r="B159" t="n">
+        <v>110411</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>723349</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6380791</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>126003983</v>
+      </c>
+      <c r="B160" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>723369</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6380814</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876780</v>
+        <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723343</v>
+        <v>722989</v>
       </c>
       <c r="R10" t="n">
-        <v>6380811</v>
+        <v>6380861</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876673</v>
+        <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>722989</v>
+        <v>723343</v>
       </c>
       <c r="R11" t="n">
-        <v>6380861</v>
+        <v>6380811</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876817</v>
+        <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,26 +1873,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723210</v>
+        <v>723017</v>
       </c>
       <c r="R12" t="n">
-        <v>6380786</v>
+        <v>6380808</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876703</v>
+        <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1989,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723050</v>
+        <v>723210</v>
       </c>
       <c r="R13" t="n">
-        <v>6380829</v>
+        <v>6380786</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876749</v>
+        <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723321</v>
+        <v>723050</v>
       </c>
       <c r="R14" t="n">
-        <v>6380856</v>
+        <v>6380829</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125876691</v>
+        <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723017</v>
+        <v>723321</v>
       </c>
       <c r="R15" t="n">
-        <v>6380808</v>
+        <v>6380856</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876672</v>
+        <v>125876696</v>
       </c>
       <c r="B20" t="n">
-        <v>98354</v>
+        <v>98224</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>722989</v>
+        <v>723042</v>
       </c>
       <c r="R20" t="n">
-        <v>6380861</v>
+        <v>6380816</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876732</v>
+        <v>125876672</v>
       </c>
       <c r="B21" t="n">
-        <v>98223</v>
+        <v>98355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723148</v>
+        <v>722989</v>
       </c>
       <c r="R21" t="n">
-        <v>6380883</v>
+        <v>6380861</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876794</v>
+        <v>125876732</v>
       </c>
       <c r="B22" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723296</v>
+        <v>723148</v>
       </c>
       <c r="R22" t="n">
-        <v>6380797</v>
+        <v>6380883</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876769</v>
+        <v>125876818</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,26 +3149,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723375</v>
+        <v>723210</v>
       </c>
       <c r="R23" t="n">
-        <v>6380878</v>
+        <v>6380786</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3223,6 +3223,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3254,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876696</v>
+        <v>125876794</v>
       </c>
       <c r="B24" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3289,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3303,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723042</v>
+        <v>723296</v>
       </c>
       <c r="R24" t="n">
-        <v>6380816</v>
+        <v>6380797</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3370,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876818</v>
+        <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98223</v>
+        <v>98366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3410,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723210</v>
+        <v>723375</v>
       </c>
       <c r="R25" t="n">
-        <v>6380786</v>
+        <v>6380878</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3455,11 +3460,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,7 +3494,7 @@
         <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>125876731</v>
       </c>
       <c r="B27" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876712</v>
+        <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98353</v>
+        <v>98224</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R31" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,6 +4146,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876805</v>
+        <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>98354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,26 +4193,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R32" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4262,11 +4267,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876806</v>
+        <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B34" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4468,13 +4468,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R34" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876698</v>
+        <v>125876682</v>
       </c>
       <c r="B35" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723026</v>
+        <v>722977</v>
       </c>
       <c r="R35" t="n">
-        <v>6380845</v>
+        <v>6380820</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876778</v>
+        <v>125876698</v>
       </c>
       <c r="B36" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,26 +4662,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723355</v>
+        <v>723026</v>
       </c>
       <c r="R36" t="n">
-        <v>6380807</v>
+        <v>6380845</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>125876752</v>
       </c>
       <c r="B37" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>125876813</v>
       </c>
       <c r="B38" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98249</v>
+        <v>98250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876803</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>107202</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,19 +5960,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723244</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380753</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6033,10 +6038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98310</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6044,21 +6049,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6073,7 +6078,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6082,13 +6087,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R48" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6149,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876733</v>
+        <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98309</v>
+        <v>98224</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,26 +6165,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6189,7 +6194,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6198,13 +6203,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723172</v>
+        <v>723221</v>
       </c>
       <c r="R49" t="n">
-        <v>6380881</v>
+        <v>6380864</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6265,10 +6270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876743</v>
+        <v>125876814</v>
       </c>
       <c r="B50" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6314,13 +6319,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723221</v>
+        <v>723228</v>
       </c>
       <c r="R50" t="n">
-        <v>6380864</v>
+        <v>6380782</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876814</v>
+        <v>125876705</v>
       </c>
       <c r="B51" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,10 +6435,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723228</v>
+        <v>723064</v>
       </c>
       <c r="R51" t="n">
-        <v>6380782</v>
+        <v>6380825</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,37 +6502,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876705</v>
+        <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>98223</v>
+        <v>107203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6535,21 +6540,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723064</v>
+        <v>723244</v>
       </c>
       <c r="R52" t="n">
-        <v>6380825</v>
+        <v>6380753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6616,7 +6616,7 @@
         <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876722</v>
+        <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6856,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723061</v>
+        <v>723093</v>
       </c>
       <c r="R55" t="n">
-        <v>6380859</v>
+        <v>6380849</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876739</v>
+        <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723173</v>
+        <v>723172</v>
       </c>
       <c r="R56" t="n">
-        <v>6380850</v>
+        <v>6380881</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876826</v>
+        <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7088,26 +7088,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723188</v>
+        <v>723006</v>
       </c>
       <c r="R57" t="n">
-        <v>6380756</v>
+        <v>6380816</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7162,11 +7162,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7198,27 +7193,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876661</v>
+        <v>125876722</v>
       </c>
       <c r="B58" t="n">
-        <v>109144</v>
+        <v>98360</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7228,7 +7223,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7247,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723022</v>
+        <v>723061</v>
       </c>
       <c r="R58" t="n">
-        <v>6380875</v>
+        <v>6380859</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7314,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876723</v>
+        <v>125876677</v>
       </c>
       <c r="B59" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7344,7 +7339,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7363,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723093</v>
+        <v>722956</v>
       </c>
       <c r="R59" t="n">
-        <v>6380849</v>
+        <v>6380853</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7430,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876736</v>
+        <v>125876739</v>
       </c>
       <c r="B60" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7460,7 +7455,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7479,10 +7474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723172</v>
+        <v>723173</v>
       </c>
       <c r="R60" t="n">
-        <v>6380881</v>
+        <v>6380850</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7546,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876686</v>
+        <v>125876738</v>
       </c>
       <c r="B61" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7571,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723006</v>
+        <v>723157</v>
       </c>
       <c r="R61" t="n">
-        <v>6380816</v>
+        <v>6380881</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7662,10 +7657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876677</v>
+        <v>125876826</v>
       </c>
       <c r="B62" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7673,26 +7668,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7711,10 +7706,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>722956</v>
+        <v>723188</v>
       </c>
       <c r="R62" t="n">
-        <v>6380853</v>
+        <v>6380756</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7747,6 +7742,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,37 +7778,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876738</v>
+        <v>125876761</v>
       </c>
       <c r="B63" t="n">
-        <v>98223</v>
+        <v>107203</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7816,21 +7816,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723157</v>
+        <v>723360</v>
       </c>
       <c r="R63" t="n">
-        <v>6380881</v>
+        <v>6380851</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7894,10 +7889,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876761</v>
+        <v>125876786</v>
       </c>
       <c r="B64" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723360</v>
+        <v>723329</v>
       </c>
       <c r="R64" t="n">
-        <v>6380851</v>
+        <v>6380785</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8005,10 +8000,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876786</v>
+        <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>107202</v>
+        <v>109145</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8016,26 +8011,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8043,16 +8038,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723329</v>
+        <v>723022</v>
       </c>
       <c r="R65" t="n">
-        <v>6380785</v>
+        <v>6380875</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,54 +8928,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876910</v>
+        <v>125876921</v>
       </c>
       <c r="B73" t="n">
-        <v>95934</v>
+        <v>5492</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723027</v>
+        <v>723364</v>
       </c>
       <c r="R73" t="n">
-        <v>6380801</v>
+        <v>6380813</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9008,6 +8999,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9034,45 +9030,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876921</v>
+        <v>125876910</v>
       </c>
       <c r="B74" t="n">
-        <v>5492</v>
+        <v>95935</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723364</v>
+        <v>723027</v>
       </c>
       <c r="R74" t="n">
-        <v>6380813</v>
+        <v>6380801</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9105,11 +9110,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9139,7 +9139,7 @@
         <v>125876741</v>
       </c>
       <c r="B75" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9252,10 +9252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876716</v>
+        <v>125876658</v>
       </c>
       <c r="B76" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9263,26 +9263,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9301,13 +9301,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R76" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9337,11 +9337,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9373,10 +9368,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876828</v>
+        <v>125876717</v>
       </c>
       <c r="B77" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9384,26 +9379,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9418,14 +9413,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723173</v>
+        <v>723080</v>
       </c>
       <c r="R77" t="n">
-        <v>6380765</v>
+        <v>6380837</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9460,6 +9455,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9489,48 +9489,62 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876757</v>
+        <v>125876716</v>
       </c>
       <c r="B78" t="n">
-        <v>103773</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723360</v>
+        <v>723080</v>
       </c>
       <c r="R78" t="n">
-        <v>6380851</v>
+        <v>6380837</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9560,6 +9574,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9591,10 +9610,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876658</v>
+        <v>125876776</v>
       </c>
       <c r="B79" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9621,7 +9640,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9640,13 +9659,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723022</v>
+        <v>723342</v>
       </c>
       <c r="R79" t="n">
-        <v>6380859</v>
+        <v>6380826</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9707,10 +9726,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876717</v>
+        <v>125876729</v>
       </c>
       <c r="B80" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9756,10 +9775,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723080</v>
+        <v>723135</v>
       </c>
       <c r="R80" t="n">
-        <v>6380837</v>
+        <v>6380877</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9792,11 +9811,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9828,10 +9842,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876776</v>
+        <v>125876828</v>
       </c>
       <c r="B81" t="n">
-        <v>98223</v>
+        <v>98360</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9839,26 +9853,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9873,17 +9887,17 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723342</v>
+        <v>723173</v>
       </c>
       <c r="R81" t="n">
-        <v>6380826</v>
+        <v>6380765</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9926,7 +9940,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9944,10 +9958,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876729</v>
+        <v>125876715</v>
       </c>
       <c r="B82" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9974,7 +9988,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9993,10 +10007,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723135</v>
+        <v>723098</v>
       </c>
       <c r="R82" t="n">
-        <v>6380877</v>
+        <v>6380819</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10060,59 +10074,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876715</v>
+        <v>125876757</v>
       </c>
       <c r="B83" t="n">
-        <v>98223</v>
+        <v>103774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723098</v>
+        <v>723360</v>
       </c>
       <c r="R83" t="n">
-        <v>6380819</v>
+        <v>6380851</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10179,7 +10179,7 @@
         <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98249</v>
+        <v>98250</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>125876781</v>
       </c>
       <c r="B92" t="n">
-        <v>98249</v>
+        <v>98250</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876683</v>
       </c>
       <c r="B94" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11568,37 +11568,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876669</v>
+        <v>125876740</v>
       </c>
       <c r="B96" t="n">
-        <v>98353</v>
+        <v>107203</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11606,21 +11606,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723014</v>
+        <v>723183</v>
       </c>
       <c r="R96" t="n">
-        <v>6380862</v>
+        <v>6380860</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11684,10 +11679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876820</v>
+        <v>125876707</v>
       </c>
       <c r="B97" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11714,7 +11709,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11733,10 +11728,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723194</v>
+        <v>723077</v>
       </c>
       <c r="R97" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876719</v>
+        <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98359</v>
+        <v>98354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11811,21 +11806,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11849,13 +11844,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723068</v>
+        <v>723014</v>
       </c>
       <c r="R98" t="n">
-        <v>6380835</v>
+        <v>6380862</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11916,10 +11911,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876707</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11946,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11965,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723077</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12035,7 +12030,7 @@
         <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12156,7 +12151,7 @@
         <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12272,7 +12267,7 @@
         <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12385,37 +12380,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>107202</v>
+        <v>98360</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12423,19 +12418,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876685</v>
+        <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>722988</v>
+        <v>723252</v>
       </c>
       <c r="R104" t="n">
-        <v>6380785</v>
+        <v>6380854</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876675</v>
+        <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,13 +12661,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>722934</v>
+        <v>722988</v>
       </c>
       <c r="R105" t="n">
-        <v>6380847</v>
+        <v>6380785</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876777</v>
+        <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12739,26 +12739,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723355</v>
+        <v>722934</v>
       </c>
       <c r="R106" t="n">
-        <v>6380807</v>
+        <v>6380847</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876706</v>
+        <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723064</v>
+        <v>723026</v>
       </c>
       <c r="R107" t="n">
-        <v>6380825</v>
+        <v>6380845</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876702</v>
+        <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98353</v>
+        <v>98360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723038</v>
+        <v>723355</v>
       </c>
       <c r="R108" t="n">
-        <v>6380832</v>
+        <v>6380807</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876755</v>
+        <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723344</v>
+        <v>723064</v>
       </c>
       <c r="R109" t="n">
-        <v>6380853</v>
+        <v>6380825</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876745</v>
+        <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98223</v>
+        <v>98354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723252</v>
+        <v>723038</v>
       </c>
       <c r="R110" t="n">
-        <v>6380854</v>
+        <v>6380832</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876699</v>
+        <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98223</v>
+        <v>98355</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723026</v>
+        <v>723344</v>
       </c>
       <c r="R111" t="n">
-        <v>6380845</v>
+        <v>6380853</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876676</v>
+        <v>125876674</v>
       </c>
       <c r="B116" t="n">
-        <v>98354</v>
+        <v>98224</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722956</v>
+        <v>722924</v>
       </c>
       <c r="R116" t="n">
-        <v>6380853</v>
+        <v>6380847</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876709</v>
+        <v>125876823</v>
       </c>
       <c r="B117" t="n">
-        <v>98359</v>
+        <v>110412</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,16 +14010,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219864</v>
+        <v>219711</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14027,31 +14027,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723074</v>
+        <v>723189</v>
       </c>
       <c r="R117" t="n">
-        <v>6380823</v>
+        <v>6380746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14115,10 +14101,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876674</v>
+        <v>125876676</v>
       </c>
       <c r="B118" t="n">
-        <v>98223</v>
+        <v>98355</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14126,26 +14112,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14164,10 +14150,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722924</v>
+        <v>722956</v>
       </c>
       <c r="R118" t="n">
-        <v>6380847</v>
+        <v>6380853</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14231,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876823</v>
+        <v>125876709</v>
       </c>
       <c r="B119" t="n">
-        <v>110411</v>
+        <v>98360</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14242,16 +14228,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219711</v>
+        <v>219864</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14259,17 +14245,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723189</v>
+        <v>723074</v>
       </c>
       <c r="R119" t="n">
-        <v>6380746</v>
+        <v>6380823</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,59 +14333,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876659</v>
+        <v>125876819</v>
       </c>
       <c r="B120" t="n">
-        <v>98249</v>
+        <v>109145</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723022</v>
+        <v>723194</v>
       </c>
       <c r="R120" t="n">
-        <v>6380869</v>
+        <v>6380741</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14449,45 +14435,59 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876819</v>
+        <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>109144</v>
+        <v>98250</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723194</v>
+        <v>723022</v>
       </c>
       <c r="R121" t="n">
-        <v>6380741</v>
+        <v>6380869</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14554,7 +14554,7 @@
         <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>125876690</v>
       </c>
       <c r="B123" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>125876767</v>
       </c>
       <c r="B124" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14894,10 +14894,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876766</v>
+        <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>98359</v>
+        <v>98224</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14905,26 +14905,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14943,10 +14943,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723369</v>
+        <v>723370</v>
       </c>
       <c r="R125" t="n">
-        <v>6380880</v>
+        <v>6380863</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15010,27 +15010,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876667</v>
+        <v>125876766</v>
       </c>
       <c r="B126" t="n">
-        <v>109144</v>
+        <v>98360</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723014</v>
+        <v>723369</v>
       </c>
       <c r="R126" t="n">
-        <v>6380862</v>
+        <v>6380880</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876718</v>
+        <v>125876667</v>
       </c>
       <c r="B127" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15175,10 +15175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723068</v>
+        <v>723014</v>
       </c>
       <c r="R127" t="n">
-        <v>6380835</v>
+        <v>6380862</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15242,32 +15242,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876763</v>
+        <v>125876718</v>
       </c>
       <c r="B128" t="n">
-        <v>98223</v>
+        <v>109145</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723370</v>
+        <v>723068</v>
       </c>
       <c r="R128" t="n">
-        <v>6380863</v>
+        <v>6380835</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15361,7 +15361,7 @@
         <v>125876792</v>
       </c>
       <c r="B129" t="n">
-        <v>107202</v>
+        <v>107203</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126003997</v>
       </c>
       <c r="B133" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>103773</v>
+        <v>103774</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,62 +17548,48 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126003976</v>
+        <v>126004076</v>
       </c>
       <c r="B148" t="n">
-        <v>98249</v>
+        <v>5492</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>223591</v>
+        <v>101410</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723349</v>
+        <v>723369</v>
       </c>
       <c r="R148" t="n">
-        <v>6380791</v>
+        <v>6380814</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17633,6 +17619,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17667,7 +17658,7 @@
         <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17780,48 +17771,62 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126004076</v>
+        <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>5492</v>
+        <v>98250</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>723369</v>
+        <v>723349</v>
       </c>
       <c r="R150" t="n">
-        <v>6380814</v>
+        <v>6380791</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17851,11 +17856,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>126003996</v>
       </c>
       <c r="B155" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>126004014</v>
       </c>
       <c r="B156" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>99006</v>
+        <v>99007</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110411</v>
+        <v>110412</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125876696</v>
       </c>
       <c r="B20" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>125876672</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>125876732</v>
       </c>
       <c r="B22" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>125876818</v>
       </c>
       <c r="B23" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>125876794</v>
       </c>
       <c r="B24" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876656</v>
+        <v>125876768</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>107205</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,21 +3529,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723038</v>
+        <v>723375</v>
       </c>
       <c r="R26" t="n">
-        <v>6380861</v>
+        <v>6380878</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,37 +3602,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876731</v>
+        <v>125876815</v>
       </c>
       <c r="B27" t="n">
-        <v>98360</v>
+        <v>107205</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3645,21 +3640,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723148</v>
+        <v>723209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380883</v>
+        <v>6380775</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3723,10 +3713,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876708</v>
+        <v>125876656</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3753,7 +3743,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3772,10 +3762,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723077</v>
+        <v>723038</v>
       </c>
       <c r="R28" t="n">
-        <v>6380813</v>
+        <v>6380861</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3839,37 +3829,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876768</v>
+        <v>125876731</v>
       </c>
       <c r="B29" t="n">
-        <v>107203</v>
+        <v>98362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3877,16 +3867,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723375</v>
+        <v>723148</v>
       </c>
       <c r="R29" t="n">
-        <v>6380878</v>
+        <v>6380883</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3950,37 +3945,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B30" t="n">
-        <v>107203</v>
+        <v>98362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3988,16 +3983,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R30" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125876778</v>
       </c>
       <c r="B34" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>125876682</v>
       </c>
       <c r="B35" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>125876698</v>
       </c>
       <c r="B36" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>125876752</v>
       </c>
       <c r="B37" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>125876813</v>
       </c>
       <c r="B38" t="n">
-        <v>107203</v>
+        <v>107205</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>125876814</v>
       </c>
       <c r="B50" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>125876705</v>
       </c>
       <c r="B51" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107203</v>
+        <v>107205</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>125876722</v>
       </c>
       <c r="B58" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>125876677</v>
       </c>
       <c r="B59" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>125876739</v>
       </c>
       <c r="B60" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>125876738</v>
       </c>
       <c r="B61" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>125876826</v>
       </c>
       <c r="B62" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7778,10 +7778,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876761</v>
+        <v>125876661</v>
       </c>
       <c r="B63" t="n">
-        <v>107203</v>
+        <v>109147</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7789,26 +7789,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7816,16 +7816,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723360</v>
+        <v>723022</v>
       </c>
       <c r="R63" t="n">
-        <v>6380851</v>
+        <v>6380875</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7889,10 +7894,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876786</v>
+        <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>107203</v>
+        <v>107205</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723329</v>
+        <v>723360</v>
       </c>
       <c r="R64" t="n">
-        <v>6380785</v>
+        <v>6380851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8000,10 +8005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876661</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>109145</v>
+        <v>107205</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8011,26 +8016,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8038,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723022</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380875</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,45 +8928,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876921</v>
+        <v>125876910</v>
       </c>
       <c r="B73" t="n">
-        <v>5492</v>
+        <v>95937</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723364</v>
+        <v>723027</v>
       </c>
       <c r="R73" t="n">
-        <v>6380813</v>
+        <v>6380801</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,11 +9008,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9030,54 +9034,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876910</v>
+        <v>125876921</v>
       </c>
       <c r="B74" t="n">
-        <v>95935</v>
+        <v>5492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723027</v>
+        <v>723364</v>
       </c>
       <c r="R74" t="n">
-        <v>6380801</v>
+        <v>6380813</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9110,6 +9105,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9136,59 +9136,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876741</v>
+        <v>125876757</v>
       </c>
       <c r="B75" t="n">
-        <v>98224</v>
+        <v>103776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723189</v>
+        <v>723360</v>
       </c>
       <c r="R75" t="n">
-        <v>6380869</v>
+        <v>6380851</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9252,10 +9238,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876658</v>
+        <v>125876741</v>
       </c>
       <c r="B76" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9282,7 +9268,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9301,10 +9287,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R76" t="n">
-        <v>6380859</v>
+        <v>6380869</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9368,10 +9354,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876717</v>
+        <v>125876658</v>
       </c>
       <c r="B77" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9398,7 +9384,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9417,10 +9403,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R77" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9453,11 +9439,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9489,10 +9470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876716</v>
+        <v>125876717</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>98226</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,26 +9481,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9544,7 +9525,7 @@
         <v>6380837</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9610,10 +9591,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876776</v>
+        <v>125876716</v>
       </c>
       <c r="B79" t="n">
-        <v>98224</v>
+        <v>98362</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9621,26 +9602,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9659,13 +9640,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R79" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9695,6 +9676,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9726,10 +9712,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876729</v>
+        <v>125876776</v>
       </c>
       <c r="B80" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9756,7 +9742,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9775,13 +9761,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723135</v>
+        <v>723342</v>
       </c>
       <c r="R80" t="n">
-        <v>6380877</v>
+        <v>6380826</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9842,10 +9828,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876828</v>
+        <v>125876729</v>
       </c>
       <c r="B81" t="n">
-        <v>98360</v>
+        <v>98226</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9853,26 +9839,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9887,14 +9873,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723173</v>
+        <v>723135</v>
       </c>
       <c r="R81" t="n">
-        <v>6380765</v>
+        <v>6380877</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9940,7 +9926,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9958,10 +9944,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876715</v>
+        <v>125876828</v>
       </c>
       <c r="B82" t="n">
-        <v>98224</v>
+        <v>98362</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9969,26 +9955,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10003,14 +9989,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723098</v>
+        <v>723173</v>
       </c>
       <c r="R82" t="n">
-        <v>6380819</v>
+        <v>6380765</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10056,7 +10042,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10074,45 +10060,59 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876757</v>
+        <v>125876715</v>
       </c>
       <c r="B83" t="n">
-        <v>103774</v>
+        <v>98226</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R83" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10179,7 +10179,7 @@
         <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876781</v>
+        <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98250</v>
+        <v>98362</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723343</v>
+        <v>723252</v>
       </c>
       <c r="R92" t="n">
-        <v>6380811</v>
+        <v>6380854</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876744</v>
+        <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98360</v>
+        <v>98226</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723252</v>
+        <v>722977</v>
       </c>
       <c r="R93" t="n">
-        <v>6380854</v>
+        <v>6380820</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876683</v>
+        <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98224</v>
+        <v>98252</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R94" t="n">
-        <v>6380820</v>
+        <v>6380811</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11457,54 +11457,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876945</v>
+        <v>125876707</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>98226</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>219769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723296</v>
+        <v>723077</v>
       </c>
       <c r="R95" t="n">
-        <v>6380797</v>
+        <v>6380813</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,11 +11544,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,6 +11552,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,37 +11573,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876740</v>
+        <v>125876669</v>
       </c>
       <c r="B96" t="n">
-        <v>107203</v>
+        <v>98356</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11606,16 +11611,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723183</v>
+        <v>723014</v>
       </c>
       <c r="R96" t="n">
-        <v>6380860</v>
+        <v>6380862</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11679,10 +11689,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876707</v>
+        <v>125876820</v>
       </c>
       <c r="B97" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11709,7 +11719,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11728,10 +11738,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723077</v>
+        <v>723194</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11795,10 +11805,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876669</v>
+        <v>125876772</v>
       </c>
       <c r="B98" t="n">
-        <v>98354</v>
+        <v>98226</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11806,26 +11816,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11844,10 +11854,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723014</v>
+        <v>723364</v>
       </c>
       <c r="R98" t="n">
-        <v>6380862</v>
+        <v>6380813</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11880,6 +11890,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11911,10 +11926,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876697</v>
       </c>
       <c r="B99" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11941,7 +11956,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11960,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723031</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380827</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12027,10 +12042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876719</v>
       </c>
       <c r="B100" t="n">
-        <v>98224</v>
+        <v>98362</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12038,26 +12053,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12076,13 +12091,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723068</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380835</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12112,11 +12127,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12148,10 +12158,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876788</v>
       </c>
       <c r="B101" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12178,7 +12188,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12197,10 +12207,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723320</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380799</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,59 +12274,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876945</v>
       </c>
       <c r="B102" t="n">
-        <v>98224</v>
+        <v>57648</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723296</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380797</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12351,6 +12356,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12359,11 +12369,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12380,37 +12385,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>98360</v>
+        <v>107205</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12418,24 +12423,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>107203</v>
+        <v>107205</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>125876674</v>
       </c>
       <c r="B116" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>125876823</v>
       </c>
       <c r="B117" t="n">
-        <v>110412</v>
+        <v>110414</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>125876676</v>
       </c>
       <c r="B118" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>125876709</v>
       </c>
       <c r="B119" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>125876819</v>
       </c>
       <c r="B120" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>125876690</v>
       </c>
       <c r="B123" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>125876767</v>
       </c>
       <c r="B124" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>125876766</v>
       </c>
       <c r="B126" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876667</v>
+        <v>125876718</v>
       </c>
       <c r="B127" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15175,10 +15175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723014</v>
+        <v>723068</v>
       </c>
       <c r="R127" t="n">
-        <v>6380862</v>
+        <v>6380835</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15242,10 +15242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876718</v>
+        <v>125876667</v>
       </c>
       <c r="B128" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723068</v>
+        <v>723014</v>
       </c>
       <c r="R128" t="n">
-        <v>6380835</v>
+        <v>6380862</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15361,7 +15361,7 @@
         <v>125876792</v>
       </c>
       <c r="B129" t="n">
-        <v>107203</v>
+        <v>107205</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15469,10 +15469,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126004016</v>
+        <v>126003980</v>
       </c>
       <c r="B130" t="n">
-        <v>98355</v>
+        <v>98226</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15480,26 +15480,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>723457</v>
+        <v>723365</v>
       </c>
       <c r="R130" t="n">
-        <v>6380869</v>
+        <v>6380795</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126003980</v>
+        <v>126004016</v>
       </c>
       <c r="B131" t="n">
-        <v>98224</v>
+        <v>98357</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,26 +15596,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15634,13 +15634,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>723365</v>
+        <v>723457</v>
       </c>
       <c r="R131" t="n">
-        <v>6380795</v>
+        <v>6380869</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126003997</v>
       </c>
       <c r="B133" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>103774</v>
+        <v>103776</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17200,10 +17200,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126003998</v>
+        <v>126003971</v>
       </c>
       <c r="B145" t="n">
-        <v>98354</v>
+        <v>98226</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17211,26 +17211,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>723508</v>
+        <v>723257</v>
       </c>
       <c r="R145" t="n">
-        <v>6380857</v>
+        <v>6380842</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17316,10 +17316,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126003971</v>
+        <v>126003998</v>
       </c>
       <c r="B146" t="n">
-        <v>98224</v>
+        <v>98356</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17327,26 +17327,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>723257</v>
+        <v>723508</v>
       </c>
       <c r="R146" t="n">
-        <v>6380842</v>
+        <v>6380857</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,48 +17548,62 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126004076</v>
+        <v>126004013</v>
       </c>
       <c r="B148" t="n">
-        <v>5492</v>
+        <v>98362</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723369</v>
+        <v>723461</v>
       </c>
       <c r="R148" t="n">
-        <v>6380814</v>
+        <v>6380878</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17619,11 +17633,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17655,62 +17664,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126004013</v>
+        <v>126004076</v>
       </c>
       <c r="B149" t="n">
-        <v>98360</v>
+        <v>5492</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219864</v>
+        <v>101410</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723461</v>
+        <v>723369</v>
       </c>
       <c r="R149" t="n">
-        <v>6380878</v>
+        <v>6380814</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17740,6 +17735,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17774,7 +17774,7 @@
         <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>126003996</v>
       </c>
       <c r="B155" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>126004014</v>
       </c>
       <c r="B156" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>99007</v>
+        <v>99009</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110412</v>
+        <v>110414</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1282,7 +1282,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125876827</v>
+        <v>125876694</v>
       </c>
       <c r="B7" t="n">
         <v>98226</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723188</v>
+        <v>723040</v>
       </c>
       <c r="R7" t="n">
-        <v>6380756</v>
+        <v>6380808</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125876721</v>
+        <v>125876827</v>
       </c>
       <c r="B8" t="n">
         <v>98226</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723053</v>
+        <v>723188</v>
       </c>
       <c r="R8" t="n">
-        <v>6380859</v>
+        <v>6380756</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125876694</v>
+        <v>125876721</v>
       </c>
       <c r="B9" t="n">
         <v>98226</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723040</v>
+        <v>723053</v>
       </c>
       <c r="R9" t="n">
-        <v>6380808</v>
+        <v>6380859</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876778</v>
+        <v>125876813</v>
       </c>
       <c r="B34" t="n">
-        <v>98226</v>
+        <v>107205</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,24 +4457,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723355</v>
+        <v>723238</v>
       </c>
       <c r="R34" t="n">
-        <v>6380807</v>
+        <v>6380770</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B35" t="n">
-        <v>98362</v>
+        <v>98226</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,26 +4541,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,13 +4579,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R35" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4651,7 +4646,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876698</v>
+        <v>125876682</v>
       </c>
       <c r="B36" t="n">
         <v>98362</v>
@@ -4681,7 +4676,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4700,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723026</v>
+        <v>722977</v>
       </c>
       <c r="R36" t="n">
-        <v>6380845</v>
+        <v>6380820</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4767,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876752</v>
+        <v>125876698</v>
       </c>
       <c r="B37" t="n">
-        <v>98226</v>
+        <v>98362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,26 +4773,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4816,10 +4811,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723026</v>
       </c>
       <c r="R37" t="n">
-        <v>6380856</v>
+        <v>6380845</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4883,37 +4878,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876813</v>
+        <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>107205</v>
+        <v>98226</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4921,16 +4916,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723238</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6380770</v>
+        <v>6380856</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -11457,59 +11457,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876707</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>98226</v>
+        <v>57648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723077</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11544,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11573,37 +11568,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876669</v>
+        <v>125876740</v>
       </c>
       <c r="B96" t="n">
-        <v>98356</v>
+        <v>107205</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11611,21 +11606,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723014</v>
+        <v>723183</v>
       </c>
       <c r="R96" t="n">
-        <v>6380862</v>
+        <v>6380860</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11689,7 +11679,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876820</v>
+        <v>125876707</v>
       </c>
       <c r="B97" t="n">
         <v>98226</v>
@@ -11719,7 +11709,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11738,10 +11728,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723194</v>
+        <v>723077</v>
       </c>
       <c r="R97" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11805,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876772</v>
+        <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98226</v>
+        <v>98356</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11816,26 +11806,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11854,10 +11844,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723364</v>
+        <v>723014</v>
       </c>
       <c r="R98" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11890,11 +11880,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11926,7 +11911,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876697</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
         <v>98226</v>
@@ -11956,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11975,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723031</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380827</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12042,10 +12027,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876719</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98362</v>
+        <v>98226</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12053,26 +12038,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12091,13 +12076,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723068</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380835</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12127,6 +12112,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12158,7 +12148,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
         <v>98226</v>
@@ -12188,7 +12178,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12207,10 +12197,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12274,32 +12264,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876945</v>
+        <v>125876719</v>
       </c>
       <c r="B102" t="n">
-        <v>57648</v>
+        <v>98362</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12307,24 +12297,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R102" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12356,11 +12351,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12369,6 +12359,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12385,37 +12380,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876788</v>
       </c>
       <c r="B103" t="n">
-        <v>107205</v>
+        <v>98226</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12423,16 +12418,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723320</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380799</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003999</v>
+        <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>109147</v>
+        <v>98357</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723516</v>
+        <v>723483</v>
       </c>
       <c r="R132" t="n">
-        <v>6380880</v>
+        <v>6380826</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,7 +15817,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126003997</v>
+        <v>126004010</v>
       </c>
       <c r="B133" t="n">
         <v>98357</v>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723483</v>
+        <v>723469</v>
       </c>
       <c r="R133" t="n">
-        <v>6380826</v>
+        <v>6380865</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004010</v>
+        <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98357</v>
+        <v>98356</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723469</v>
+        <v>723496</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126004004</v>
+        <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>98356</v>
+        <v>109147</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723496</v>
+        <v>723516</v>
       </c>
       <c r="R135" t="n">
-        <v>6380865</v>
+        <v>6380880</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16745,45 +16745,59 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B141" t="n">
-        <v>103776</v>
+        <v>98226</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R141" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16818,11 +16832,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16834,7 +16843,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16852,59 +16861,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B142" t="n">
-        <v>98226</v>
+        <v>103776</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R142" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16939,6 +16934,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -17200,10 +17200,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126003971</v>
+        <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98226</v>
+        <v>98356</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17211,26 +17211,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>723257</v>
+        <v>723508</v>
       </c>
       <c r="R145" t="n">
-        <v>6380842</v>
+        <v>6380857</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17316,10 +17316,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126003998</v>
+        <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98356</v>
+        <v>98226</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17327,26 +17327,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>723508</v>
+        <v>723257</v>
       </c>
       <c r="R146" t="n">
-        <v>6380857</v>
+        <v>6380842</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125876694</v>
+        <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723040</v>
+        <v>723188</v>
       </c>
       <c r="R7" t="n">
-        <v>6380808</v>
+        <v>6380756</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125876827</v>
+        <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723188</v>
+        <v>723053</v>
       </c>
       <c r="R8" t="n">
-        <v>6380756</v>
+        <v>6380859</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125876721</v>
+        <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723053</v>
+        <v>723040</v>
       </c>
       <c r="R9" t="n">
-        <v>6380859</v>
+        <v>6380808</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125876696</v>
       </c>
       <c r="B20" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>125876672</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>125876732</v>
       </c>
       <c r="B22" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>125876818</v>
       </c>
       <c r="B23" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>125876794</v>
       </c>
       <c r="B24" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>125876768</v>
       </c>
       <c r="B26" t="n">
-        <v>107205</v>
+        <v>107209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>125876815</v>
       </c>
       <c r="B27" t="n">
-        <v>107205</v>
+        <v>107209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>125876656</v>
       </c>
       <c r="B28" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>125876731</v>
       </c>
       <c r="B29" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>125876708</v>
       </c>
       <c r="B30" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125876813</v>
       </c>
       <c r="B34" t="n">
-        <v>107205</v>
+        <v>107209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876778</v>
+        <v>125876663</v>
       </c>
       <c r="B35" t="n">
-        <v>98226</v>
+        <v>98256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4579,13 +4579,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723355</v>
+        <v>723022</v>
       </c>
       <c r="R35" t="n">
-        <v>6380807</v>
+        <v>6380875</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B36" t="n">
-        <v>98362</v>
+        <v>98230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4657,26 +4657,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R36" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876698</v>
+        <v>125876682</v>
       </c>
       <c r="B37" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723026</v>
+        <v>722977</v>
       </c>
       <c r="R37" t="n">
-        <v>6380845</v>
+        <v>6380820</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876752</v>
+        <v>125876698</v>
       </c>
       <c r="B38" t="n">
-        <v>98226</v>
+        <v>98366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4889,26 +4889,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723026</v>
       </c>
       <c r="R38" t="n">
-        <v>6380856</v>
+        <v>6380845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876663</v>
+        <v>125876752</v>
       </c>
       <c r="B39" t="n">
-        <v>98252</v>
+        <v>98230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723022</v>
+        <v>723321</v>
       </c>
       <c r="R39" t="n">
-        <v>6380875</v>
+        <v>6380856</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876803</v>
       </c>
       <c r="B47" t="n">
-        <v>98362</v>
+        <v>107209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,24 +5960,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723244</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380753</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6033,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B48" t="n">
-        <v>98312</v>
+        <v>98366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,21 +6044,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6078,7 +6073,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6087,13 +6082,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R48" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6149,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876743</v>
+        <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>98226</v>
+        <v>98316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,26 +6160,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6194,7 +6189,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6203,13 +6198,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723221</v>
+        <v>723172</v>
       </c>
       <c r="R49" t="n">
-        <v>6380864</v>
+        <v>6380881</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6270,10 +6265,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876814</v>
+        <v>125876743</v>
       </c>
       <c r="B50" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,13 +6314,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723228</v>
+        <v>723221</v>
       </c>
       <c r="R50" t="n">
-        <v>6380782</v>
+        <v>6380864</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6386,10 +6381,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876705</v>
+        <v>125876814</v>
       </c>
       <c r="B51" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,10 +6430,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723064</v>
+        <v>723228</v>
       </c>
       <c r="R51" t="n">
-        <v>6380825</v>
+        <v>6380782</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,37 +6497,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876803</v>
+        <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>107205</v>
+        <v>98230</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6540,16 +6535,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723244</v>
+        <v>723064</v>
       </c>
       <c r="R52" t="n">
-        <v>6380753</v>
+        <v>6380825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6616,7 +6616,7 @@
         <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>125876722</v>
       </c>
       <c r="B58" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>125876677</v>
       </c>
       <c r="B59" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>125876739</v>
       </c>
       <c r="B60" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>125876738</v>
       </c>
       <c r="B61" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>125876826</v>
       </c>
       <c r="B62" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7778,10 +7778,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876661</v>
+        <v>125876761</v>
       </c>
       <c r="B63" t="n">
-        <v>109147</v>
+        <v>107209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7789,26 +7789,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7816,21 +7816,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723022</v>
+        <v>723360</v>
       </c>
       <c r="R63" t="n">
-        <v>6380875</v>
+        <v>6380851</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7894,10 +7889,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876761</v>
+        <v>125876786</v>
       </c>
       <c r="B64" t="n">
-        <v>107205</v>
+        <v>107209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723360</v>
+        <v>723329</v>
       </c>
       <c r="R64" t="n">
-        <v>6380851</v>
+        <v>6380785</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8005,10 +8000,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876786</v>
+        <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>107205</v>
+        <v>109151</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8016,26 +8011,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8043,16 +8038,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723329</v>
+        <v>723022</v>
       </c>
       <c r="R65" t="n">
-        <v>6380785</v>
+        <v>6380875</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876910</v>
+        <v>125876741</v>
       </c>
       <c r="B73" t="n">
-        <v>95937</v>
+        <v>98230</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8939,31 +8939,36 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>219769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8972,13 +8977,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723027</v>
+        <v>723189</v>
       </c>
       <c r="R73" t="n">
-        <v>6380801</v>
+        <v>6380869</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9018,6 +9023,11 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9034,48 +9044,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876921</v>
+        <v>125876658</v>
       </c>
       <c r="B74" t="n">
-        <v>5492</v>
+        <v>98230</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>101410</v>
+        <v>219769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723364</v>
+        <v>723022</v>
       </c>
       <c r="R74" t="n">
-        <v>6380813</v>
+        <v>6380859</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9107,11 +9131,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9120,6 +9139,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9136,45 +9160,59 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876757</v>
+        <v>125876717</v>
       </c>
       <c r="B75" t="n">
-        <v>103776</v>
+        <v>98230</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723360</v>
+        <v>723080</v>
       </c>
       <c r="R75" t="n">
-        <v>6380851</v>
+        <v>6380837</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9207,6 +9245,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9238,10 +9281,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876741</v>
+        <v>125876716</v>
       </c>
       <c r="B76" t="n">
-        <v>98226</v>
+        <v>98366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9249,26 +9292,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9287,13 +9330,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723189</v>
+        <v>723080</v>
       </c>
       <c r="R76" t="n">
-        <v>6380869</v>
+        <v>6380837</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9323,6 +9366,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9354,10 +9402,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876658</v>
+        <v>125876776</v>
       </c>
       <c r="B77" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9384,7 +9432,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9403,13 +9451,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723022</v>
+        <v>723342</v>
       </c>
       <c r="R77" t="n">
-        <v>6380859</v>
+        <v>6380826</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9470,10 +9518,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876717</v>
+        <v>125876729</v>
       </c>
       <c r="B78" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9519,10 +9567,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723080</v>
+        <v>723135</v>
       </c>
       <c r="R78" t="n">
-        <v>6380837</v>
+        <v>6380877</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9555,11 +9603,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9591,10 +9634,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876716</v>
+        <v>125876828</v>
       </c>
       <c r="B79" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9621,7 +9664,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9636,17 +9679,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723080</v>
+        <v>723173</v>
       </c>
       <c r="R79" t="n">
-        <v>6380837</v>
+        <v>6380765</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9678,11 +9721,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9694,7 +9732,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9712,10 +9750,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876776</v>
+        <v>125876715</v>
       </c>
       <c r="B80" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9742,7 +9780,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9761,13 +9799,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723342</v>
+        <v>723098</v>
       </c>
       <c r="R80" t="n">
-        <v>6380826</v>
+        <v>6380819</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9828,59 +9866,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876729</v>
+        <v>125876757</v>
       </c>
       <c r="B81" t="n">
-        <v>98226</v>
+        <v>103780</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723135</v>
+        <v>723360</v>
       </c>
       <c r="R81" t="n">
-        <v>6380877</v>
+        <v>6380851</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9944,10 +9968,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876828</v>
+        <v>125876910</v>
       </c>
       <c r="B82" t="n">
-        <v>98362</v>
+        <v>95941</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9955,51 +9979,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723173</v>
+        <v>723027</v>
       </c>
       <c r="R82" t="n">
-        <v>6380765</v>
+        <v>6380801</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10039,11 +10058,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Alvar och torräng.</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10060,62 +10074,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876715</v>
+        <v>125876921</v>
       </c>
       <c r="B83" t="n">
-        <v>98226</v>
+        <v>5492</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219769</v>
+        <v>101410</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723098</v>
+        <v>723364</v>
       </c>
       <c r="R83" t="n">
-        <v>6380819</v>
+        <v>6380813</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10147,6 +10147,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10155,11 +10160,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10179,7 +10179,7 @@
         <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98252</v>
+        <v>98256</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98252</v>
+        <v>98256</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>107209</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R95" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,11 +11539,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,6 +11547,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,10 +11568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876740</v>
+        <v>125876945</v>
       </c>
       <c r="B96" t="n">
-        <v>107205</v>
+        <v>57648</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11579,43 +11579,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723183</v>
+        <v>723296</v>
       </c>
       <c r="R96" t="n">
-        <v>6380860</v>
+        <v>6380797</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11650,6 +11650,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11658,11 +11663,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11682,7 +11682,7 @@
         <v>125876707</v>
       </c>
       <c r="B97" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98362</v>
+        <v>98230</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12275,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,13 +12313,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876788</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>98226</v>
+        <v>98366</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12391,26 +12391,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12429,13 +12429,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723320</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380799</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876745</v>
+        <v>125876685</v>
       </c>
       <c r="B104" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723252</v>
+        <v>722988</v>
       </c>
       <c r="R104" t="n">
-        <v>6380854</v>
+        <v>6380785</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876685</v>
+        <v>125876675</v>
       </c>
       <c r="B105" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,13 +12661,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>722988</v>
+        <v>722934</v>
       </c>
       <c r="R105" t="n">
-        <v>6380785</v>
+        <v>6380847</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876675</v>
+        <v>125876706</v>
       </c>
       <c r="B106" t="n">
-        <v>98226</v>
+        <v>98366</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12739,26 +12739,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>722934</v>
+        <v>723064</v>
       </c>
       <c r="R106" t="n">
-        <v>6380847</v>
+        <v>6380825</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876699</v>
+        <v>125876702</v>
       </c>
       <c r="B107" t="n">
-        <v>98226</v>
+        <v>98360</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723026</v>
+        <v>723038</v>
       </c>
       <c r="R107" t="n">
-        <v>6380845</v>
+        <v>6380832</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876777</v>
+        <v>125876755</v>
       </c>
       <c r="B108" t="n">
-        <v>98362</v>
+        <v>98361</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723355</v>
+        <v>723344</v>
       </c>
       <c r="R108" t="n">
-        <v>6380807</v>
+        <v>6380853</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876706</v>
+        <v>125876745</v>
       </c>
       <c r="B109" t="n">
-        <v>98362</v>
+        <v>98230</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723064</v>
+        <v>723252</v>
       </c>
       <c r="R109" t="n">
-        <v>6380825</v>
+        <v>6380854</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876702</v>
+        <v>125876699</v>
       </c>
       <c r="B110" t="n">
-        <v>98356</v>
+        <v>98230</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723038</v>
+        <v>723026</v>
       </c>
       <c r="R110" t="n">
-        <v>6380832</v>
+        <v>6380845</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876755</v>
+        <v>125876777</v>
       </c>
       <c r="B111" t="n">
-        <v>98357</v>
+        <v>98366</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,13 +13357,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723344</v>
+        <v>723355</v>
       </c>
       <c r="R111" t="n">
-        <v>6380853</v>
+        <v>6380807</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>107205</v>
+        <v>107209</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876674</v>
+        <v>125876823</v>
       </c>
       <c r="B116" t="n">
-        <v>98226</v>
+        <v>110418</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,48 +13894,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722924</v>
+        <v>723189</v>
       </c>
       <c r="R116" t="n">
-        <v>6380847</v>
+        <v>6380746</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13985,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876823</v>
+        <v>125876674</v>
       </c>
       <c r="B117" t="n">
-        <v>110414</v>
+        <v>98230</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,34 +13996,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219711</v>
+        <v>219769</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723189</v>
+        <v>722924</v>
       </c>
       <c r="R117" t="n">
-        <v>6380746</v>
+        <v>6380847</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14104,7 +14104,7 @@
         <v>125876676</v>
       </c>
       <c r="B118" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>125876709</v>
       </c>
       <c r="B119" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>125876819</v>
       </c>
       <c r="B120" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>98252</v>
+        <v>98256</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14551,37 +14551,37 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876710</v>
+        <v>125876792</v>
       </c>
       <c r="B122" t="n">
-        <v>98368</v>
+        <v>107209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>220079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14595,10 +14595,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723098</v>
+        <v>723296</v>
       </c>
       <c r="R122" t="n">
-        <v>6380819</v>
+        <v>6380797</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14662,10 +14662,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876690</v>
+        <v>125876710</v>
       </c>
       <c r="B123" t="n">
-        <v>98226</v>
+        <v>98372</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14673,26 +14673,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14700,21 +14700,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723004</v>
+        <v>723098</v>
       </c>
       <c r="R123" t="n">
-        <v>6380791</v>
+        <v>6380819</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14778,10 +14773,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876767</v>
+        <v>125876690</v>
       </c>
       <c r="B124" t="n">
-        <v>98362</v>
+        <v>98230</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14789,21 +14784,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14827,10 +14822,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723375</v>
+        <v>723004</v>
       </c>
       <c r="R124" t="n">
-        <v>6380878</v>
+        <v>6380791</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,10 +14889,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876763</v>
+        <v>125876767</v>
       </c>
       <c r="B125" t="n">
-        <v>98226</v>
+        <v>98366</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14905,26 +14900,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14943,10 +14938,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723370</v>
+        <v>723375</v>
       </c>
       <c r="R125" t="n">
-        <v>6380863</v>
+        <v>6380878</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15010,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876766</v>
+        <v>125876763</v>
       </c>
       <c r="B126" t="n">
-        <v>98362</v>
+        <v>98230</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15021,26 +15016,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15059,10 +15054,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723369</v>
+        <v>723370</v>
       </c>
       <c r="R126" t="n">
-        <v>6380880</v>
+        <v>6380863</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,27 +15121,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876718</v>
+        <v>125876766</v>
       </c>
       <c r="B127" t="n">
-        <v>109147</v>
+        <v>98366</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15156,7 +15151,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15175,10 +15170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723068</v>
+        <v>723369</v>
       </c>
       <c r="R127" t="n">
-        <v>6380835</v>
+        <v>6380880</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15245,7 +15240,7 @@
         <v>125876667</v>
       </c>
       <c r="B128" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15358,10 +15353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876792</v>
+        <v>125876718</v>
       </c>
       <c r="B129" t="n">
-        <v>107205</v>
+        <v>109151</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15369,26 +15364,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15396,16 +15391,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R129" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15469,10 +15469,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126003980</v>
+        <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98226</v>
+        <v>98361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15480,26 +15480,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>723365</v>
+        <v>723457</v>
       </c>
       <c r="R130" t="n">
-        <v>6380795</v>
+        <v>6380869</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126004016</v>
+        <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98357</v>
+        <v>98230</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,26 +15596,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15634,13 +15634,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>723457</v>
+        <v>723365</v>
       </c>
       <c r="R131" t="n">
-        <v>6380869</v>
+        <v>6380795</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003997</v>
+        <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>98357</v>
+        <v>109151</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723483</v>
+        <v>723516</v>
       </c>
       <c r="R132" t="n">
-        <v>6380826</v>
+        <v>6380880</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,10 +15817,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126004010</v>
+        <v>126003997</v>
       </c>
       <c r="B133" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723469</v>
+        <v>723483</v>
       </c>
       <c r="R133" t="n">
-        <v>6380865</v>
+        <v>6380826</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004004</v>
+        <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98356</v>
+        <v>98361</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723496</v>
+        <v>723469</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126003999</v>
+        <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>109147</v>
+        <v>98360</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723516</v>
+        <v>723496</v>
       </c>
       <c r="R135" t="n">
-        <v>6380880</v>
+        <v>6380865</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16745,59 +16745,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>98226</v>
+        <v>103780</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R141" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16832,6 +16818,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16843,7 +16834,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16861,45 +16852,59 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>103776</v>
+        <v>98230</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R142" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16934,11 +16939,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,62 +17548,48 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126004013</v>
+        <v>126004076</v>
       </c>
       <c r="B148" t="n">
-        <v>98362</v>
+        <v>5492</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219864</v>
+        <v>101410</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723461</v>
+        <v>723369</v>
       </c>
       <c r="R148" t="n">
-        <v>6380878</v>
+        <v>6380814</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17633,6 +17619,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17664,48 +17655,62 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126004076</v>
+        <v>126003976</v>
       </c>
       <c r="B149" t="n">
-        <v>5492</v>
+        <v>98256</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723369</v>
+        <v>723349</v>
       </c>
       <c r="R149" t="n">
-        <v>6380814</v>
+        <v>6380791</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17735,11 +17740,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17771,10 +17771,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126003976</v>
+        <v>126004013</v>
       </c>
       <c r="B150" t="n">
-        <v>98252</v>
+        <v>98366</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17782,26 +17782,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>723349</v>
+        <v>723461</v>
       </c>
       <c r="R150" t="n">
-        <v>6380791</v>
+        <v>6380878</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126004002</v>
+        <v>126003990</v>
       </c>
       <c r="B154" t="n">
-        <v>98357</v>
+        <v>99013</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723516</v>
+        <v>723426</v>
       </c>
       <c r="R154" t="n">
-        <v>6380880</v>
+        <v>6380811</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,6 +18322,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18333,7 +18338,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18351,10 +18356,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126003996</v>
+        <v>126004002</v>
       </c>
       <c r="B155" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18381,7 +18386,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18400,10 +18405,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723479</v>
+        <v>723516</v>
       </c>
       <c r="R155" t="n">
-        <v>6380833</v>
+        <v>6380880</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18467,10 +18472,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126004014</v>
+        <v>126003996</v>
       </c>
       <c r="B156" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18497,7 +18502,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18516,10 +18521,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723461</v>
+        <v>723479</v>
       </c>
       <c r="R156" t="n">
-        <v>6380878</v>
+        <v>6380833</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18583,47 +18588,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126003990</v>
+        <v>126004014</v>
       </c>
       <c r="B157" t="n">
-        <v>99009</v>
+        <v>98361</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18632,10 +18637,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723426</v>
+        <v>723461</v>
       </c>
       <c r="R157" t="n">
-        <v>6380811</v>
+        <v>6380878</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18670,11 +18675,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110414</v>
+        <v>110418</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98226</v>
+        <v>98230</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -4530,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876663</v>
+        <v>125876778</v>
       </c>
       <c r="B35" t="n">
-        <v>98256</v>
+        <v>98230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4579,13 +4579,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723022</v>
+        <v>723355</v>
       </c>
       <c r="R35" t="n">
-        <v>6380875</v>
+        <v>6380807</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876778</v>
+        <v>125876682</v>
       </c>
       <c r="B36" t="n">
-        <v>98230</v>
+        <v>98366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4657,26 +4657,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723355</v>
+        <v>722977</v>
       </c>
       <c r="R36" t="n">
-        <v>6380807</v>
+        <v>6380820</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876682</v>
+        <v>125876698</v>
       </c>
       <c r="B37" t="n">
         <v>98366</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>722977</v>
+        <v>723026</v>
       </c>
       <c r="R37" t="n">
-        <v>6380820</v>
+        <v>6380845</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876698</v>
+        <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>98366</v>
+        <v>98230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4889,26 +4889,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723026</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6380845</v>
+        <v>6380856</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876752</v>
+        <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98230</v>
+        <v>98256</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723321</v>
+        <v>723022</v>
       </c>
       <c r="R39" t="n">
-        <v>6380856</v>
+        <v>6380875</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876803</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>107209</v>
+        <v>98366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,19 +5960,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723244</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380753</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6033,10 +6038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98366</v>
+        <v>98316</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6044,21 +6049,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6073,7 +6078,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6082,13 +6087,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R48" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6149,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876733</v>
+        <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98316</v>
+        <v>98230</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,26 +6165,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6189,7 +6194,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6198,13 +6203,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723172</v>
+        <v>723221</v>
       </c>
       <c r="R49" t="n">
-        <v>6380881</v>
+        <v>6380864</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6265,7 +6270,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876743</v>
+        <v>125876814</v>
       </c>
       <c r="B50" t="n">
         <v>98230</v>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6314,13 +6319,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723221</v>
+        <v>723228</v>
       </c>
       <c r="R50" t="n">
-        <v>6380864</v>
+        <v>6380782</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,7 +6386,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876814</v>
+        <v>125876705</v>
       </c>
       <c r="B51" t="n">
         <v>98230</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,10 +6435,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723228</v>
+        <v>723064</v>
       </c>
       <c r="R51" t="n">
-        <v>6380782</v>
+        <v>6380825</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6497,37 +6502,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876705</v>
+        <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>98230</v>
+        <v>107209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6535,21 +6540,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723064</v>
+        <v>723244</v>
       </c>
       <c r="R52" t="n">
-        <v>6380825</v>
+        <v>6380753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876740</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>107209</v>
+        <v>57648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723183</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380860</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11547,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,54 +11568,59 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876945</v>
+        <v>125876707</v>
       </c>
       <c r="B96" t="n">
-        <v>57648</v>
+        <v>98230</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>219769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723296</v>
+        <v>723077</v>
       </c>
       <c r="R96" t="n">
-        <v>6380797</v>
+        <v>6380813</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11650,11 +11655,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11663,6 +11663,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11679,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876707</v>
+        <v>125876669</v>
       </c>
       <c r="B97" t="n">
-        <v>98230</v>
+        <v>98360</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11690,26 +11695,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11728,10 +11733,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723077</v>
+        <v>723014</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11795,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876669</v>
+        <v>125876820</v>
       </c>
       <c r="B98" t="n">
-        <v>98360</v>
+        <v>98230</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11806,26 +11811,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723014</v>
+        <v>723194</v>
       </c>
       <c r="R98" t="n">
-        <v>6380862</v>
+        <v>6380741</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11911,7 +11916,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876772</v>
       </c>
       <c r="B99" t="n">
         <v>98230</v>
@@ -11941,7 +11946,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11960,10 +11965,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723364</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11996,6 +12001,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12027,7 +12037,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876697</v>
       </c>
       <c r="B100" t="n">
         <v>98230</v>
@@ -12057,7 +12067,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12076,10 +12086,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723031</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380827</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12112,11 +12122,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12148,7 +12153,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876788</v>
       </c>
       <c r="B101" t="n">
         <v>98230</v>
@@ -12178,7 +12183,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12197,10 +12202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723320</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380799</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,10 +12269,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876719</v>
       </c>
       <c r="B102" t="n">
-        <v>98230</v>
+        <v>98366</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12280,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,13 +12318,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723068</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380835</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12380,37 +12385,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>98366</v>
+        <v>107209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12418,24 +12423,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876685</v>
+        <v>125876745</v>
       </c>
       <c r="B104" t="n">
         <v>98230</v>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>722988</v>
+        <v>723252</v>
       </c>
       <c r="R104" t="n">
-        <v>6380785</v>
+        <v>6380854</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,7 +12612,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876675</v>
+        <v>125876685</v>
       </c>
       <c r="B105" t="n">
         <v>98230</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,13 +12661,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>722934</v>
+        <v>722988</v>
       </c>
       <c r="R105" t="n">
-        <v>6380847</v>
+        <v>6380785</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876706</v>
+        <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98366</v>
+        <v>98230</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12739,26 +12739,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723064</v>
+        <v>722934</v>
       </c>
       <c r="R106" t="n">
-        <v>6380825</v>
+        <v>6380847</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876702</v>
+        <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98360</v>
+        <v>98230</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723038</v>
+        <v>723026</v>
       </c>
       <c r="R107" t="n">
-        <v>6380832</v>
+        <v>6380845</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876755</v>
+        <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98361</v>
+        <v>98366</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723344</v>
+        <v>723355</v>
       </c>
       <c r="R108" t="n">
-        <v>6380853</v>
+        <v>6380807</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876745</v>
+        <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98230</v>
+        <v>98366</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723252</v>
+        <v>723064</v>
       </c>
       <c r="R109" t="n">
-        <v>6380854</v>
+        <v>6380825</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876699</v>
+        <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98230</v>
+        <v>98360</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723026</v>
+        <v>723038</v>
       </c>
       <c r="R110" t="n">
-        <v>6380845</v>
+        <v>6380832</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876777</v>
+        <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98366</v>
+        <v>98361</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,13 +13357,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723355</v>
+        <v>723344</v>
       </c>
       <c r="R111" t="n">
-        <v>6380807</v>
+        <v>6380853</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -17548,48 +17548,62 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126004076</v>
+        <v>126003976</v>
       </c>
       <c r="B148" t="n">
-        <v>5492</v>
+        <v>98256</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723369</v>
+        <v>723349</v>
       </c>
       <c r="R148" t="n">
-        <v>6380814</v>
+        <v>6380791</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17619,11 +17633,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17655,62 +17664,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126003976</v>
+        <v>126004076</v>
       </c>
       <c r="B149" t="n">
-        <v>98256</v>
+        <v>5492</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>101410</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723349</v>
+        <v>723369</v>
       </c>
       <c r="R149" t="n">
-        <v>6380791</v>
+        <v>6380814</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17740,6 +17735,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125876696</v>
       </c>
       <c r="B20" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>125876672</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>125876732</v>
       </c>
       <c r="B22" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>125876818</v>
       </c>
       <c r="B23" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>125876794</v>
       </c>
       <c r="B24" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876768</v>
+        <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>107209</v>
+        <v>98367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,16 +3529,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723375</v>
+        <v>723038</v>
       </c>
       <c r="R26" t="n">
-        <v>6380878</v>
+        <v>6380861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3602,37 +3607,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876815</v>
+        <v>125876731</v>
       </c>
       <c r="B27" t="n">
-        <v>107209</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3640,16 +3645,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723209</v>
+        <v>723148</v>
       </c>
       <c r="R27" t="n">
-        <v>6380775</v>
+        <v>6380883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3713,10 +3723,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876656</v>
+        <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3753,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3762,10 +3772,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723038</v>
+        <v>723077</v>
       </c>
       <c r="R28" t="n">
-        <v>6380861</v>
+        <v>6380813</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3829,37 +3839,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876731</v>
+        <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>98366</v>
+        <v>107210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3867,21 +3877,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R29" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3945,37 +3950,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>107210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3983,21 +3988,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R30" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876813</v>
+        <v>125876778</v>
       </c>
       <c r="B34" t="n">
-        <v>107209</v>
+        <v>98231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,19 +4457,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723238</v>
+        <v>723355</v>
       </c>
       <c r="R34" t="n">
-        <v>6380770</v>
+        <v>6380807</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4530,10 +4535,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876778</v>
+        <v>125876682</v>
       </c>
       <c r="B35" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4541,26 +4546,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4579,13 +4584,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723355</v>
+        <v>722977</v>
       </c>
       <c r="R35" t="n">
-        <v>6380807</v>
+        <v>6380820</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4646,10 +4651,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876682</v>
+        <v>125876698</v>
       </c>
       <c r="B36" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4676,7 +4681,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4695,10 +4700,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>722977</v>
+        <v>723026</v>
       </c>
       <c r="R36" t="n">
-        <v>6380820</v>
+        <v>6380845</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4762,10 +4767,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876698</v>
+        <v>125876752</v>
       </c>
       <c r="B37" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,26 +4778,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,10 +4816,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723026</v>
+        <v>723321</v>
       </c>
       <c r="R37" t="n">
-        <v>6380845</v>
+        <v>6380856</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4878,37 +4883,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876752</v>
+        <v>125876813</v>
       </c>
       <c r="B38" t="n">
-        <v>98230</v>
+        <v>107210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4916,21 +4921,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723238</v>
       </c>
       <c r="R38" t="n">
-        <v>6380856</v>
+        <v>6380770</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4997,7 +4997,7 @@
         <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98256</v>
+        <v>98257</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>125876814</v>
       </c>
       <c r="B50" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>125876705</v>
       </c>
       <c r="B51" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107209</v>
+        <v>107210</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6613,37 +6613,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876714</v>
+        <v>125876761</v>
       </c>
       <c r="B53" t="n">
-        <v>98316</v>
+        <v>107210</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6651,21 +6651,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723098</v>
+        <v>723360</v>
       </c>
       <c r="R53" t="n">
-        <v>6380819</v>
+        <v>6380851</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,37 +6724,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876681</v>
+        <v>125876786</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>107210</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>220079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6767,21 +6762,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>722977</v>
+        <v>723329</v>
       </c>
       <c r="R54" t="n">
-        <v>6380820</v>
+        <v>6380785</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,10 +6835,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876723</v>
+        <v>125876714</v>
       </c>
       <c r="B55" t="n">
-        <v>98230</v>
+        <v>98317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6856,26 +6846,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6885,7 +6875,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6894,10 +6884,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723093</v>
+        <v>723098</v>
       </c>
       <c r="R55" t="n">
-        <v>6380849</v>
+        <v>6380819</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6951,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876736</v>
+        <v>125876681</v>
       </c>
       <c r="B56" t="n">
-        <v>98230</v>
+        <v>98362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6972,26 +6962,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723172</v>
+        <v>722977</v>
       </c>
       <c r="R56" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876686</v>
+        <v>125876723</v>
       </c>
       <c r="B57" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7097,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723006</v>
+        <v>723093</v>
       </c>
       <c r="R57" t="n">
-        <v>6380816</v>
+        <v>6380849</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,10 +7183,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876722</v>
+        <v>125876736</v>
       </c>
       <c r="B58" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,26 +7194,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7242,10 +7232,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723061</v>
+        <v>723172</v>
       </c>
       <c r="R58" t="n">
-        <v>6380859</v>
+        <v>6380881</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7299,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876677</v>
+        <v>125876686</v>
       </c>
       <c r="B59" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7339,7 +7329,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7358,10 +7348,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>722956</v>
+        <v>723006</v>
       </c>
       <c r="R59" t="n">
-        <v>6380853</v>
+        <v>6380816</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,10 +7415,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876739</v>
+        <v>125876722</v>
       </c>
       <c r="B60" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7436,26 +7426,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7474,10 +7464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723173</v>
+        <v>723061</v>
       </c>
       <c r="R60" t="n">
-        <v>6380850</v>
+        <v>6380859</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,10 +7531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876738</v>
+        <v>125876677</v>
       </c>
       <c r="B61" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7571,7 +7561,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7590,10 +7580,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723157</v>
+        <v>722956</v>
       </c>
       <c r="R61" t="n">
-        <v>6380881</v>
+        <v>6380853</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7657,10 +7647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876826</v>
+        <v>125876739</v>
       </c>
       <c r="B62" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7668,26 +7658,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7706,10 +7696,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723188</v>
+        <v>723173</v>
       </c>
       <c r="R62" t="n">
-        <v>6380756</v>
+        <v>6380850</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7742,11 +7732,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,37 +7763,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876761</v>
+        <v>125876738</v>
       </c>
       <c r="B63" t="n">
-        <v>107209</v>
+        <v>98231</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7816,16 +7801,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723360</v>
+        <v>723157</v>
       </c>
       <c r="R63" t="n">
-        <v>6380851</v>
+        <v>6380881</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7889,37 +7879,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876786</v>
+        <v>125876826</v>
       </c>
       <c r="B64" t="n">
-        <v>107209</v>
+        <v>98367</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7927,16 +7917,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723329</v>
+        <v>723188</v>
       </c>
       <c r="R64" t="n">
-        <v>6380785</v>
+        <v>6380756</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7969,6 +7964,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8003,7 +8003,7 @@
         <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,59 +8928,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876741</v>
+        <v>125876757</v>
       </c>
       <c r="B73" t="n">
-        <v>98230</v>
+        <v>103781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723189</v>
+        <v>723360</v>
       </c>
       <c r="R73" t="n">
-        <v>6380869</v>
+        <v>6380851</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9044,10 +9030,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876658</v>
+        <v>125876741</v>
       </c>
       <c r="B74" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9074,7 +9060,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9093,10 +9079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R74" t="n">
-        <v>6380859</v>
+        <v>6380869</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9160,10 +9146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876717</v>
+        <v>125876658</v>
       </c>
       <c r="B75" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9190,7 +9176,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9209,10 +9195,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R75" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9245,11 +9231,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9281,10 +9262,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876716</v>
+        <v>125876717</v>
       </c>
       <c r="B76" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9292,26 +9273,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9336,7 +9317,7 @@
         <v>6380837</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9402,10 +9383,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876776</v>
+        <v>125876716</v>
       </c>
       <c r="B77" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9413,26 +9394,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9451,13 +9432,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R77" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9487,6 +9468,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9518,10 +9504,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876729</v>
+        <v>125876776</v>
       </c>
       <c r="B78" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9548,7 +9534,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9567,13 +9553,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723135</v>
+        <v>723342</v>
       </c>
       <c r="R78" t="n">
-        <v>6380877</v>
+        <v>6380826</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9634,10 +9620,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876828</v>
+        <v>125876729</v>
       </c>
       <c r="B79" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9645,26 +9631,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9679,14 +9665,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723173</v>
+        <v>723135</v>
       </c>
       <c r="R79" t="n">
-        <v>6380765</v>
+        <v>6380877</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9732,7 +9718,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9750,10 +9736,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876715</v>
+        <v>125876828</v>
       </c>
       <c r="B80" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9761,26 +9747,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9795,14 +9781,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723098</v>
+        <v>723173</v>
       </c>
       <c r="R80" t="n">
-        <v>6380819</v>
+        <v>6380765</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9848,7 +9834,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9866,45 +9852,59 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876757</v>
+        <v>125876715</v>
       </c>
       <c r="B81" t="n">
-        <v>103780</v>
+        <v>98231</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R81" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9968,10 +9968,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876910</v>
+        <v>125876810</v>
       </c>
       <c r="B82" t="n">
-        <v>95941</v>
+        <v>98257</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9979,31 +9979,36 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2180</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10012,13 +10017,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723027</v>
+        <v>723234</v>
       </c>
       <c r="R82" t="n">
-        <v>6380801</v>
+        <v>6380772</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10058,6 +10063,11 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10176,10 +10186,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876810</v>
+        <v>125876910</v>
       </c>
       <c r="B84" t="n">
-        <v>98256</v>
+        <v>95942</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10187,36 +10197,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10225,13 +10230,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723234</v>
+        <v>723027</v>
       </c>
       <c r="R84" t="n">
-        <v>6380772</v>
+        <v>6380801</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10271,11 +10276,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98256</v>
+        <v>98257</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>107210</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R95" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,11 +11539,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,6 +11547,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,59 +11568,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876707</v>
+        <v>125876945</v>
       </c>
       <c r="B96" t="n">
-        <v>98230</v>
+        <v>57648</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723077</v>
+        <v>723296</v>
       </c>
       <c r="R96" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11655,6 +11650,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11663,11 +11663,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11684,10 +11679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876669</v>
+        <v>125876707</v>
       </c>
       <c r="B97" t="n">
-        <v>98360</v>
+        <v>98231</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,26 +11690,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11733,10 +11728,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723014</v>
+        <v>723077</v>
       </c>
       <c r="R97" t="n">
-        <v>6380862</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876820</v>
+        <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98230</v>
+        <v>98361</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11811,26 +11806,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,10 +11844,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723194</v>
+        <v>723014</v>
       </c>
       <c r="R98" t="n">
-        <v>6380741</v>
+        <v>6380862</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11916,10 +11911,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876772</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11946,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11965,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723364</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12001,11 +11996,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12037,10 +12027,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876697</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12067,7 +12057,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12086,10 +12076,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723031</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380827</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12122,6 +12112,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,10 +12148,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12183,7 +12178,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12269,10 +12264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12280,26 +12275,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12318,13 +12313,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12385,37 +12380,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>107209</v>
+        <v>98367</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12423,19 +12418,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>107209</v>
+        <v>107210</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876823</v>
+        <v>125876674</v>
       </c>
       <c r="B116" t="n">
-        <v>110418</v>
+        <v>98231</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,34 +13894,48 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219711</v>
+        <v>219769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723189</v>
+        <v>722924</v>
       </c>
       <c r="R116" t="n">
-        <v>6380746</v>
+        <v>6380847</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13985,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876674</v>
+        <v>125876823</v>
       </c>
       <c r="B117" t="n">
-        <v>98230</v>
+        <v>110419</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13996,48 +14010,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>722924</v>
+        <v>723189</v>
       </c>
       <c r="R117" t="n">
-        <v>6380847</v>
+        <v>6380746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14104,7 +14104,7 @@
         <v>125876676</v>
       </c>
       <c r="B118" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>125876709</v>
       </c>
       <c r="B119" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14333,45 +14333,59 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876819</v>
+        <v>125876659</v>
       </c>
       <c r="B120" t="n">
-        <v>109151</v>
+        <v>98257</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723194</v>
+        <v>723022</v>
       </c>
       <c r="R120" t="n">
-        <v>6380741</v>
+        <v>6380869</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14435,59 +14449,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876659</v>
+        <v>125876819</v>
       </c>
       <c r="B121" t="n">
-        <v>98256</v>
+        <v>109152</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723022</v>
+        <v>723194</v>
       </c>
       <c r="R121" t="n">
-        <v>6380869</v>
+        <v>6380741</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14551,37 +14551,37 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876792</v>
+        <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>107209</v>
+        <v>98373</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14595,10 +14595,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723296</v>
+        <v>723098</v>
       </c>
       <c r="R122" t="n">
-        <v>6380797</v>
+        <v>6380819</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14662,10 +14662,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876710</v>
+        <v>125876690</v>
       </c>
       <c r="B123" t="n">
-        <v>98372</v>
+        <v>98231</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14673,26 +14673,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14700,16 +14700,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723098</v>
+        <v>723004</v>
       </c>
       <c r="R123" t="n">
-        <v>6380819</v>
+        <v>6380791</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14773,10 +14778,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876690</v>
+        <v>125876767</v>
       </c>
       <c r="B124" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14784,21 +14789,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14822,10 +14827,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723004</v>
+        <v>723375</v>
       </c>
       <c r="R124" t="n">
-        <v>6380791</v>
+        <v>6380878</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14889,10 +14894,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876767</v>
+        <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>98366</v>
+        <v>98231</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14900,26 +14905,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14938,10 +14943,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723375</v>
+        <v>723370</v>
       </c>
       <c r="R125" t="n">
-        <v>6380878</v>
+        <v>6380863</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,10 +15010,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876763</v>
+        <v>125876766</v>
       </c>
       <c r="B126" t="n">
-        <v>98230</v>
+        <v>98367</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15016,26 +15021,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15054,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723370</v>
+        <v>723369</v>
       </c>
       <c r="R126" t="n">
-        <v>6380863</v>
+        <v>6380880</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,27 +15126,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876766</v>
+        <v>125876667</v>
       </c>
       <c r="B127" t="n">
-        <v>98366</v>
+        <v>109152</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15151,7 +15156,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15170,10 +15175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723369</v>
+        <v>723014</v>
       </c>
       <c r="R127" t="n">
-        <v>6380880</v>
+        <v>6380862</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,10 +15242,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876667</v>
+        <v>125876718</v>
       </c>
       <c r="B128" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15286,10 +15291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723014</v>
+        <v>723068</v>
       </c>
       <c r="R128" t="n">
-        <v>6380862</v>
+        <v>6380835</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,10 +15358,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876718</v>
+        <v>125876792</v>
       </c>
       <c r="B129" t="n">
-        <v>109151</v>
+        <v>107210</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15364,26 +15369,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15391,21 +15396,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723068</v>
+        <v>723296</v>
       </c>
       <c r="R129" t="n">
-        <v>6380835</v>
+        <v>6380797</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003999</v>
+        <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>109151</v>
+        <v>98362</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723516</v>
+        <v>723483</v>
       </c>
       <c r="R132" t="n">
-        <v>6380880</v>
+        <v>6380826</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,10 +15817,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126003997</v>
+        <v>126004010</v>
       </c>
       <c r="B133" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723483</v>
+        <v>723469</v>
       </c>
       <c r="R133" t="n">
-        <v>6380826</v>
+        <v>6380865</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,7 +15933,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004010</v>
+        <v>126004004</v>
       </c>
       <c r="B134" t="n">
         <v>98361</v>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723469</v>
+        <v>723496</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126004004</v>
+        <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>98360</v>
+        <v>109152</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723496</v>
+        <v>723516</v>
       </c>
       <c r="R135" t="n">
-        <v>6380865</v>
+        <v>6380880</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>103780</v>
+        <v>103781</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,62 +17548,48 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126003976</v>
+        <v>126004076</v>
       </c>
       <c r="B148" t="n">
-        <v>98256</v>
+        <v>5492</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>223591</v>
+        <v>101410</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723349</v>
+        <v>723369</v>
       </c>
       <c r="R148" t="n">
-        <v>6380791</v>
+        <v>6380814</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17633,6 +17619,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17664,48 +17655,62 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126004076</v>
+        <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>5492</v>
+        <v>98367</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723369</v>
+        <v>723461</v>
       </c>
       <c r="R149" t="n">
-        <v>6380814</v>
+        <v>6380878</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17735,11 +17740,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17771,10 +17771,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126004013</v>
+        <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98366</v>
+        <v>98257</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17782,26 +17782,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>723461</v>
+        <v>723349</v>
       </c>
       <c r="R150" t="n">
-        <v>6380878</v>
+        <v>6380791</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126003990</v>
+        <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>99013</v>
+        <v>98362</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723426</v>
+        <v>723516</v>
       </c>
       <c r="R154" t="n">
-        <v>6380811</v>
+        <v>6380880</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,11 +18322,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18338,7 +18333,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18356,10 +18351,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126004002</v>
+        <v>126003996</v>
       </c>
       <c r="B155" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18386,7 +18381,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18405,10 +18400,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723516</v>
+        <v>723479</v>
       </c>
       <c r="R155" t="n">
-        <v>6380880</v>
+        <v>6380833</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18472,10 +18467,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126003996</v>
+        <v>126004014</v>
       </c>
       <c r="B156" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18502,7 +18497,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18521,10 +18516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723479</v>
+        <v>723461</v>
       </c>
       <c r="R156" t="n">
-        <v>6380833</v>
+        <v>6380878</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18588,47 +18583,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126004014</v>
+        <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>98361</v>
+        <v>99014</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18637,10 +18632,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723461</v>
+        <v>723426</v>
       </c>
       <c r="R157" t="n">
-        <v>6380878</v>
+        <v>6380811</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18675,6 +18670,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110418</v>
+        <v>110419</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876740</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>107210</v>
+        <v>57648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723183</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380860</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11547,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,54 +11568,59 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876945</v>
+        <v>125876707</v>
       </c>
       <c r="B96" t="n">
-        <v>57648</v>
+        <v>98231</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>219769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723296</v>
+        <v>723077</v>
       </c>
       <c r="R96" t="n">
-        <v>6380797</v>
+        <v>6380813</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11650,11 +11655,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11663,6 +11663,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11679,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876707</v>
+        <v>125876669</v>
       </c>
       <c r="B97" t="n">
-        <v>98231</v>
+        <v>98361</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11690,26 +11695,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11728,10 +11733,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723077</v>
+        <v>723014</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11795,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876669</v>
+        <v>125876820</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>98231</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11806,26 +11811,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723014</v>
+        <v>723194</v>
       </c>
       <c r="R98" t="n">
-        <v>6380862</v>
+        <v>6380741</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11911,7 +11916,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876772</v>
       </c>
       <c r="B99" t="n">
         <v>98231</v>
@@ -11941,7 +11946,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11960,10 +11965,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723364</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11996,6 +12001,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12027,7 +12037,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876697</v>
       </c>
       <c r="B100" t="n">
         <v>98231</v>
@@ -12057,7 +12067,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12076,10 +12086,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723031</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380827</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12112,11 +12122,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12148,7 +12153,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876788</v>
       </c>
       <c r="B101" t="n">
         <v>98231</v>
@@ -12178,7 +12183,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12197,10 +12202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723320</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380799</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,10 +12269,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876719</v>
       </c>
       <c r="B102" t="n">
-        <v>98231</v>
+        <v>98367</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12280,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,13 +12318,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723068</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380835</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12380,37 +12385,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>98367</v>
+        <v>107210</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12418,24 +12423,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13424,37 +13424,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876664</v>
+        <v>125876811</v>
       </c>
       <c r="B112" t="n">
-        <v>98231</v>
+        <v>107210</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13462,21 +13462,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723022</v>
+        <v>723234</v>
       </c>
       <c r="R112" t="n">
-        <v>6380875</v>
+        <v>6380772</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,7 +13535,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876782</v>
+        <v>125876664</v>
       </c>
       <c r="B113" t="n">
         <v>98231</v>
@@ -13570,7 +13565,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13589,10 +13584,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723338</v>
+        <v>723022</v>
       </c>
       <c r="R113" t="n">
-        <v>6380799</v>
+        <v>6380875</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,10 +13651,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B114" t="n">
-        <v>98361</v>
+        <v>98231</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13667,26 +13662,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13705,10 +13700,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R114" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13772,37 +13767,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876811</v>
+        <v>125876765</v>
       </c>
       <c r="B115" t="n">
-        <v>107210</v>
+        <v>98361</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13810,16 +13805,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723234</v>
+        <v>723369</v>
       </c>
       <c r="R115" t="n">
-        <v>6380772</v>
+        <v>6380880</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -16745,45 +16745,59 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B141" t="n">
-        <v>103781</v>
+        <v>98231</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R141" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16818,11 +16832,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16834,7 +16843,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16852,59 +16861,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B142" t="n">
-        <v>98231</v>
+        <v>103781</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R142" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16939,6 +16934,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -6613,37 +6613,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876761</v>
+        <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>107210</v>
+        <v>98317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6651,16 +6651,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R53" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6724,37 +6729,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876786</v>
+        <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>107210</v>
+        <v>98362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220079</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6762,16 +6767,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723329</v>
+        <v>722977</v>
       </c>
       <c r="R54" t="n">
-        <v>6380785</v>
+        <v>6380820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6835,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876714</v>
+        <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98317</v>
+        <v>98231</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6846,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6875,7 +6885,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6884,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723098</v>
+        <v>723093</v>
       </c>
       <c r="R55" t="n">
-        <v>6380819</v>
+        <v>6380849</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6951,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876681</v>
+        <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98362</v>
+        <v>98231</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6962,26 +6972,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7000,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>722977</v>
+        <v>723172</v>
       </c>
       <c r="R56" t="n">
-        <v>6380820</v>
+        <v>6380881</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7067,7 +7077,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876723</v>
+        <v>125876686</v>
       </c>
       <c r="B57" t="n">
         <v>98231</v>
@@ -7097,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7116,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723093</v>
+        <v>723006</v>
       </c>
       <c r="R57" t="n">
-        <v>6380849</v>
+        <v>6380816</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7183,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876736</v>
+        <v>125876722</v>
       </c>
       <c r="B58" t="n">
-        <v>98231</v>
+        <v>98367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7194,26 +7204,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7232,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723172</v>
+        <v>723061</v>
       </c>
       <c r="R58" t="n">
-        <v>6380881</v>
+        <v>6380859</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7299,7 +7309,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876686</v>
+        <v>125876677</v>
       </c>
       <c r="B59" t="n">
         <v>98231</v>
@@ -7329,7 +7339,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7348,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723006</v>
+        <v>722956</v>
       </c>
       <c r="R59" t="n">
-        <v>6380816</v>
+        <v>6380853</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7415,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876722</v>
+        <v>125876739</v>
       </c>
       <c r="B60" t="n">
-        <v>98367</v>
+        <v>98231</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7426,26 +7436,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7464,10 +7474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723061</v>
+        <v>723173</v>
       </c>
       <c r="R60" t="n">
-        <v>6380859</v>
+        <v>6380850</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7531,7 +7541,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876677</v>
+        <v>125876738</v>
       </c>
       <c r="B61" t="n">
         <v>98231</v>
@@ -7561,7 +7571,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7580,10 +7590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>722956</v>
+        <v>723157</v>
       </c>
       <c r="R61" t="n">
-        <v>6380853</v>
+        <v>6380881</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7647,10 +7657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876739</v>
+        <v>125876826</v>
       </c>
       <c r="B62" t="n">
-        <v>98231</v>
+        <v>98367</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7658,26 +7668,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7696,10 +7706,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723173</v>
+        <v>723188</v>
       </c>
       <c r="R62" t="n">
-        <v>6380850</v>
+        <v>6380756</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7732,6 +7742,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7763,37 +7778,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876738</v>
+        <v>125876661</v>
       </c>
       <c r="B63" t="n">
-        <v>98231</v>
+        <v>109152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7812,10 +7827,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723157</v>
+        <v>723022</v>
       </c>
       <c r="R63" t="n">
-        <v>6380881</v>
+        <v>6380875</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7879,37 +7894,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876826</v>
+        <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>98367</v>
+        <v>107210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7917,21 +7932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723188</v>
+        <v>723360</v>
       </c>
       <c r="R64" t="n">
-        <v>6380756</v>
+        <v>6380851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7964,11 +7974,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8000,10 +8005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876661</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>109152</v>
+        <v>107210</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8011,26 +8016,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8038,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723022</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380875</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876744</v>
+        <v>125876781</v>
       </c>
       <c r="B92" t="n">
-        <v>98367</v>
+        <v>98257</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723252</v>
+        <v>723343</v>
       </c>
       <c r="R92" t="n">
-        <v>6380854</v>
+        <v>6380811</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876683</v>
+        <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98231</v>
+        <v>98367</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>722977</v>
+        <v>723252</v>
       </c>
       <c r="R93" t="n">
-        <v>6380820</v>
+        <v>6380854</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876781</v>
+        <v>125876683</v>
       </c>
       <c r="B94" t="n">
-        <v>98257</v>
+        <v>98231</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723343</v>
+        <v>722977</v>
       </c>
       <c r="R94" t="n">
-        <v>6380811</v>
+        <v>6380820</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>107210</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R95" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,11 +11539,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,6 +11547,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,59 +11568,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876707</v>
+        <v>125876945</v>
       </c>
       <c r="B96" t="n">
-        <v>98231</v>
+        <v>57648</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723077</v>
+        <v>723296</v>
       </c>
       <c r="R96" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11655,6 +11650,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11663,11 +11663,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11684,10 +11679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876669</v>
+        <v>125876707</v>
       </c>
       <c r="B97" t="n">
-        <v>98361</v>
+        <v>98231</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,26 +11690,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11733,10 +11728,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723014</v>
+        <v>723077</v>
       </c>
       <c r="R97" t="n">
-        <v>6380862</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876820</v>
+        <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98231</v>
+        <v>98361</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11811,26 +11806,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,10 +11844,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723194</v>
+        <v>723014</v>
       </c>
       <c r="R98" t="n">
-        <v>6380741</v>
+        <v>6380862</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11916,7 +11911,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876772</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
         <v>98231</v>
@@ -11946,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11965,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723364</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12001,11 +11996,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12037,7 +12027,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876697</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
         <v>98231</v>
@@ -12067,7 +12057,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12086,10 +12076,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723031</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380827</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12122,6 +12112,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,7 +12148,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
         <v>98231</v>
@@ -12183,7 +12178,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12269,10 +12264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98367</v>
+        <v>98231</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12280,26 +12275,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12318,13 +12313,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12385,37 +12380,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>107210</v>
+        <v>98367</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12423,19 +12418,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876670</v>
+        <v>125876672</v>
       </c>
       <c r="B18" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723014</v>
+        <v>722989</v>
       </c>
       <c r="R18" t="n">
-        <v>6380862</v>
+        <v>6380861</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876774</v>
+        <v>125876732</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723342</v>
+        <v>723148</v>
       </c>
       <c r="R19" t="n">
-        <v>6380826</v>
+        <v>6380883</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876696</v>
+        <v>125876818</v>
       </c>
       <c r="B20" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723042</v>
+        <v>723210</v>
       </c>
       <c r="R20" t="n">
-        <v>6380816</v>
+        <v>6380786</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,6 +2875,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876672</v>
+        <v>125876794</v>
       </c>
       <c r="B21" t="n">
-        <v>98362</v>
+        <v>98233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2955,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>722989</v>
+        <v>723296</v>
       </c>
       <c r="R21" t="n">
-        <v>6380861</v>
+        <v>6380797</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876732</v>
+        <v>125876769</v>
       </c>
       <c r="B22" t="n">
-        <v>98231</v>
+        <v>98375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,21 +3038,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3062,7 +3067,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R22" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876818</v>
+        <v>125876670</v>
       </c>
       <c r="B23" t="n">
-        <v>98231</v>
+        <v>98364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,26 +3154,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723210</v>
+        <v>723014</v>
       </c>
       <c r="R23" t="n">
-        <v>6380786</v>
+        <v>6380862</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3223,11 +3228,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876794</v>
+        <v>125876774</v>
       </c>
       <c r="B24" t="n">
-        <v>98231</v>
+        <v>98363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,26 +3270,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723296</v>
+        <v>723342</v>
       </c>
       <c r="R24" t="n">
-        <v>6380797</v>
+        <v>6380826</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876769</v>
+        <v>125876696</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>98233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723375</v>
+        <v>723042</v>
       </c>
       <c r="R25" t="n">
-        <v>6380878</v>
+        <v>6380816</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3494,7 +3494,7 @@
         <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>125876731</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>107210</v>
+        <v>107212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>107210</v>
+        <v>107212</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876778</v>
+        <v>125876813</v>
       </c>
       <c r="B34" t="n">
-        <v>98231</v>
+        <v>107212</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,24 +4457,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723355</v>
+        <v>723238</v>
       </c>
       <c r="R34" t="n">
-        <v>6380807</v>
+        <v>6380770</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B35" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,26 +4541,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,13 +4579,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R35" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4651,10 +4646,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876698</v>
+        <v>125876682</v>
       </c>
       <c r="B36" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4681,7 +4676,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4700,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723026</v>
+        <v>722977</v>
       </c>
       <c r="R36" t="n">
-        <v>6380845</v>
+        <v>6380820</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4767,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876752</v>
+        <v>125876698</v>
       </c>
       <c r="B37" t="n">
-        <v>98231</v>
+        <v>98369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,26 +4773,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4816,10 +4811,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723026</v>
       </c>
       <c r="R37" t="n">
-        <v>6380856</v>
+        <v>6380845</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4883,37 +4878,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876813</v>
+        <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>107210</v>
+        <v>98233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4921,16 +4916,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723238</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6380770</v>
+        <v>6380856</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4997,7 +4997,7 @@
         <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>125876814</v>
       </c>
       <c r="B50" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>125876705</v>
       </c>
       <c r="B51" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107210</v>
+        <v>107212</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>125876722</v>
       </c>
       <c r="B58" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>125876677</v>
       </c>
       <c r="B59" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>125876739</v>
       </c>
       <c r="B60" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>125876738</v>
       </c>
       <c r="B61" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>125876826</v>
       </c>
       <c r="B62" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>125876661</v>
       </c>
       <c r="B63" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>107210</v>
+        <v>107212</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>107210</v>
+        <v>107212</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876785</v>
       </c>
       <c r="B70" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,48 +8928,62 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876757</v>
+        <v>125876810</v>
       </c>
       <c r="B73" t="n">
-        <v>103781</v>
+        <v>98259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220164</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723360</v>
+        <v>723234</v>
       </c>
       <c r="R73" t="n">
-        <v>6380851</v>
+        <v>6380772</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9030,10 +9044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876741</v>
+        <v>125876910</v>
       </c>
       <c r="B74" t="n">
-        <v>98231</v>
+        <v>95944</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9041,36 +9055,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219769</v>
+        <v>2180</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9079,13 +9088,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723189</v>
+        <v>723027</v>
       </c>
       <c r="R74" t="n">
-        <v>6380869</v>
+        <v>6380801</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9125,11 +9134,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9146,62 +9150,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876658</v>
+        <v>125876921</v>
       </c>
       <c r="B75" t="n">
-        <v>98231</v>
+        <v>5492</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219769</v>
+        <v>101410</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723022</v>
+        <v>723364</v>
       </c>
       <c r="R75" t="n">
-        <v>6380859</v>
+        <v>6380813</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9233,6 +9223,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9241,11 +9236,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9262,10 +9252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876717</v>
+        <v>125876741</v>
       </c>
       <c r="B76" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9292,7 +9282,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9311,10 +9301,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723080</v>
+        <v>723189</v>
       </c>
       <c r="R76" t="n">
-        <v>6380837</v>
+        <v>6380869</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9347,11 +9337,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9383,10 +9368,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876716</v>
+        <v>125876658</v>
       </c>
       <c r="B77" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,26 +9379,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9432,13 +9417,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R77" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9468,11 +9453,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9504,10 +9484,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876776</v>
+        <v>125876717</v>
       </c>
       <c r="B78" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9534,7 +9514,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9553,13 +9533,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R78" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9589,6 +9569,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9620,10 +9605,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876729</v>
+        <v>125876716</v>
       </c>
       <c r="B79" t="n">
-        <v>98231</v>
+        <v>98369</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9631,26 +9616,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9669,13 +9654,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723135</v>
+        <v>723080</v>
       </c>
       <c r="R79" t="n">
-        <v>6380877</v>
+        <v>6380837</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9705,6 +9690,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9736,10 +9726,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876828</v>
+        <v>125876776</v>
       </c>
       <c r="B80" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9747,26 +9737,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9781,17 +9771,17 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723173</v>
+        <v>723342</v>
       </c>
       <c r="R80" t="n">
-        <v>6380765</v>
+        <v>6380826</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9834,7 +9824,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9852,10 +9842,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876715</v>
+        <v>125876729</v>
       </c>
       <c r="B81" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9882,7 +9872,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9901,10 +9891,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723098</v>
+        <v>723135</v>
       </c>
       <c r="R81" t="n">
-        <v>6380819</v>
+        <v>6380877</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9968,10 +9958,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876810</v>
+        <v>125876828</v>
       </c>
       <c r="B82" t="n">
-        <v>98257</v>
+        <v>98369</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9979,26 +9969,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10008,22 +9998,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723234</v>
+        <v>723173</v>
       </c>
       <c r="R82" t="n">
-        <v>6380772</v>
+        <v>6380765</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10066,7 +10056,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10084,48 +10074,62 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876921</v>
+        <v>125876715</v>
       </c>
       <c r="B83" t="n">
-        <v>5492</v>
+        <v>98233</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101410</v>
+        <v>219769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723364</v>
+        <v>723098</v>
       </c>
       <c r="R83" t="n">
-        <v>6380813</v>
+        <v>6380819</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10157,11 +10161,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10170,6 +10169,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10186,57 +10190,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876910</v>
+        <v>125876757</v>
       </c>
       <c r="B84" t="n">
-        <v>95942</v>
+        <v>103783</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2180</v>
+        <v>220164</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723027</v>
+        <v>723360</v>
       </c>
       <c r="R84" t="n">
-        <v>6380801</v>
+        <v>6380851</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10276,6 +10271,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876781</v>
+        <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98257</v>
+        <v>98369</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723343</v>
+        <v>723252</v>
       </c>
       <c r="R92" t="n">
-        <v>6380811</v>
+        <v>6380854</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876744</v>
+        <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723252</v>
+        <v>722977</v>
       </c>
       <c r="R93" t="n">
-        <v>6380854</v>
+        <v>6380820</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876683</v>
+        <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98231</v>
+        <v>98259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R94" t="n">
-        <v>6380820</v>
+        <v>6380811</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11457,37 +11457,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876740</v>
+        <v>125876707</v>
       </c>
       <c r="B95" t="n">
-        <v>107210</v>
+        <v>98233</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11495,16 +11495,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723183</v>
+        <v>723077</v>
       </c>
       <c r="R95" t="n">
-        <v>6380860</v>
+        <v>6380813</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11568,32 +11573,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876945</v>
+        <v>125876669</v>
       </c>
       <c r="B96" t="n">
-        <v>57648</v>
+        <v>98363</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11601,21 +11606,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723296</v>
+        <v>723014</v>
       </c>
       <c r="R96" t="n">
-        <v>6380797</v>
+        <v>6380862</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11650,11 +11660,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11663,6 +11668,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11679,10 +11689,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876707</v>
+        <v>125876772</v>
       </c>
       <c r="B97" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11709,7 +11719,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11728,7 +11738,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723077</v>
+        <v>723364</v>
       </c>
       <c r="R97" t="n">
         <v>6380813</v>
@@ -11764,6 +11774,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11795,10 +11810,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876669</v>
+        <v>125876697</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>98233</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11806,21 +11821,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11844,10 +11859,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723014</v>
+        <v>723031</v>
       </c>
       <c r="R98" t="n">
-        <v>6380862</v>
+        <v>6380827</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11911,10 +11926,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876788</v>
       </c>
       <c r="B99" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11941,7 +11956,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11960,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723320</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380799</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12027,10 +12042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876719</v>
       </c>
       <c r="B100" t="n">
-        <v>98231</v>
+        <v>98369</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12038,26 +12053,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12076,13 +12091,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723068</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380835</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12112,11 +12127,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12148,37 +12158,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876740</v>
       </c>
       <c r="B101" t="n">
-        <v>98231</v>
+        <v>107212</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12186,21 +12196,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723183</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380860</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,59 +12269,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876945</v>
       </c>
       <c r="B102" t="n">
-        <v>98231</v>
+        <v>57649</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723296</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380797</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12351,6 +12351,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12359,11 +12364,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876820</v>
       </c>
       <c r="B103" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12391,26 +12391,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12429,13 +12429,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723194</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380741</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13424,37 +13424,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876811</v>
+        <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>107210</v>
+        <v>98233</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13462,16 +13462,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723234</v>
+        <v>723022</v>
       </c>
       <c r="R112" t="n">
-        <v>6380772</v>
+        <v>6380875</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13535,10 +13540,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876664</v>
+        <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13565,7 +13570,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13584,10 +13589,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723022</v>
+        <v>723338</v>
       </c>
       <c r="R113" t="n">
-        <v>6380875</v>
+        <v>6380799</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13651,10 +13656,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876782</v>
+        <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98231</v>
+        <v>98363</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13662,26 +13667,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13700,10 +13705,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723338</v>
+        <v>723369</v>
       </c>
       <c r="R114" t="n">
-        <v>6380799</v>
+        <v>6380880</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,37 +13772,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876765</v>
+        <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>98361</v>
+        <v>107212</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13805,21 +13810,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723369</v>
+        <v>723234</v>
       </c>
       <c r="R115" t="n">
-        <v>6380880</v>
+        <v>6380772</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876674</v>
+        <v>125876823</v>
       </c>
       <c r="B116" t="n">
-        <v>98231</v>
+        <v>110421</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,48 +13894,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722924</v>
+        <v>723189</v>
       </c>
       <c r="R116" t="n">
-        <v>6380847</v>
+        <v>6380746</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13985,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876823</v>
+        <v>125876676</v>
       </c>
       <c r="B117" t="n">
-        <v>110419</v>
+        <v>98364</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,34 +13996,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723189</v>
+        <v>722956</v>
       </c>
       <c r="R117" t="n">
-        <v>6380746</v>
+        <v>6380853</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B118" t="n">
-        <v>98362</v>
+        <v>98369</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14112,26 +14112,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14150,10 +14150,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R118" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,27 +14217,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876709</v>
+        <v>125876819</v>
       </c>
       <c r="B119" t="n">
-        <v>98367</v>
+        <v>109154</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14245,31 +14245,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723074</v>
+        <v>723194</v>
       </c>
       <c r="R119" t="n">
-        <v>6380823</v>
+        <v>6380741</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14336,7 +14322,7 @@
         <v>125876659</v>
       </c>
       <c r="B120" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14449,45 +14435,59 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876819</v>
+        <v>125876674</v>
       </c>
       <c r="B121" t="n">
-        <v>109152</v>
+        <v>98233</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723194</v>
+        <v>722924</v>
       </c>
       <c r="R121" t="n">
-        <v>6380741</v>
+        <v>6380847</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14551,32 +14551,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876710</v>
+        <v>125876667</v>
       </c>
       <c r="B122" t="n">
-        <v>98373</v>
+        <v>109154</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -14589,16 +14589,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723098</v>
+        <v>723014</v>
       </c>
       <c r="R122" t="n">
-        <v>6380819</v>
+        <v>6380862</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14662,37 +14667,37 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876690</v>
+        <v>125876718</v>
       </c>
       <c r="B123" t="n">
-        <v>98231</v>
+        <v>109154</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14711,10 +14716,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723004</v>
+        <v>723068</v>
       </c>
       <c r="R123" t="n">
-        <v>6380791</v>
+        <v>6380835</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14778,37 +14783,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876767</v>
+        <v>125876792</v>
       </c>
       <c r="B124" t="n">
-        <v>98367</v>
+        <v>107212</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14816,21 +14821,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723375</v>
+        <v>723296</v>
       </c>
       <c r="R124" t="n">
-        <v>6380878</v>
+        <v>6380797</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,10 +14894,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876763</v>
+        <v>125876710</v>
       </c>
       <c r="B125" t="n">
-        <v>98231</v>
+        <v>98375</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14905,21 +14905,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -14932,21 +14932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723370</v>
+        <v>723098</v>
       </c>
       <c r="R125" t="n">
-        <v>6380863</v>
+        <v>6380819</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15010,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876766</v>
+        <v>125876690</v>
       </c>
       <c r="B126" t="n">
-        <v>98367</v>
+        <v>98233</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15021,26 +15016,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15059,10 +15054,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723369</v>
+        <v>723004</v>
       </c>
       <c r="R126" t="n">
-        <v>6380880</v>
+        <v>6380791</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,27 +15121,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876667</v>
+        <v>125876767</v>
       </c>
       <c r="B127" t="n">
-        <v>109152</v>
+        <v>98369</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15156,7 +15151,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15175,10 +15170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723014</v>
+        <v>723375</v>
       </c>
       <c r="R127" t="n">
-        <v>6380862</v>
+        <v>6380878</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15242,32 +15237,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876718</v>
+        <v>125876763</v>
       </c>
       <c r="B128" t="n">
-        <v>109152</v>
+        <v>98233</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15291,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723068</v>
+        <v>723370</v>
       </c>
       <c r="R128" t="n">
-        <v>6380835</v>
+        <v>6380863</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15358,32 +15353,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876792</v>
+        <v>125876766</v>
       </c>
       <c r="B129" t="n">
-        <v>107210</v>
+        <v>98369</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15396,16 +15391,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723296</v>
+        <v>723369</v>
       </c>
       <c r="R129" t="n">
-        <v>6380797</v>
+        <v>6380880</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126004010</v>
       </c>
       <c r="B133" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126003986</v>
       </c>
       <c r="B141" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>126003972</v>
       </c>
       <c r="B142" t="n">
-        <v>103781</v>
+        <v>103783</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126004002</v>
+        <v>126003990</v>
       </c>
       <c r="B154" t="n">
-        <v>98362</v>
+        <v>99016</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723516</v>
+        <v>723426</v>
       </c>
       <c r="R154" t="n">
-        <v>6380880</v>
+        <v>6380811</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,6 +18322,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18333,7 +18338,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18351,10 +18356,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126003996</v>
+        <v>126004002</v>
       </c>
       <c r="B155" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18381,7 +18386,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18400,10 +18405,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723479</v>
+        <v>723516</v>
       </c>
       <c r="R155" t="n">
-        <v>6380833</v>
+        <v>6380880</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18467,10 +18472,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126004014</v>
+        <v>126003996</v>
       </c>
       <c r="B156" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18497,7 +18502,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18516,10 +18521,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723461</v>
+        <v>723479</v>
       </c>
       <c r="R156" t="n">
-        <v>6380878</v>
+        <v>6380833</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18583,47 +18588,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126003990</v>
+        <v>126004014</v>
       </c>
       <c r="B157" t="n">
-        <v>99014</v>
+        <v>98364</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18632,10 +18637,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723426</v>
+        <v>723461</v>
       </c>
       <c r="R157" t="n">
-        <v>6380811</v>
+        <v>6380878</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18670,11 +18675,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98231</v>
+        <v>98233</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876806</v>
+        <v>125876712</v>
       </c>
       <c r="B31" t="n">
-        <v>98233</v>
+        <v>98363</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R31" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,11 +4146,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,10 +4177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876712</v>
+        <v>125876805</v>
       </c>
       <c r="B32" t="n">
-        <v>98363</v>
+        <v>98369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4193,26 +4188,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R32" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,6 +4262,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876805</v>
+        <v>125876806</v>
       </c>
       <c r="B33" t="n">
-        <v>98369</v>
+        <v>98233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876803</v>
       </c>
       <c r="B47" t="n">
-        <v>98369</v>
+        <v>107212</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,24 +5960,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723244</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380753</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6033,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B48" t="n">
-        <v>98319</v>
+        <v>98369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,21 +6044,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6078,7 +6073,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6087,13 +6082,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R48" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6149,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876743</v>
+        <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>98233</v>
+        <v>98319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,26 +6160,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6194,7 +6189,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6203,13 +6198,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723221</v>
+        <v>723172</v>
       </c>
       <c r="R49" t="n">
-        <v>6380864</v>
+        <v>6380881</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6270,7 +6265,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876814</v>
+        <v>125876743</v>
       </c>
       <c r="B50" t="n">
         <v>98233</v>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,13 +6314,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723228</v>
+        <v>723221</v>
       </c>
       <c r="R50" t="n">
-        <v>6380782</v>
+        <v>6380864</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6386,7 +6381,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876705</v>
+        <v>125876814</v>
       </c>
       <c r="B51" t="n">
         <v>98233</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,10 +6430,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723064</v>
+        <v>723228</v>
       </c>
       <c r="R51" t="n">
-        <v>6380825</v>
+        <v>6380782</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6502,37 +6497,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876803</v>
+        <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>107212</v>
+        <v>98233</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6540,16 +6535,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723244</v>
+        <v>723064</v>
       </c>
       <c r="R52" t="n">
-        <v>6380753</v>
+        <v>6380825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -11457,7 +11457,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876707</v>
+        <v>125876820</v>
       </c>
       <c r="B95" t="n">
         <v>98233</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723077</v>
+        <v>723194</v>
       </c>
       <c r="R95" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11573,10 +11573,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876669</v>
+        <v>125876707</v>
       </c>
       <c r="B96" t="n">
-        <v>98363</v>
+        <v>98233</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11584,26 +11584,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723014</v>
+        <v>723077</v>
       </c>
       <c r="R96" t="n">
-        <v>6380862</v>
+        <v>6380813</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11689,10 +11689,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876772</v>
+        <v>125876669</v>
       </c>
       <c r="B97" t="n">
-        <v>98233</v>
+        <v>98363</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11700,26 +11700,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11738,10 +11738,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723364</v>
+        <v>723014</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11774,11 +11774,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11810,7 +11805,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876697</v>
+        <v>125876772</v>
       </c>
       <c r="B98" t="n">
         <v>98233</v>
@@ -11840,7 +11835,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11859,10 +11854,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723031</v>
+        <v>723364</v>
       </c>
       <c r="R98" t="n">
-        <v>6380827</v>
+        <v>6380813</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11895,6 +11890,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11926,7 +11926,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B99" t="n">
         <v>98233</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R99" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12042,10 +12042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B100" t="n">
-        <v>98369</v>
+        <v>98233</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12053,26 +12053,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12091,13 +12091,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R100" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12158,37 +12158,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B101" t="n">
-        <v>107212</v>
+        <v>98369</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12196,19 +12196,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R101" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12269,10 +12274,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B102" t="n">
-        <v>57649</v>
+        <v>107212</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12280,43 +12285,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R102" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12351,11 +12356,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12364,6 +12364,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12380,59 +12385,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876820</v>
+        <v>125876945</v>
       </c>
       <c r="B103" t="n">
-        <v>98233</v>
+        <v>57649</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723194</v>
+        <v>723296</v>
       </c>
       <c r="R103" t="n">
-        <v>6380741</v>
+        <v>6380797</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12467,6 +12467,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12475,11 +12480,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13424,10 +13424,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876664</v>
+        <v>125876765</v>
       </c>
       <c r="B112" t="n">
-        <v>98233</v>
+        <v>98363</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,21 +13435,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723022</v>
+        <v>723369</v>
       </c>
       <c r="R112" t="n">
-        <v>6380875</v>
+        <v>6380880</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,7 +13540,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876782</v>
+        <v>125876664</v>
       </c>
       <c r="B113" t="n">
         <v>98233</v>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723338</v>
+        <v>723022</v>
       </c>
       <c r="R113" t="n">
-        <v>6380799</v>
+        <v>6380875</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,10 +13656,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B114" t="n">
-        <v>98363</v>
+        <v>98233</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13667,26 +13667,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13705,10 +13705,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R114" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -14551,32 +14551,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876667</v>
+        <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>109154</v>
+        <v>98375</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -14589,21 +14589,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723014</v>
+        <v>723098</v>
       </c>
       <c r="R122" t="n">
-        <v>6380862</v>
+        <v>6380819</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14667,37 +14662,37 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876718</v>
+        <v>125876690</v>
       </c>
       <c r="B123" t="n">
-        <v>109154</v>
+        <v>98233</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14716,10 +14711,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723068</v>
+        <v>723004</v>
       </c>
       <c r="R123" t="n">
-        <v>6380835</v>
+        <v>6380791</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14783,37 +14778,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876792</v>
+        <v>125876767</v>
       </c>
       <c r="B124" t="n">
-        <v>107212</v>
+        <v>98369</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14821,16 +14816,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723296</v>
+        <v>723375</v>
       </c>
       <c r="R124" t="n">
-        <v>6380797</v>
+        <v>6380878</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,10 +14894,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876710</v>
+        <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>98375</v>
+        <v>98233</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14905,21 +14905,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -14932,16 +14932,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723098</v>
+        <v>723370</v>
       </c>
       <c r="R125" t="n">
-        <v>6380819</v>
+        <v>6380863</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,10 +15010,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876690</v>
+        <v>125876766</v>
       </c>
       <c r="B126" t="n">
-        <v>98233</v>
+        <v>98369</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15016,26 +15021,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15054,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723004</v>
+        <v>723369</v>
       </c>
       <c r="R126" t="n">
-        <v>6380791</v>
+        <v>6380880</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,27 +15126,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876767</v>
+        <v>125876667</v>
       </c>
       <c r="B127" t="n">
-        <v>98369</v>
+        <v>109154</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15151,7 +15156,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15170,10 +15175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723375</v>
+        <v>723014</v>
       </c>
       <c r="R127" t="n">
-        <v>6380878</v>
+        <v>6380862</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,32 +15242,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876763</v>
+        <v>125876718</v>
       </c>
       <c r="B128" t="n">
-        <v>98233</v>
+        <v>109154</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15286,10 +15291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723370</v>
+        <v>723068</v>
       </c>
       <c r="R128" t="n">
-        <v>6380863</v>
+        <v>6380835</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,32 +15358,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876766</v>
+        <v>125876792</v>
       </c>
       <c r="B129" t="n">
-        <v>98369</v>
+        <v>107212</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15391,21 +15396,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723369</v>
+        <v>723296</v>
       </c>
       <c r="R129" t="n">
-        <v>6380880</v>
+        <v>6380797</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876817</v>
+        <v>125876703</v>
       </c>
       <c r="B13" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1989,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723210</v>
+        <v>723050</v>
       </c>
       <c r="R13" t="n">
-        <v>6380786</v>
+        <v>6380829</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876703</v>
+        <v>125876817</v>
       </c>
       <c r="B14" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723050</v>
+        <v>723210</v>
       </c>
       <c r="R14" t="n">
-        <v>6380829</v>
+        <v>6380786</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125876678</v>
+        <v>125876696</v>
       </c>
       <c r="B16" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>722965</v>
+        <v>723042</v>
       </c>
       <c r="R16" t="n">
-        <v>6380842</v>
+        <v>6380816</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125876680</v>
+        <v>125876732</v>
       </c>
       <c r="B17" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>722962</v>
+        <v>723148</v>
       </c>
       <c r="R17" t="n">
-        <v>6380832</v>
+        <v>6380883</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876672</v>
+        <v>125876818</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>98235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>722989</v>
+        <v>723210</v>
       </c>
       <c r="R18" t="n">
-        <v>6380861</v>
+        <v>6380786</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2643,6 +2643,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876732</v>
+        <v>125876794</v>
       </c>
       <c r="B19" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2709,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723148</v>
+        <v>723296</v>
       </c>
       <c r="R19" t="n">
-        <v>6380883</v>
+        <v>6380797</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2790,10 +2795,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876818</v>
+        <v>125876678</v>
       </c>
       <c r="B20" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,26 +2806,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,10 +2844,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723210</v>
+        <v>722965</v>
       </c>
       <c r="R20" t="n">
-        <v>6380786</v>
+        <v>6380842</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,11 +2880,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876794</v>
+        <v>125876680</v>
       </c>
       <c r="B21" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,26 +2922,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723296</v>
+        <v>722962</v>
       </c>
       <c r="R21" t="n">
-        <v>6380797</v>
+        <v>6380832</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876769</v>
+        <v>125876670</v>
       </c>
       <c r="B22" t="n">
-        <v>98375</v>
+        <v>98366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,26 +3038,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723375</v>
+        <v>723014</v>
       </c>
       <c r="R22" t="n">
-        <v>6380878</v>
+        <v>6380862</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876670</v>
+        <v>125876774</v>
       </c>
       <c r="B23" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,26 +3154,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723014</v>
+        <v>723342</v>
       </c>
       <c r="R23" t="n">
-        <v>6380862</v>
+        <v>6380826</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876774</v>
+        <v>125876672</v>
       </c>
       <c r="B24" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,26 +3270,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723342</v>
+        <v>722989</v>
       </c>
       <c r="R24" t="n">
-        <v>6380826</v>
+        <v>6380861</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876696</v>
+        <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98233</v>
+        <v>98377</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723042</v>
+        <v>723375</v>
       </c>
       <c r="R25" t="n">
-        <v>6380816</v>
+        <v>6380878</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876656</v>
+        <v>125876768</v>
       </c>
       <c r="B26" t="n">
-        <v>98369</v>
+        <v>107214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,21 +3529,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723038</v>
+        <v>723375</v>
       </c>
       <c r="R26" t="n">
-        <v>6380861</v>
+        <v>6380878</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,10 +3602,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876731</v>
+        <v>125876656</v>
       </c>
       <c r="B27" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723148</v>
+        <v>723038</v>
       </c>
       <c r="R27" t="n">
-        <v>6380883</v>
+        <v>6380861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3723,37 +3718,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B28" t="n">
-        <v>98369</v>
+        <v>107214</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3761,21 +3756,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R28" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3839,37 +3829,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876768</v>
+        <v>125876731</v>
       </c>
       <c r="B29" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3877,16 +3867,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723375</v>
+        <v>723148</v>
       </c>
       <c r="R29" t="n">
-        <v>6380878</v>
+        <v>6380883</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3950,37 +3945,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B30" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3988,16 +3983,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R30" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876712</v>
+        <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98363</v>
+        <v>98235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R31" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,6 +4146,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876805</v>
+        <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98369</v>
+        <v>98365</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,26 +4193,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R32" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4262,11 +4267,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876806</v>
+        <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876813</v>
+        <v>125876663</v>
       </c>
       <c r="B34" t="n">
-        <v>107212</v>
+        <v>98261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,16 +4457,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723238</v>
+        <v>723022</v>
       </c>
       <c r="R34" t="n">
-        <v>6380770</v>
+        <v>6380875</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4530,37 +4535,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876778</v>
+        <v>125876813</v>
       </c>
       <c r="B35" t="n">
-        <v>98233</v>
+        <v>107214</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4568,24 +4573,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723355</v>
+        <v>723238</v>
       </c>
       <c r="R35" t="n">
-        <v>6380807</v>
+        <v>6380770</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>125876682</v>
       </c>
       <c r="B36" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>125876698</v>
       </c>
       <c r="B37" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876752</v>
+        <v>125876778</v>
       </c>
       <c r="B38" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723355</v>
       </c>
       <c r="R38" t="n">
-        <v>6380856</v>
+        <v>6380807</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876663</v>
+        <v>125876752</v>
       </c>
       <c r="B39" t="n">
-        <v>98259</v>
+        <v>98235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723022</v>
+        <v>723321</v>
       </c>
       <c r="R39" t="n">
-        <v>6380875</v>
+        <v>6380856</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876812</v>
+        <v>125876756</v>
       </c>
       <c r="B40" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,16 +5148,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723238</v>
+        <v>723344</v>
       </c>
       <c r="R40" t="n">
-        <v>6380770</v>
+        <v>6380853</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5221,10 +5226,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876671</v>
+        <v>125876812</v>
       </c>
       <c r="B41" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5251,7 +5256,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5259,21 +5264,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>722989</v>
+        <v>723238</v>
       </c>
       <c r="R41" t="n">
-        <v>6380861</v>
+        <v>6380770</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876762</v>
+        <v>125876671</v>
       </c>
       <c r="B42" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723370</v>
+        <v>722989</v>
       </c>
       <c r="R42" t="n">
-        <v>6380863</v>
+        <v>6380861</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876756</v>
+        <v>125876762</v>
       </c>
       <c r="B43" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723344</v>
+        <v>723370</v>
       </c>
       <c r="R43" t="n">
-        <v>6380853</v>
+        <v>6380863</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125876704</v>
+        <v>125876711</v>
       </c>
       <c r="B45" t="n">
-        <v>98369</v>
+        <v>98366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,26 +5696,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723050</v>
+        <v>723098</v>
       </c>
       <c r="R45" t="n">
-        <v>6380829</v>
+        <v>6380819</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5770,11 +5770,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5806,10 +5801,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125876711</v>
+        <v>125876704</v>
       </c>
       <c r="B46" t="n">
-        <v>98364</v>
+        <v>98371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,26 +5812,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723098</v>
+        <v>723050</v>
       </c>
       <c r="R46" t="n">
-        <v>6380819</v>
+        <v>6380829</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5891,6 +5886,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5922,32 +5922,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876803</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5960,19 +5960,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723244</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380753</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6033,32 +6038,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876728</v>
+        <v>125876803</v>
       </c>
       <c r="B48" t="n">
-        <v>98369</v>
+        <v>107214</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6071,24 +6076,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723135</v>
+        <v>723244</v>
       </c>
       <c r="R48" t="n">
-        <v>6380877</v>
+        <v>6380753</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>125876743</v>
       </c>
       <c r="B50" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>125876814</v>
       </c>
       <c r="B51" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876681</v>
+        <v>125876723</v>
       </c>
       <c r="B54" t="n">
-        <v>98364</v>
+        <v>98235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>722977</v>
+        <v>723093</v>
       </c>
       <c r="R54" t="n">
-        <v>6380820</v>
+        <v>6380849</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876723</v>
+        <v>125876736</v>
       </c>
       <c r="B55" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723093</v>
+        <v>723172</v>
       </c>
       <c r="R55" t="n">
-        <v>6380849</v>
+        <v>6380881</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876736</v>
+        <v>125876686</v>
       </c>
       <c r="B56" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723172</v>
+        <v>723006</v>
       </c>
       <c r="R56" t="n">
-        <v>6380881</v>
+        <v>6380816</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876686</v>
+        <v>125876677</v>
       </c>
       <c r="B57" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723006</v>
+        <v>722956</v>
       </c>
       <c r="R57" t="n">
-        <v>6380816</v>
+        <v>6380853</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876722</v>
+        <v>125876739</v>
       </c>
       <c r="B58" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,26 +7204,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723061</v>
+        <v>723173</v>
       </c>
       <c r="R58" t="n">
-        <v>6380859</v>
+        <v>6380850</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876677</v>
+        <v>125876738</v>
       </c>
       <c r="B59" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>722956</v>
+        <v>723157</v>
       </c>
       <c r="R59" t="n">
-        <v>6380853</v>
+        <v>6380881</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,37 +7425,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876739</v>
+        <v>125876761</v>
       </c>
       <c r="B60" t="n">
-        <v>98233</v>
+        <v>107214</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7463,21 +7463,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723173</v>
+        <v>723360</v>
       </c>
       <c r="R60" t="n">
-        <v>6380850</v>
+        <v>6380851</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,10 +7536,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876738</v>
+        <v>125876681</v>
       </c>
       <c r="B61" t="n">
-        <v>98233</v>
+        <v>98366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,26 +7547,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7590,10 +7585,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723157</v>
+        <v>722977</v>
       </c>
       <c r="R61" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7657,37 +7652,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876826</v>
+        <v>125876786</v>
       </c>
       <c r="B62" t="n">
-        <v>98369</v>
+        <v>107214</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7695,21 +7690,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723188</v>
+        <v>723329</v>
       </c>
       <c r="R62" t="n">
-        <v>6380756</v>
+        <v>6380785</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7742,11 +7732,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7781,7 +7766,7 @@
         <v>125876661</v>
       </c>
       <c r="B63" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7894,37 +7879,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876761</v>
+        <v>125876722</v>
       </c>
       <c r="B64" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7932,16 +7917,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723360</v>
+        <v>723061</v>
       </c>
       <c r="R64" t="n">
-        <v>6380851</v>
+        <v>6380859</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8005,37 +7995,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876786</v>
+        <v>125876826</v>
       </c>
       <c r="B65" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8043,16 +8033,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723329</v>
+        <v>723188</v>
       </c>
       <c r="R65" t="n">
-        <v>6380785</v>
+        <v>6380756</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8085,6 +8080,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8116,10 +8116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125876784</v>
+        <v>125876785</v>
       </c>
       <c r="B66" t="n">
-        <v>98364</v>
+        <v>98235</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8127,26 +8127,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8232,27 +8232,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876695</v>
+        <v>125876735</v>
       </c>
       <c r="B67" t="n">
-        <v>98369</v>
+        <v>109156</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723040</v>
+        <v>723172</v>
       </c>
       <c r="R67" t="n">
-        <v>6380808</v>
+        <v>6380881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876793</v>
+        <v>125876784</v>
       </c>
       <c r="B68" t="n">
-        <v>98369</v>
+        <v>98366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,21 +8359,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723296</v>
+        <v>723343</v>
       </c>
       <c r="R68" t="n">
-        <v>6380797</v>
+        <v>6380788</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876665</v>
+        <v>125876695</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>98371</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8475,26 +8475,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723022</v>
+        <v>723040</v>
       </c>
       <c r="R69" t="n">
-        <v>6380875</v>
+        <v>6380808</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876785</v>
+        <v>125876793</v>
       </c>
       <c r="B70" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723343</v>
+        <v>723296</v>
       </c>
       <c r="R70" t="n">
-        <v>6380788</v>
+        <v>6380797</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125876742</v>
+        <v>125876665</v>
       </c>
       <c r="B71" t="n">
-        <v>98369</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723189</v>
+        <v>723022</v>
       </c>
       <c r="R71" t="n">
-        <v>6380869</v>
+        <v>6380875</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8812,27 +8812,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125876735</v>
+        <v>125876742</v>
       </c>
       <c r="B72" t="n">
-        <v>109154</v>
+        <v>98371</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723172</v>
+        <v>723189</v>
       </c>
       <c r="R72" t="n">
-        <v>6380881</v>
+        <v>6380869</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876810</v>
+        <v>125876910</v>
       </c>
       <c r="B73" t="n">
-        <v>98259</v>
+        <v>95946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8939,36 +8939,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8977,13 +8972,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723234</v>
+        <v>723027</v>
       </c>
       <c r="R73" t="n">
-        <v>6380772</v>
+        <v>6380801</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9023,11 +9018,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9044,54 +9034,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876910</v>
+        <v>125876921</v>
       </c>
       <c r="B74" t="n">
-        <v>95944</v>
+        <v>5492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723027</v>
+        <v>723364</v>
       </c>
       <c r="R74" t="n">
-        <v>6380801</v>
+        <v>6380813</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9124,6 +9105,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9150,48 +9136,62 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876921</v>
+        <v>125876741</v>
       </c>
       <c r="B75" t="n">
-        <v>5492</v>
+        <v>98235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>101410</v>
+        <v>219769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723364</v>
+        <v>723189</v>
       </c>
       <c r="R75" t="n">
-        <v>6380813</v>
+        <v>6380869</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9223,11 +9223,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9236,6 +9231,11 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9252,10 +9252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876741</v>
+        <v>125876658</v>
       </c>
       <c r="B76" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723189</v>
+        <v>723022</v>
       </c>
       <c r="R76" t="n">
-        <v>6380869</v>
+        <v>6380859</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876658</v>
+        <v>125876717</v>
       </c>
       <c r="B77" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723022</v>
+        <v>723080</v>
       </c>
       <c r="R77" t="n">
-        <v>6380859</v>
+        <v>6380837</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9453,6 +9453,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9484,10 +9489,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876717</v>
+        <v>125876776</v>
       </c>
       <c r="B78" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9514,7 +9519,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9533,13 +9538,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723080</v>
+        <v>723342</v>
       </c>
       <c r="R78" t="n">
-        <v>6380837</v>
+        <v>6380826</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9569,11 +9574,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9605,10 +9605,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876716</v>
+        <v>125876729</v>
       </c>
       <c r="B79" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9616,26 +9616,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9654,13 +9654,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723080</v>
+        <v>723135</v>
       </c>
       <c r="R79" t="n">
-        <v>6380837</v>
+        <v>6380877</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9690,11 +9690,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9726,10 +9721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876776</v>
+        <v>125876715</v>
       </c>
       <c r="B80" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9756,7 +9751,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9775,13 +9770,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723342</v>
+        <v>723098</v>
       </c>
       <c r="R80" t="n">
-        <v>6380826</v>
+        <v>6380819</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9842,10 +9837,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876729</v>
+        <v>125876716</v>
       </c>
       <c r="B81" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9853,26 +9848,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9891,13 +9886,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723135</v>
+        <v>723080</v>
       </c>
       <c r="R81" t="n">
-        <v>6380877</v>
+        <v>6380837</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9927,6 +9922,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9961,7 +9961,7 @@
         <v>125876828</v>
       </c>
       <c r="B82" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876715</v>
+        <v>125876810</v>
       </c>
       <c r="B83" t="n">
-        <v>98233</v>
+        <v>98261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10085,26 +10085,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10123,13 +10123,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723098</v>
+        <v>723234</v>
       </c>
       <c r="R83" t="n">
-        <v>6380819</v>
+        <v>6380772</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>125876757</v>
       </c>
       <c r="B84" t="n">
-        <v>103783</v>
+        <v>103785</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876727</v>
+        <v>125876725</v>
       </c>
       <c r="B88" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10651,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10689,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723123</v>
+        <v>723122</v>
       </c>
       <c r="R88" t="n">
-        <v>6380868</v>
+        <v>6380858</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876754</v>
+        <v>125876727</v>
       </c>
       <c r="B89" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R89" t="n">
-        <v>6380853</v>
+        <v>6380868</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10841,11 +10841,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876666</v>
+        <v>125876754</v>
       </c>
       <c r="B90" t="n">
-        <v>98363</v>
+        <v>98371</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10888,26 +10883,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10926,13 +10921,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723022</v>
+        <v>723344</v>
       </c>
       <c r="R90" t="n">
-        <v>6380875</v>
+        <v>6380853</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10962,6 +10957,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10993,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876725</v>
+        <v>125876666</v>
       </c>
       <c r="B91" t="n">
-        <v>98233</v>
+        <v>98365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723122</v>
+        <v>723022</v>
       </c>
       <c r="R91" t="n">
-        <v>6380858</v>
+        <v>6380875</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11112,7 +11112,7 @@
         <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11457,59 +11457,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876820</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>98233</v>
+        <v>57649</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723194</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380741</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11544,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11576,7 +11571,7 @@
         <v>125876707</v>
       </c>
       <c r="B96" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11689,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876669</v>
+        <v>125876820</v>
       </c>
       <c r="B97" t="n">
-        <v>98363</v>
+        <v>98235</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11700,26 +11695,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11738,10 +11733,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723014</v>
+        <v>723194</v>
       </c>
       <c r="R97" t="n">
-        <v>6380862</v>
+        <v>6380741</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11808,7 +11803,7 @@
         <v>125876772</v>
       </c>
       <c r="B98" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11929,7 +11924,7 @@
         <v>125876697</v>
       </c>
       <c r="B99" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12045,7 +12040,7 @@
         <v>125876788</v>
       </c>
       <c r="B100" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12158,37 +12153,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B101" t="n">
-        <v>98369</v>
+        <v>107214</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12196,24 +12191,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R101" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12274,37 +12264,37 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876740</v>
+        <v>125876669</v>
       </c>
       <c r="B102" t="n">
-        <v>107212</v>
+        <v>98365</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12312,16 +12302,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723183</v>
+        <v>723014</v>
       </c>
       <c r="R102" t="n">
-        <v>6380860</v>
+        <v>6380862</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12385,32 +12380,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876945</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>57649</v>
+        <v>98371</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12418,24 +12413,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12467,11 +12467,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +12475,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13424,10 +13424,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876765</v>
+        <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98363</v>
+        <v>98235</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,21 +13435,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723369</v>
+        <v>723022</v>
       </c>
       <c r="R112" t="n">
-        <v>6380880</v>
+        <v>6380875</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876664</v>
+        <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723022</v>
+        <v>723338</v>
       </c>
       <c r="R113" t="n">
-        <v>6380875</v>
+        <v>6380799</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,37 +13656,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876782</v>
+        <v>125876811</v>
       </c>
       <c r="B114" t="n">
-        <v>98233</v>
+        <v>107214</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13694,21 +13694,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723338</v>
+        <v>723234</v>
       </c>
       <c r="R114" t="n">
-        <v>6380799</v>
+        <v>6380772</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13772,37 +13767,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876811</v>
+        <v>125876765</v>
       </c>
       <c r="B115" t="n">
-        <v>107212</v>
+        <v>98365</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13810,16 +13805,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723234</v>
+        <v>723369</v>
       </c>
       <c r="R115" t="n">
-        <v>6380772</v>
+        <v>6380880</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,27 +13883,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876823</v>
+        <v>125876819</v>
       </c>
       <c r="B116" t="n">
-        <v>110421</v>
+        <v>109156</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13918,10 +13918,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723189</v>
+        <v>723194</v>
       </c>
       <c r="R116" t="n">
-        <v>6380746</v>
+        <v>6380741</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13985,10 +13985,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876676</v>
+        <v>125876659</v>
       </c>
       <c r="B117" t="n">
-        <v>98364</v>
+        <v>98261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13996,26 +13996,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>722956</v>
+        <v>723022</v>
       </c>
       <c r="R117" t="n">
-        <v>6380853</v>
+        <v>6380869</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876709</v>
+        <v>125876674</v>
       </c>
       <c r="B118" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14112,26 +14112,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14150,10 +14150,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>723074</v>
+        <v>722924</v>
       </c>
       <c r="R118" t="n">
-        <v>6380823</v>
+        <v>6380847</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,27 +14217,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876819</v>
+        <v>125876823</v>
       </c>
       <c r="B119" t="n">
-        <v>109154</v>
+        <v>110423</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14252,10 +14252,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723194</v>
+        <v>723189</v>
       </c>
       <c r="R119" t="n">
-        <v>6380741</v>
+        <v>6380746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14319,10 +14319,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876659</v>
+        <v>125876676</v>
       </c>
       <c r="B120" t="n">
-        <v>98259</v>
+        <v>98366</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14330,26 +14330,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723022</v>
+        <v>722956</v>
       </c>
       <c r="R120" t="n">
-        <v>6380869</v>
+        <v>6380853</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14435,10 +14435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876674</v>
+        <v>125876709</v>
       </c>
       <c r="B121" t="n">
-        <v>98233</v>
+        <v>98371</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14446,26 +14446,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -14484,10 +14484,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>722924</v>
+        <v>723074</v>
       </c>
       <c r="R121" t="n">
-        <v>6380847</v>
+        <v>6380823</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14551,32 +14551,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876710</v>
+        <v>125876667</v>
       </c>
       <c r="B122" t="n">
-        <v>98375</v>
+        <v>109156</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -14589,16 +14589,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723098</v>
+        <v>723014</v>
       </c>
       <c r="R122" t="n">
-        <v>6380819</v>
+        <v>6380862</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14662,37 +14667,37 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876690</v>
+        <v>125876718</v>
       </c>
       <c r="B123" t="n">
-        <v>98233</v>
+        <v>109156</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14711,10 +14716,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723004</v>
+        <v>723068</v>
       </c>
       <c r="R123" t="n">
-        <v>6380791</v>
+        <v>6380835</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14778,10 +14783,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876767</v>
+        <v>125876690</v>
       </c>
       <c r="B124" t="n">
-        <v>98369</v>
+        <v>98235</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14789,21 +14794,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14827,10 +14832,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723375</v>
+        <v>723004</v>
       </c>
       <c r="R124" t="n">
-        <v>6380878</v>
+        <v>6380791</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14897,7 +14902,7 @@
         <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15010,10 +15015,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876766</v>
+        <v>125876710</v>
       </c>
       <c r="B126" t="n">
-        <v>98369</v>
+        <v>98377</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15021,26 +15026,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15048,21 +15053,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723369</v>
+        <v>723098</v>
       </c>
       <c r="R126" t="n">
-        <v>6380880</v>
+        <v>6380819</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876667</v>
+        <v>125876792</v>
       </c>
       <c r="B127" t="n">
-        <v>109154</v>
+        <v>107214</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15137,26 +15137,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15164,21 +15164,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723014</v>
+        <v>723296</v>
       </c>
       <c r="R127" t="n">
-        <v>6380862</v>
+        <v>6380797</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15242,27 +15237,27 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876718</v>
+        <v>125876767</v>
       </c>
       <c r="B128" t="n">
-        <v>109154</v>
+        <v>98371</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -15272,7 +15267,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15291,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723068</v>
+        <v>723375</v>
       </c>
       <c r="R128" t="n">
-        <v>6380835</v>
+        <v>6380878</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15358,32 +15353,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876792</v>
+        <v>125876766</v>
       </c>
       <c r="B129" t="n">
-        <v>107212</v>
+        <v>98371</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15396,16 +15391,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723296</v>
+        <v>723369</v>
       </c>
       <c r="R129" t="n">
-        <v>6380797</v>
+        <v>6380880</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15469,10 +15469,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126004016</v>
+        <v>126003980</v>
       </c>
       <c r="B130" t="n">
-        <v>98364</v>
+        <v>98235</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15480,26 +15480,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>723457</v>
+        <v>723365</v>
       </c>
       <c r="R130" t="n">
-        <v>6380869</v>
+        <v>6380795</v>
       </c>
       <c r="S130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126003980</v>
+        <v>126004016</v>
       </c>
       <c r="B131" t="n">
-        <v>98233</v>
+        <v>98366</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,26 +15596,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15634,13 +15634,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>723365</v>
+        <v>723457</v>
       </c>
       <c r="R131" t="n">
-        <v>6380795</v>
+        <v>6380869</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126004010</v>
       </c>
       <c r="B133" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16745,59 +16745,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>98233</v>
+        <v>103785</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R141" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16832,6 +16818,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16843,7 +16834,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16861,45 +16852,59 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>103783</v>
+        <v>98235</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R142" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16934,11 +16939,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>126003990</v>
       </c>
       <c r="B154" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>126004002</v>
       </c>
       <c r="B155" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>126003996</v>
       </c>
       <c r="B156" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>126004014</v>
       </c>
       <c r="B157" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18704,10 +18704,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126004000</v>
+        <v>126003973</v>
       </c>
       <c r="B158" t="n">
-        <v>98319</v>
+        <v>110423</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18715,26 +18715,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>723516</v>
+        <v>723349</v>
       </c>
       <c r="R158" t="n">
-        <v>6380880</v>
+        <v>6380791</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18820,10 +18820,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126003973</v>
+        <v>126004000</v>
       </c>
       <c r="B159" t="n">
-        <v>110421</v>
+        <v>98321</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18831,26 +18831,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18869,10 +18869,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>723349</v>
+        <v>723516</v>
       </c>
       <c r="R159" t="n">
-        <v>6380791</v>
+        <v>6380880</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98233</v>
+        <v>98235</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -5685,10 +5685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125876711</v>
+        <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,26 +5696,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723098</v>
+        <v>723050</v>
       </c>
       <c r="R45" t="n">
-        <v>6380819</v>
+        <v>6380829</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5770,6 +5770,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5801,10 +5806,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125876704</v>
+        <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98371</v>
+        <v>98366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5812,26 +5817,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5850,10 +5855,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723050</v>
+        <v>723098</v>
       </c>
       <c r="R46" t="n">
-        <v>6380829</v>
+        <v>6380819</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5886,11 +5891,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B47" t="n">
-        <v>98371</v>
+        <v>98321</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,37 +6038,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876803</v>
+        <v>125876743</v>
       </c>
       <c r="B48" t="n">
-        <v>107214</v>
+        <v>98235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6076,19 +6076,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723244</v>
+        <v>723221</v>
       </c>
       <c r="R48" t="n">
-        <v>6380753</v>
+        <v>6380864</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6149,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876733</v>
+        <v>125876814</v>
       </c>
       <c r="B49" t="n">
-        <v>98321</v>
+        <v>98235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,26 +6165,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6189,7 +6194,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723172</v>
+        <v>723228</v>
       </c>
       <c r="R49" t="n">
-        <v>6380881</v>
+        <v>6380782</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6265,7 +6270,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876743</v>
+        <v>125876705</v>
       </c>
       <c r="B50" t="n">
         <v>98235</v>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6314,13 +6319,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723221</v>
+        <v>723064</v>
       </c>
       <c r="R50" t="n">
-        <v>6380864</v>
+        <v>6380825</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876814</v>
+        <v>125876728</v>
       </c>
       <c r="B51" t="n">
-        <v>98235</v>
+        <v>98371</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,26 +6397,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723228</v>
+        <v>723135</v>
       </c>
       <c r="R51" t="n">
-        <v>6380782</v>
+        <v>6380877</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,37 +6502,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876705</v>
+        <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>98235</v>
+        <v>107214</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6535,21 +6540,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723064</v>
+        <v>723244</v>
       </c>
       <c r="R52" t="n">
-        <v>6380825</v>
+        <v>6380753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -8116,37 +8116,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125876785</v>
+        <v>125876735</v>
       </c>
       <c r="B66" t="n">
-        <v>98235</v>
+        <v>109156</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723343</v>
+        <v>723172</v>
       </c>
       <c r="R66" t="n">
-        <v>6380788</v>
+        <v>6380881</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8232,37 +8232,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876735</v>
+        <v>125876784</v>
       </c>
       <c r="B67" t="n">
-        <v>109156</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723172</v>
+        <v>723343</v>
       </c>
       <c r="R67" t="n">
-        <v>6380881</v>
+        <v>6380788</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876784</v>
+        <v>125876695</v>
       </c>
       <c r="B68" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,26 +8359,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723343</v>
+        <v>723040</v>
       </c>
       <c r="R68" t="n">
-        <v>6380788</v>
+        <v>6380808</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,7 +8464,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876695</v>
+        <v>125876793</v>
       </c>
       <c r="B69" t="n">
         <v>98371</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723040</v>
+        <v>723296</v>
       </c>
       <c r="R69" t="n">
-        <v>6380808</v>
+        <v>6380797</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876793</v>
+        <v>125876665</v>
       </c>
       <c r="B70" t="n">
-        <v>98371</v>
+        <v>98366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723296</v>
+        <v>723022</v>
       </c>
       <c r="R70" t="n">
-        <v>6380797</v>
+        <v>6380875</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125876665</v>
+        <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R71" t="n">
-        <v>6380875</v>
+        <v>6380869</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125876742</v>
+        <v>125876785</v>
       </c>
       <c r="B72" t="n">
-        <v>98371</v>
+        <v>98235</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8823,26 +8823,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723189</v>
+        <v>723343</v>
       </c>
       <c r="R72" t="n">
-        <v>6380869</v>
+        <v>6380788</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876724</v>
+        <v>125876666</v>
       </c>
       <c r="B87" t="n">
-        <v>98235</v>
+        <v>98365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,26 +10535,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723123</v>
+        <v>723022</v>
       </c>
       <c r="R87" t="n">
-        <v>6380848</v>
+        <v>6380875</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10640,7 +10640,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876725</v>
+        <v>125876724</v>
       </c>
       <c r="B88" t="n">
         <v>98235</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723122</v>
+        <v>723123</v>
       </c>
       <c r="R88" t="n">
-        <v>6380858</v>
+        <v>6380848</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876727</v>
+        <v>125876725</v>
       </c>
       <c r="B89" t="n">
-        <v>98371</v>
+        <v>98235</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10767,26 +10767,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723123</v>
+        <v>723122</v>
       </c>
       <c r="R89" t="n">
-        <v>6380868</v>
+        <v>6380858</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876754</v>
+        <v>125876727</v>
       </c>
       <c r="B90" t="n">
         <v>98371</v>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10921,13 +10921,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R90" t="n">
-        <v>6380853</v>
+        <v>6380868</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10957,11 +10957,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10993,10 +10988,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876666</v>
+        <v>125876754</v>
       </c>
       <c r="B91" t="n">
-        <v>98365</v>
+        <v>98371</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,26 +10999,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11042,13 +11037,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723022</v>
+        <v>723344</v>
       </c>
       <c r="R91" t="n">
-        <v>6380875</v>
+        <v>6380853</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11078,6 +11073,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876745</v>
+        <v>125876702</v>
       </c>
       <c r="B104" t="n">
-        <v>98235</v>
+        <v>98365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12507,26 +12507,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723252</v>
+        <v>723038</v>
       </c>
       <c r="R104" t="n">
-        <v>6380854</v>
+        <v>6380832</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876685</v>
+        <v>125876755</v>
       </c>
       <c r="B105" t="n">
-        <v>98235</v>
+        <v>98366</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12623,26 +12623,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>722988</v>
+        <v>723344</v>
       </c>
       <c r="R105" t="n">
-        <v>6380785</v>
+        <v>6380853</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12728,7 +12728,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876675</v>
+        <v>125876745</v>
       </c>
       <c r="B106" t="n">
         <v>98235</v>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>722934</v>
+        <v>723252</v>
       </c>
       <c r="R106" t="n">
-        <v>6380847</v>
+        <v>6380854</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876699</v>
+        <v>125876685</v>
       </c>
       <c r="B107" t="n">
         <v>98235</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723026</v>
+        <v>722988</v>
       </c>
       <c r="R107" t="n">
-        <v>6380845</v>
+        <v>6380785</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876777</v>
+        <v>125876675</v>
       </c>
       <c r="B108" t="n">
-        <v>98371</v>
+        <v>98235</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723355</v>
+        <v>722934</v>
       </c>
       <c r="R108" t="n">
-        <v>6380807</v>
+        <v>6380847</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876706</v>
+        <v>125876699</v>
       </c>
       <c r="B109" t="n">
-        <v>98371</v>
+        <v>98235</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723064</v>
+        <v>723026</v>
       </c>
       <c r="R109" t="n">
-        <v>6380825</v>
+        <v>6380845</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876702</v>
+        <v>125876777</v>
       </c>
       <c r="B110" t="n">
-        <v>98365</v>
+        <v>98371</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723038</v>
+        <v>723355</v>
       </c>
       <c r="R110" t="n">
-        <v>6380832</v>
+        <v>6380807</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876755</v>
+        <v>125876706</v>
       </c>
       <c r="B111" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723344</v>
+        <v>723064</v>
       </c>
       <c r="R111" t="n">
-        <v>6380853</v>
+        <v>6380825</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13656,37 +13656,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876811</v>
+        <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>107214</v>
+        <v>98365</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13694,16 +13694,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723234</v>
+        <v>723369</v>
       </c>
       <c r="R114" t="n">
-        <v>6380772</v>
+        <v>6380880</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,37 +13772,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876765</v>
+        <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>98365</v>
+        <v>107214</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13805,21 +13810,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723369</v>
+        <v>723234</v>
       </c>
       <c r="R115" t="n">
-        <v>6380880</v>
+        <v>6380772</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,45 +13883,59 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876819</v>
+        <v>125876674</v>
       </c>
       <c r="B116" t="n">
-        <v>109156</v>
+        <v>98235</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723194</v>
+        <v>722924</v>
       </c>
       <c r="R116" t="n">
-        <v>6380741</v>
+        <v>6380847</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13985,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876659</v>
+        <v>125876823</v>
       </c>
       <c r="B117" t="n">
-        <v>98261</v>
+        <v>110423</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13996,48 +14010,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223591</v>
+        <v>219711</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R117" t="n">
-        <v>6380869</v>
+        <v>6380746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,59 +14101,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876674</v>
+        <v>125876819</v>
       </c>
       <c r="B118" t="n">
-        <v>98235</v>
+        <v>109156</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722924</v>
+        <v>723194</v>
       </c>
       <c r="R118" t="n">
-        <v>6380847</v>
+        <v>6380741</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,10 +14203,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876823</v>
+        <v>125876676</v>
       </c>
       <c r="B119" t="n">
-        <v>110423</v>
+        <v>98366</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14228,34 +14214,48 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723189</v>
+        <v>722956</v>
       </c>
       <c r="R119" t="n">
-        <v>6380746</v>
+        <v>6380853</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14319,10 +14319,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B120" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14330,26 +14330,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R120" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14435,10 +14435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876709</v>
+        <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>98371</v>
+        <v>98261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14446,26 +14446,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14484,10 +14484,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723074</v>
+        <v>723022</v>
       </c>
       <c r="R121" t="n">
-        <v>6380823</v>
+        <v>6380869</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14551,37 +14551,37 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876667</v>
+        <v>125876690</v>
       </c>
       <c r="B122" t="n">
-        <v>109156</v>
+        <v>98235</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14600,10 +14600,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723014</v>
+        <v>723004</v>
       </c>
       <c r="R122" t="n">
-        <v>6380862</v>
+        <v>6380791</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14667,32 +14667,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876718</v>
+        <v>125876763</v>
       </c>
       <c r="B123" t="n">
-        <v>109156</v>
+        <v>98235</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14716,10 +14716,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723068</v>
+        <v>723370</v>
       </c>
       <c r="R123" t="n">
-        <v>6380835</v>
+        <v>6380863</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14783,10 +14783,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876690</v>
+        <v>125876710</v>
       </c>
       <c r="B124" t="n">
-        <v>98235</v>
+        <v>98377</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14794,26 +14794,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14821,21 +14821,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723004</v>
+        <v>723098</v>
       </c>
       <c r="R124" t="n">
-        <v>6380791</v>
+        <v>6380819</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14899,37 +14894,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876763</v>
+        <v>125876792</v>
       </c>
       <c r="B125" t="n">
-        <v>98235</v>
+        <v>107214</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14937,21 +14932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723370</v>
+        <v>723296</v>
       </c>
       <c r="R125" t="n">
-        <v>6380863</v>
+        <v>6380797</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15015,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876710</v>
+        <v>125876767</v>
       </c>
       <c r="B126" t="n">
-        <v>98377</v>
+        <v>98371</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15026,26 +15016,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15053,16 +15043,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723098</v>
+        <v>723375</v>
       </c>
       <c r="R126" t="n">
-        <v>6380819</v>
+        <v>6380878</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,32 +15121,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876792</v>
+        <v>125876766</v>
       </c>
       <c r="B127" t="n">
-        <v>107214</v>
+        <v>98371</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -15164,16 +15159,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723296</v>
+        <v>723369</v>
       </c>
       <c r="R127" t="n">
-        <v>6380797</v>
+        <v>6380880</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,27 +15237,27 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876767</v>
+        <v>125876667</v>
       </c>
       <c r="B128" t="n">
-        <v>98371</v>
+        <v>109156</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723375</v>
+        <v>723014</v>
       </c>
       <c r="R128" t="n">
-        <v>6380878</v>
+        <v>6380862</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,27 +15353,27 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876766</v>
+        <v>125876718</v>
       </c>
       <c r="B129" t="n">
-        <v>98371</v>
+        <v>109156</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723369</v>
+        <v>723068</v>
       </c>
       <c r="R129" t="n">
-        <v>6380880</v>
+        <v>6380835</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15469,10 +15469,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126003980</v>
+        <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98235</v>
+        <v>98366</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15480,26 +15480,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>723365</v>
+        <v>723457</v>
       </c>
       <c r="R130" t="n">
-        <v>6380795</v>
+        <v>6380869</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126004016</v>
+        <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98366</v>
+        <v>98235</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,26 +15596,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15634,13 +15634,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>723457</v>
+        <v>723365</v>
       </c>
       <c r="R131" t="n">
-        <v>6380869</v>
+        <v>6380795</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003997</v>
+        <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>98366</v>
+        <v>109156</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723483</v>
+        <v>723516</v>
       </c>
       <c r="R132" t="n">
-        <v>6380826</v>
+        <v>6380880</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,7 +15817,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126004010</v>
+        <v>126003997</v>
       </c>
       <c r="B133" t="n">
         <v>98366</v>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723469</v>
+        <v>723483</v>
       </c>
       <c r="R133" t="n">
-        <v>6380865</v>
+        <v>6380826</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004004</v>
+        <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723496</v>
+        <v>723469</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126003999</v>
+        <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>109156</v>
+        <v>98365</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723516</v>
+        <v>723496</v>
       </c>
       <c r="R135" t="n">
-        <v>6380880</v>
+        <v>6380865</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16281,10 +16281,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126003974</v>
+        <v>126003978</v>
       </c>
       <c r="B137" t="n">
-        <v>98371</v>
+        <v>98235</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16292,26 +16292,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16397,10 +16397,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126003993</v>
+        <v>126003974</v>
       </c>
       <c r="B138" t="n">
-        <v>98366</v>
+        <v>98371</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16408,26 +16408,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>723470</v>
+        <v>723349</v>
       </c>
       <c r="R138" t="n">
-        <v>6380822</v>
+        <v>6380791</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16513,7 +16513,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126003995</v>
+        <v>126003993</v>
       </c>
       <c r="B139" t="n">
         <v>98366</v>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16565,7 +16565,7 @@
         <v>723470</v>
       </c>
       <c r="R139" t="n">
-        <v>6380826</v>
+        <v>6380822</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16629,10 +16629,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126003978</v>
+        <v>126003995</v>
       </c>
       <c r="B140" t="n">
-        <v>98235</v>
+        <v>98366</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16640,26 +16640,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>723349</v>
+        <v>723470</v>
       </c>
       <c r="R140" t="n">
-        <v>6380791</v>
+        <v>6380826</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876691</v>
       </c>
       <c r="B12" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876703</v>
+        <v>125876817</v>
       </c>
       <c r="B13" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1989,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723050</v>
+        <v>723210</v>
       </c>
       <c r="R13" t="n">
-        <v>6380829</v>
+        <v>6380786</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876817</v>
+        <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723210</v>
+        <v>723050</v>
       </c>
       <c r="R14" t="n">
-        <v>6380786</v>
+        <v>6380829</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2213,7 +2213,7 @@
         <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125876696</v>
+        <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723042</v>
+        <v>722965</v>
       </c>
       <c r="R16" t="n">
-        <v>6380816</v>
+        <v>6380842</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125876732</v>
+        <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723148</v>
+        <v>722962</v>
       </c>
       <c r="R17" t="n">
-        <v>6380883</v>
+        <v>6380832</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876818</v>
+        <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98235</v>
+        <v>98368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723210</v>
+        <v>723014</v>
       </c>
       <c r="R18" t="n">
-        <v>6380786</v>
+        <v>6380862</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2643,11 +2643,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876794</v>
+        <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98235</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,26 +2685,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2728,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723296</v>
+        <v>723342</v>
       </c>
       <c r="R19" t="n">
-        <v>6380797</v>
+        <v>6380826</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2795,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876678</v>
+        <v>125876696</v>
       </c>
       <c r="B20" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2844,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>722965</v>
+        <v>723042</v>
       </c>
       <c r="R20" t="n">
-        <v>6380842</v>
+        <v>6380816</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876680</v>
+        <v>125876672</v>
       </c>
       <c r="B21" t="n">
-        <v>98371</v>
+        <v>98368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,26 +2917,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2960,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>722962</v>
+        <v>722989</v>
       </c>
       <c r="R21" t="n">
-        <v>6380832</v>
+        <v>6380861</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3027,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876670</v>
+        <v>125876732</v>
       </c>
       <c r="B22" t="n">
-        <v>98366</v>
+        <v>98237</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,26 +3033,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3076,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723014</v>
+        <v>723148</v>
       </c>
       <c r="R22" t="n">
-        <v>6380862</v>
+        <v>6380883</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3143,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876774</v>
+        <v>125876818</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98237</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,26 +3149,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3192,13 +3187,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723342</v>
+        <v>723210</v>
       </c>
       <c r="R23" t="n">
-        <v>6380826</v>
+        <v>6380786</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3228,6 +3223,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876672</v>
+        <v>125876794</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98237</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>722989</v>
+        <v>723296</v>
       </c>
       <c r="R24" t="n">
-        <v>6380861</v>
+        <v>6380797</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3378,7 +3378,7 @@
         <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876768</v>
+        <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>107214</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,16 +3529,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723375</v>
+        <v>723038</v>
       </c>
       <c r="R26" t="n">
-        <v>6380878</v>
+        <v>6380861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3602,10 +3607,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876656</v>
+        <v>125876731</v>
       </c>
       <c r="B27" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723038</v>
+        <v>723148</v>
       </c>
       <c r="R27" t="n">
-        <v>6380861</v>
+        <v>6380883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3718,37 +3723,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>107214</v>
+        <v>98373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3756,16 +3761,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R28" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3829,37 +3839,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876731</v>
+        <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>98371</v>
+        <v>107218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3867,21 +3877,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R29" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3945,37 +3950,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>98371</v>
+        <v>107218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3983,21 +3988,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R30" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>125876663</v>
       </c>
       <c r="B34" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4535,37 +4535,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876813</v>
+        <v>125876778</v>
       </c>
       <c r="B35" t="n">
-        <v>107214</v>
+        <v>98237</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4573,19 +4573,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723238</v>
+        <v>723355</v>
       </c>
       <c r="R35" t="n">
-        <v>6380770</v>
+        <v>6380807</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4649,7 +4654,7 @@
         <v>125876682</v>
       </c>
       <c r="B36" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4770,7 @@
         <v>125876698</v>
       </c>
       <c r="B37" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4878,10 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876778</v>
+        <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4908,7 +4913,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,13 +4932,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723355</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6380807</v>
+        <v>6380856</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4994,37 +4999,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876752</v>
+        <v>125876813</v>
       </c>
       <c r="B39" t="n">
-        <v>98235</v>
+        <v>107218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5032,21 +5037,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723321</v>
+        <v>723238</v>
       </c>
       <c r="R39" t="n">
-        <v>6380856</v>
+        <v>6380770</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876756</v>
+        <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,21 +5148,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723344</v>
+        <v>723238</v>
       </c>
       <c r="R40" t="n">
-        <v>6380853</v>
+        <v>6380770</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5226,10 +5221,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876812</v>
+        <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5256,7 +5251,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5264,16 +5259,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723238</v>
+        <v>722989</v>
       </c>
       <c r="R41" t="n">
-        <v>6380770</v>
+        <v>6380861</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876671</v>
+        <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>722989</v>
+        <v>723370</v>
       </c>
       <c r="R42" t="n">
-        <v>6380861</v>
+        <v>6380863</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876762</v>
+        <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723370</v>
+        <v>723344</v>
       </c>
       <c r="R43" t="n">
-        <v>6380863</v>
+        <v>6380853</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98321</v>
+        <v>98373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876743</v>
+        <v>125876733</v>
       </c>
       <c r="B48" t="n">
-        <v>98235</v>
+        <v>98323</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,26 +6049,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723221</v>
+        <v>723172</v>
       </c>
       <c r="R48" t="n">
-        <v>6380864</v>
+        <v>6380881</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876814</v>
+        <v>125876743</v>
       </c>
       <c r="B49" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723228</v>
+        <v>723221</v>
       </c>
       <c r="R49" t="n">
-        <v>6380782</v>
+        <v>6380864</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876705</v>
+        <v>125876814</v>
       </c>
       <c r="B50" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723064</v>
+        <v>723228</v>
       </c>
       <c r="R50" t="n">
-        <v>6380825</v>
+        <v>6380782</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876728</v>
+        <v>125876705</v>
       </c>
       <c r="B51" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,26 +6397,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723135</v>
+        <v>723064</v>
       </c>
       <c r="R51" t="n">
-        <v>6380877</v>
+        <v>6380825</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107214</v>
+        <v>107218</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6613,32 +6613,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876714</v>
+        <v>125876661</v>
       </c>
       <c r="B53" t="n">
-        <v>98321</v>
+        <v>109160</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723098</v>
+        <v>723022</v>
       </c>
       <c r="R53" t="n">
-        <v>6380819</v>
+        <v>6380875</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876723</v>
+        <v>125876714</v>
       </c>
       <c r="B54" t="n">
-        <v>98235</v>
+        <v>98323</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723093</v>
+        <v>723098</v>
       </c>
       <c r="R54" t="n">
-        <v>6380849</v>
+        <v>6380819</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876736</v>
+        <v>125876681</v>
       </c>
       <c r="B55" t="n">
-        <v>98235</v>
+        <v>98368</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6856,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723172</v>
+        <v>722977</v>
       </c>
       <c r="R55" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876686</v>
+        <v>125876723</v>
       </c>
       <c r="B56" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723006</v>
+        <v>723093</v>
       </c>
       <c r="R56" t="n">
-        <v>6380816</v>
+        <v>6380849</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876677</v>
+        <v>125876736</v>
       </c>
       <c r="B57" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>722956</v>
+        <v>723172</v>
       </c>
       <c r="R57" t="n">
-        <v>6380853</v>
+        <v>6380881</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876739</v>
+        <v>125876686</v>
       </c>
       <c r="B58" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723173</v>
+        <v>723006</v>
       </c>
       <c r="R58" t="n">
-        <v>6380850</v>
+        <v>6380816</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876738</v>
+        <v>125876722</v>
       </c>
       <c r="B59" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7320,26 +7320,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723157</v>
+        <v>723061</v>
       </c>
       <c r="R59" t="n">
-        <v>6380881</v>
+        <v>6380859</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,37 +7425,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876761</v>
+        <v>125876677</v>
       </c>
       <c r="B60" t="n">
-        <v>107214</v>
+        <v>98237</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7463,16 +7463,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723360</v>
+        <v>722956</v>
       </c>
       <c r="R60" t="n">
-        <v>6380851</v>
+        <v>6380853</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7536,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876681</v>
+        <v>125876739</v>
       </c>
       <c r="B61" t="n">
-        <v>98366</v>
+        <v>98237</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,26 +7552,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7585,10 +7590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>722977</v>
+        <v>723173</v>
       </c>
       <c r="R61" t="n">
-        <v>6380820</v>
+        <v>6380850</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7652,37 +7657,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876786</v>
+        <v>125876738</v>
       </c>
       <c r="B62" t="n">
-        <v>107214</v>
+        <v>98237</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7690,16 +7695,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723329</v>
+        <v>723157</v>
       </c>
       <c r="R62" t="n">
-        <v>6380785</v>
+        <v>6380881</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7763,27 +7773,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876661</v>
+        <v>125876826</v>
       </c>
       <c r="B63" t="n">
-        <v>109156</v>
+        <v>98373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7793,7 +7803,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7812,10 +7822,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723022</v>
+        <v>723188</v>
       </c>
       <c r="R63" t="n">
-        <v>6380875</v>
+        <v>6380756</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7848,6 +7858,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7879,37 +7894,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876722</v>
+        <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>98371</v>
+        <v>107218</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7917,21 +7932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723061</v>
+        <v>723360</v>
       </c>
       <c r="R64" t="n">
-        <v>6380859</v>
+        <v>6380851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7995,37 +8005,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876826</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>98371</v>
+        <v>107218</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8033,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723188</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380756</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8080,11 +8085,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8119,7 +8119,7 @@
         <v>125876735</v>
       </c>
       <c r="B66" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876784</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>125876695</v>
       </c>
       <c r="B68" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>125876793</v>
       </c>
       <c r="B69" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>125876665</v>
       </c>
       <c r="B70" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125876742</v>
+        <v>125876785</v>
       </c>
       <c r="B71" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723189</v>
+        <v>723343</v>
       </c>
       <c r="R71" t="n">
-        <v>6380869</v>
+        <v>6380788</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125876785</v>
+        <v>125876742</v>
       </c>
       <c r="B72" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8823,26 +8823,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723343</v>
+        <v>723189</v>
       </c>
       <c r="R72" t="n">
-        <v>6380788</v>
+        <v>6380869</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8931,7 +8931,7 @@
         <v>125876910</v>
       </c>
       <c r="B73" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>125876741</v>
       </c>
       <c r="B75" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>125876658</v>
       </c>
       <c r="B76" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>125876717</v>
       </c>
       <c r="B77" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876776</v>
+        <v>125876716</v>
       </c>
       <c r="B78" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,26 +9500,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9538,13 +9538,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R78" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9574,6 +9574,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9605,10 +9610,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876729</v>
+        <v>125876776</v>
       </c>
       <c r="B79" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9635,7 +9640,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9654,13 +9659,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723135</v>
+        <v>723342</v>
       </c>
       <c r="R79" t="n">
-        <v>6380877</v>
+        <v>6380826</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9721,10 +9726,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876715</v>
+        <v>125876729</v>
       </c>
       <c r="B80" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9756,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9770,10 +9775,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723098</v>
+        <v>723135</v>
       </c>
       <c r="R80" t="n">
-        <v>6380819</v>
+        <v>6380877</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9837,10 +9842,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876716</v>
+        <v>125876828</v>
       </c>
       <c r="B81" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9872,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9882,17 +9887,17 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723080</v>
+        <v>723173</v>
       </c>
       <c r="R81" t="n">
-        <v>6380837</v>
+        <v>6380765</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9924,11 +9929,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9958,10 +9958,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876828</v>
+        <v>125876715</v>
       </c>
       <c r="B82" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9969,26 +9969,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10003,14 +10003,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723173</v>
+        <v>723098</v>
       </c>
       <c r="R82" t="n">
-        <v>6380765</v>
+        <v>6380819</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10077,7 +10077,7 @@
         <v>125876810</v>
       </c>
       <c r="B83" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>125876757</v>
       </c>
       <c r="B84" t="n">
-        <v>103785</v>
+        <v>103789</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876666</v>
+        <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98365</v>
+        <v>98237</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,26 +10535,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723022</v>
+        <v>723123</v>
       </c>
       <c r="R87" t="n">
-        <v>6380875</v>
+        <v>6380848</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876724</v>
+        <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10651,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10692,10 +10692,10 @@
         <v>723123</v>
       </c>
       <c r="R88" t="n">
-        <v>6380848</v>
+        <v>6380868</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876725</v>
+        <v>125876754</v>
       </c>
       <c r="B89" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10767,26 +10767,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723122</v>
+        <v>723344</v>
       </c>
       <c r="R89" t="n">
-        <v>6380858</v>
+        <v>6380853</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10841,6 +10841,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10872,10 +10877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876727</v>
+        <v>125876666</v>
       </c>
       <c r="B90" t="n">
-        <v>98371</v>
+        <v>98367</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10883,26 +10888,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10921,13 +10926,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723123</v>
+        <v>723022</v>
       </c>
       <c r="R90" t="n">
-        <v>6380868</v>
+        <v>6380875</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10988,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876754</v>
+        <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10999,26 +11004,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11037,13 +11042,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723344</v>
+        <v>723122</v>
       </c>
       <c r="R91" t="n">
-        <v>6380853</v>
+        <v>6380858</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11073,11 +11078,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11112,7 +11112,7 @@
         <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11568,37 +11568,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876707</v>
+        <v>125876740</v>
       </c>
       <c r="B96" t="n">
-        <v>98235</v>
+        <v>107218</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11606,21 +11606,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723077</v>
+        <v>723183</v>
       </c>
       <c r="R96" t="n">
-        <v>6380813</v>
+        <v>6380860</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11684,10 +11679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876820</v>
+        <v>125876707</v>
       </c>
       <c r="B97" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11714,7 +11709,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11733,10 +11728,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723194</v>
+        <v>723077</v>
       </c>
       <c r="R97" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876772</v>
+        <v>125876669</v>
       </c>
       <c r="B98" t="n">
-        <v>98235</v>
+        <v>98367</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11811,26 +11806,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,10 +11844,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723364</v>
+        <v>723014</v>
       </c>
       <c r="R98" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11885,11 +11880,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11921,10 +11911,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876697</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11951,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11970,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723031</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380827</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12037,10 +12027,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876788</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12067,7 +12057,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12086,10 +12076,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723320</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380799</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12122,6 +12112,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,37 +12148,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876740</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>107214</v>
+        <v>98237</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12191,16 +12186,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723183</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380860</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876669</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98365</v>
+        <v>98237</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12275,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,10 +12313,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723014</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380862</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12383,7 +12383,7 @@
         <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876702</v>
+        <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98365</v>
+        <v>98237</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12507,26 +12507,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723038</v>
+        <v>723252</v>
       </c>
       <c r="R104" t="n">
-        <v>6380832</v>
+        <v>6380854</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876755</v>
+        <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98366</v>
+        <v>98237</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12623,26 +12623,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>723344</v>
+        <v>722988</v>
       </c>
       <c r="R105" t="n">
-        <v>6380853</v>
+        <v>6380785</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876745</v>
+        <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>723252</v>
+        <v>722934</v>
       </c>
       <c r="R106" t="n">
-        <v>6380854</v>
+        <v>6380847</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876685</v>
+        <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>722988</v>
+        <v>723026</v>
       </c>
       <c r="R107" t="n">
-        <v>6380785</v>
+        <v>6380845</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876675</v>
+        <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>722934</v>
+        <v>723355</v>
       </c>
       <c r="R108" t="n">
-        <v>6380847</v>
+        <v>6380807</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876699</v>
+        <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723026</v>
+        <v>723064</v>
       </c>
       <c r="R109" t="n">
-        <v>6380845</v>
+        <v>6380825</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876777</v>
+        <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98371</v>
+        <v>98367</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723355</v>
+        <v>723038</v>
       </c>
       <c r="R110" t="n">
-        <v>6380807</v>
+        <v>6380832</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876706</v>
+        <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98371</v>
+        <v>98368</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723064</v>
+        <v>723344</v>
       </c>
       <c r="R111" t="n">
-        <v>6380825</v>
+        <v>6380853</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>107214</v>
+        <v>107218</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13883,59 +13883,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876674</v>
+        <v>125876819</v>
       </c>
       <c r="B116" t="n">
-        <v>98235</v>
+        <v>109160</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722924</v>
+        <v>723194</v>
       </c>
       <c r="R116" t="n">
-        <v>6380847</v>
+        <v>6380741</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13985,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876823</v>
+        <v>125876674</v>
       </c>
       <c r="B117" t="n">
-        <v>110423</v>
+        <v>98237</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,34 +13996,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219711</v>
+        <v>219769</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723189</v>
+        <v>722924</v>
       </c>
       <c r="R117" t="n">
-        <v>6380746</v>
+        <v>6380847</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,45 +14101,59 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876819</v>
+        <v>125876676</v>
       </c>
       <c r="B118" t="n">
-        <v>109156</v>
+        <v>98368</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>723194</v>
+        <v>722956</v>
       </c>
       <c r="R118" t="n">
-        <v>6380741</v>
+        <v>6380853</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14203,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B119" t="n">
-        <v>98366</v>
+        <v>98373</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14214,26 +14228,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14252,10 +14266,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R119" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14319,10 +14333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876709</v>
+        <v>125876823</v>
       </c>
       <c r="B120" t="n">
-        <v>98371</v>
+        <v>110427</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14330,16 +14344,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219864</v>
+        <v>219711</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -14347,31 +14361,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723074</v>
+        <v>723189</v>
       </c>
       <c r="R120" t="n">
-        <v>6380823</v>
+        <v>6380746</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14438,7 +14438,7 @@
         <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14551,37 +14551,37 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876690</v>
+        <v>125876667</v>
       </c>
       <c r="B122" t="n">
-        <v>98235</v>
+        <v>109160</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14600,10 +14600,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723004</v>
+        <v>723014</v>
       </c>
       <c r="R122" t="n">
-        <v>6380791</v>
+        <v>6380862</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14667,32 +14667,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876763</v>
+        <v>125876718</v>
       </c>
       <c r="B123" t="n">
-        <v>98235</v>
+        <v>109160</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14716,10 +14716,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723370</v>
+        <v>723068</v>
       </c>
       <c r="R123" t="n">
-        <v>6380863</v>
+        <v>6380835</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14783,37 +14783,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876710</v>
+        <v>125876792</v>
       </c>
       <c r="B124" t="n">
-        <v>98377</v>
+        <v>107218</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>220079</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14827,10 +14827,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723098</v>
+        <v>723296</v>
       </c>
       <c r="R124" t="n">
-        <v>6380819</v>
+        <v>6380797</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,37 +14894,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876792</v>
+        <v>125876710</v>
       </c>
       <c r="B125" t="n">
-        <v>107214</v>
+        <v>98379</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14938,10 +14938,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723296</v>
+        <v>723098</v>
       </c>
       <c r="R125" t="n">
-        <v>6380797</v>
+        <v>6380819</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876767</v>
+        <v>125876690</v>
       </c>
       <c r="B126" t="n">
-        <v>98371</v>
+        <v>98237</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15016,21 +15016,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723375</v>
+        <v>723004</v>
       </c>
       <c r="R126" t="n">
-        <v>6380878</v>
+        <v>6380791</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,10 +15121,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876766</v>
+        <v>125876767</v>
       </c>
       <c r="B127" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15170,10 +15170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723369</v>
+        <v>723375</v>
       </c>
       <c r="R127" t="n">
-        <v>6380880</v>
+        <v>6380878</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,32 +15237,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876667</v>
+        <v>125876763</v>
       </c>
       <c r="B128" t="n">
-        <v>109156</v>
+        <v>98237</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723014</v>
+        <v>723370</v>
       </c>
       <c r="R128" t="n">
-        <v>6380862</v>
+        <v>6380863</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,27 +15353,27 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876718</v>
+        <v>125876766</v>
       </c>
       <c r="B129" t="n">
-        <v>109156</v>
+        <v>98373</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723068</v>
+        <v>723369</v>
       </c>
       <c r="R129" t="n">
-        <v>6380835</v>
+        <v>6380880</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126003997</v>
       </c>
       <c r="B133" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16281,10 +16281,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126003978</v>
+        <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98235</v>
+        <v>98373</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16292,26 +16292,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16397,10 +16397,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126003974</v>
+        <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98371</v>
+        <v>98368</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16408,26 +16408,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>723349</v>
+        <v>723470</v>
       </c>
       <c r="R138" t="n">
-        <v>6380791</v>
+        <v>6380822</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16513,10 +16513,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126003993</v>
+        <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16565,7 +16565,7 @@
         <v>723470</v>
       </c>
       <c r="R139" t="n">
-        <v>6380822</v>
+        <v>6380826</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16629,10 +16629,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126003995</v>
+        <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98366</v>
+        <v>98237</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16640,26 +16640,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>723470</v>
+        <v>723349</v>
       </c>
       <c r="R140" t="n">
-        <v>6380826</v>
+        <v>6380791</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -16748,7 +16748,7 @@
         <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>103785</v>
+        <v>103789</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,48 +17548,62 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126004076</v>
+        <v>126004013</v>
       </c>
       <c r="B148" t="n">
-        <v>5492</v>
+        <v>98373</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723369</v>
+        <v>723461</v>
       </c>
       <c r="R148" t="n">
-        <v>6380814</v>
+        <v>6380878</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17619,11 +17633,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17655,62 +17664,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126004013</v>
+        <v>126004076</v>
       </c>
       <c r="B149" t="n">
-        <v>98371</v>
+        <v>5492</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219864</v>
+        <v>101410</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723461</v>
+        <v>723369</v>
       </c>
       <c r="R149" t="n">
-        <v>6380878</v>
+        <v>6380814</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17740,6 +17735,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17774,7 +17774,7 @@
         <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126003990</v>
+        <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>99018</v>
+        <v>98368</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723426</v>
+        <v>723516</v>
       </c>
       <c r="R154" t="n">
-        <v>6380811</v>
+        <v>6380880</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,11 +18322,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18338,7 +18333,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18356,10 +18351,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126004002</v>
+        <v>126003996</v>
       </c>
       <c r="B155" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18386,7 +18381,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18405,10 +18400,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723516</v>
+        <v>723479</v>
       </c>
       <c r="R155" t="n">
-        <v>6380880</v>
+        <v>6380833</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18472,10 +18467,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126003996</v>
+        <v>126004014</v>
       </c>
       <c r="B156" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18502,7 +18497,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18521,10 +18516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723479</v>
+        <v>723461</v>
       </c>
       <c r="R156" t="n">
-        <v>6380833</v>
+        <v>6380878</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18588,47 +18583,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126004014</v>
+        <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>98366</v>
+        <v>99020</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18637,10 +18632,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723461</v>
+        <v>723426</v>
       </c>
       <c r="R157" t="n">
-        <v>6380878</v>
+        <v>6380811</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18675,6 +18670,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18704,10 +18704,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126003973</v>
+        <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>110423</v>
+        <v>98323</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18715,26 +18715,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>723349</v>
+        <v>723516</v>
       </c>
       <c r="R158" t="n">
-        <v>6380791</v>
+        <v>6380880</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18820,10 +18820,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126004000</v>
+        <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>98321</v>
+        <v>110427</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18831,26 +18831,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18869,10 +18869,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>723516</v>
+        <v>723349</v>
       </c>
       <c r="R159" t="n">
-        <v>6380880</v>
+        <v>6380791</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98235</v>
+        <v>98237</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -8928,57 +8928,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876910</v>
+        <v>125876757</v>
       </c>
       <c r="B73" t="n">
-        <v>95948</v>
+        <v>103789</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>220164</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723027</v>
+        <v>723360</v>
       </c>
       <c r="R73" t="n">
-        <v>6380801</v>
+        <v>6380851</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9018,6 +9009,11 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9034,48 +9030,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876921</v>
+        <v>125876810</v>
       </c>
       <c r="B74" t="n">
-        <v>5492</v>
+        <v>98263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723364</v>
+        <v>723234</v>
       </c>
       <c r="R74" t="n">
-        <v>6380813</v>
+        <v>6380772</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9107,11 +9117,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9120,6 +9125,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9136,10 +9146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876741</v>
+        <v>125876910</v>
       </c>
       <c r="B75" t="n">
-        <v>98237</v>
+        <v>95948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9147,36 +9157,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219769</v>
+        <v>2180</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9185,13 +9190,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723189</v>
+        <v>723027</v>
       </c>
       <c r="R75" t="n">
-        <v>6380869</v>
+        <v>6380801</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9231,11 +9236,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9252,62 +9252,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876658</v>
+        <v>125876921</v>
       </c>
       <c r="B76" t="n">
-        <v>98237</v>
+        <v>5492</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219769</v>
+        <v>101410</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723022</v>
+        <v>723364</v>
       </c>
       <c r="R76" t="n">
-        <v>6380859</v>
+        <v>6380813</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9339,6 +9325,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9347,11 +9338,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9368,7 +9354,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876717</v>
+        <v>125876741</v>
       </c>
       <c r="B77" t="n">
         <v>98237</v>
@@ -9398,7 +9384,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9417,10 +9403,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723080</v>
+        <v>723189</v>
       </c>
       <c r="R77" t="n">
-        <v>6380837</v>
+        <v>6380869</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9453,11 +9439,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9489,10 +9470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876716</v>
+        <v>125876658</v>
       </c>
       <c r="B78" t="n">
-        <v>98373</v>
+        <v>98237</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,26 +9481,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9538,13 +9519,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R78" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9574,11 +9555,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9610,7 +9586,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876776</v>
+        <v>125876717</v>
       </c>
       <c r="B79" t="n">
         <v>98237</v>
@@ -9640,7 +9616,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9659,13 +9635,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R79" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9695,6 +9671,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9726,10 +9707,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876729</v>
+        <v>125876716</v>
       </c>
       <c r="B80" t="n">
-        <v>98237</v>
+        <v>98373</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9737,26 +9718,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9775,13 +9756,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723135</v>
+        <v>723080</v>
       </c>
       <c r="R80" t="n">
-        <v>6380877</v>
+        <v>6380837</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9811,6 +9792,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9842,10 +9828,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876828</v>
+        <v>125876776</v>
       </c>
       <c r="B81" t="n">
-        <v>98373</v>
+        <v>98237</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9853,26 +9839,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9887,17 +9873,17 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723173</v>
+        <v>723342</v>
       </c>
       <c r="R81" t="n">
-        <v>6380765</v>
+        <v>6380826</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9940,7 +9926,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9958,7 +9944,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876715</v>
+        <v>125876729</v>
       </c>
       <c r="B82" t="n">
         <v>98237</v>
@@ -9988,7 +9974,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10007,10 +9993,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723098</v>
+        <v>723135</v>
       </c>
       <c r="R82" t="n">
-        <v>6380819</v>
+        <v>6380877</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10074,10 +10060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876810</v>
+        <v>125876828</v>
       </c>
       <c r="B83" t="n">
-        <v>98263</v>
+        <v>98373</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10085,26 +10071,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10114,22 +10100,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723234</v>
+        <v>723173</v>
       </c>
       <c r="R83" t="n">
-        <v>6380772</v>
+        <v>6380765</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10172,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10190,45 +10176,59 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876757</v>
+        <v>125876715</v>
       </c>
       <c r="B84" t="n">
-        <v>103789</v>
+        <v>98237</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R84" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -11568,37 +11568,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876740</v>
+        <v>125876707</v>
       </c>
       <c r="B96" t="n">
-        <v>107218</v>
+        <v>98237</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11606,16 +11606,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723183</v>
+        <v>723077</v>
       </c>
       <c r="R96" t="n">
-        <v>6380860</v>
+        <v>6380813</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11679,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876707</v>
+        <v>125876669</v>
       </c>
       <c r="B97" t="n">
-        <v>98237</v>
+        <v>98367</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11690,26 +11695,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11728,10 +11733,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723077</v>
+        <v>723014</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11795,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876669</v>
+        <v>125876820</v>
       </c>
       <c r="B98" t="n">
-        <v>98367</v>
+        <v>98237</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11806,26 +11811,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723014</v>
+        <v>723194</v>
       </c>
       <c r="R98" t="n">
-        <v>6380862</v>
+        <v>6380741</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11911,7 +11916,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876772</v>
       </c>
       <c r="B99" t="n">
         <v>98237</v>
@@ -11941,7 +11946,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11960,10 +11965,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723364</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11996,6 +12001,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12027,7 +12037,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876697</v>
       </c>
       <c r="B100" t="n">
         <v>98237</v>
@@ -12057,7 +12067,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12076,10 +12086,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723031</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380827</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12112,11 +12122,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12148,7 +12153,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876788</v>
       </c>
       <c r="B101" t="n">
         <v>98237</v>
@@ -12178,7 +12183,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12197,10 +12202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723320</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380799</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12264,10 +12269,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876719</v>
       </c>
       <c r="B102" t="n">
-        <v>98237</v>
+        <v>98373</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12275,26 +12280,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12313,13 +12318,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723068</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380835</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12380,37 +12385,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>98373</v>
+        <v>107218</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12418,24 +12423,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -17664,48 +17664,62 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126004076</v>
+        <v>126003976</v>
       </c>
       <c r="B149" t="n">
-        <v>5492</v>
+        <v>98263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723369</v>
+        <v>723349</v>
       </c>
       <c r="R149" t="n">
-        <v>6380814</v>
+        <v>6380791</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17735,11 +17749,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17771,62 +17780,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126003976</v>
+        <v>126004076</v>
       </c>
       <c r="B150" t="n">
-        <v>98263</v>
+        <v>5492</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>223591</v>
+        <v>101410</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>723349</v>
+        <v>723369</v>
       </c>
       <c r="R150" t="n">
-        <v>6380791</v>
+        <v>6380814</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17856,6 +17851,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD150" t="b">

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876673</v>
+        <v>125876817</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,26 +1641,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722989</v>
+        <v>723210</v>
       </c>
       <c r="R10" t="n">
-        <v>6380861</v>
+        <v>6380786</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876780</v>
+        <v>125876749</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,26 +1757,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723343</v>
+        <v>723321</v>
       </c>
       <c r="R11" t="n">
-        <v>6380811</v>
+        <v>6380856</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876691</v>
+        <v>125876673</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723017</v>
+        <v>722989</v>
       </c>
       <c r="R12" t="n">
-        <v>6380808</v>
+        <v>6380861</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876817</v>
+        <v>125876780</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,26 +1989,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723210</v>
+        <v>723343</v>
       </c>
       <c r="R13" t="n">
-        <v>6380786</v>
+        <v>6380811</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876703</v>
+        <v>125876691</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723050</v>
+        <v>723017</v>
       </c>
       <c r="R14" t="n">
-        <v>6380829</v>
+        <v>6380808</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125876749</v>
+        <v>125876703</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723321</v>
+        <v>723050</v>
       </c>
       <c r="R15" t="n">
-        <v>6380856</v>
+        <v>6380829</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>125876670</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>125876774</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876696</v>
+        <v>125876672</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>98372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723042</v>
+        <v>722989</v>
       </c>
       <c r="R20" t="n">
-        <v>6380816</v>
+        <v>6380861</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876672</v>
+        <v>125876769</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98383</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>722989</v>
+        <v>723375</v>
       </c>
       <c r="R21" t="n">
-        <v>6380861</v>
+        <v>6380878</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876732</v>
+        <v>125876696</v>
       </c>
       <c r="B22" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723148</v>
+        <v>723042</v>
       </c>
       <c r="R22" t="n">
-        <v>6380883</v>
+        <v>6380816</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876818</v>
+        <v>125876732</v>
       </c>
       <c r="B23" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723210</v>
+        <v>723148</v>
       </c>
       <c r="R23" t="n">
-        <v>6380786</v>
+        <v>6380883</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3223,11 +3223,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,10 +3254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876794</v>
+        <v>125876818</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3284,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723296</v>
+        <v>723210</v>
       </c>
       <c r="R24" t="n">
-        <v>6380797</v>
+        <v>6380786</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3344,6 +3339,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876769</v>
+        <v>125876794</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723375</v>
+        <v>723296</v>
       </c>
       <c r="R25" t="n">
-        <v>6380878</v>
+        <v>6380797</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876656</v>
+        <v>125876768</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>107231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,21 +3529,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723038</v>
+        <v>723375</v>
       </c>
       <c r="R26" t="n">
-        <v>6380861</v>
+        <v>6380878</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,10 +3602,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876731</v>
+        <v>125876656</v>
       </c>
       <c r="B27" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723148</v>
+        <v>723038</v>
       </c>
       <c r="R27" t="n">
-        <v>6380883</v>
+        <v>6380861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3723,37 +3718,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B28" t="n">
-        <v>98373</v>
+        <v>107231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3761,21 +3756,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R28" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3839,37 +3829,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876768</v>
+        <v>125876731</v>
       </c>
       <c r="B29" t="n">
-        <v>107218</v>
+        <v>98377</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3877,16 +3867,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723375</v>
+        <v>723148</v>
       </c>
       <c r="R29" t="n">
-        <v>6380878</v>
+        <v>6380883</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3950,37 +3945,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B30" t="n">
-        <v>107218</v>
+        <v>98377</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3988,16 +3983,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R30" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876663</v>
+        <v>125876813</v>
       </c>
       <c r="B34" t="n">
-        <v>98263</v>
+        <v>107231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223591</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,21 +4457,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723022</v>
+        <v>723238</v>
       </c>
       <c r="R34" t="n">
-        <v>6380875</v>
+        <v>6380770</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4535,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876778</v>
+        <v>125876682</v>
       </c>
       <c r="B35" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,26 +4541,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,13 +4579,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723355</v>
+        <v>722977</v>
       </c>
       <c r="R35" t="n">
-        <v>6380807</v>
+        <v>6380820</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4651,10 +4646,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876682</v>
+        <v>125876698</v>
       </c>
       <c r="B36" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4681,7 +4676,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4700,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>722977</v>
+        <v>723026</v>
       </c>
       <c r="R36" t="n">
-        <v>6380820</v>
+        <v>6380845</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4767,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876698</v>
+        <v>125876778</v>
       </c>
       <c r="B37" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,26 +4773,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4816,13 +4811,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723026</v>
+        <v>723355</v>
       </c>
       <c r="R37" t="n">
-        <v>6380845</v>
+        <v>6380807</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4886,7 +4881,7 @@
         <v>125876752</v>
       </c>
       <c r="B38" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4999,37 +4994,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876813</v>
+        <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>107218</v>
+        <v>98267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5037,16 +5032,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723238</v>
+        <v>723022</v>
       </c>
       <c r="R39" t="n">
-        <v>6380770</v>
+        <v>6380875</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5113,7 +5113,7 @@
         <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B47" t="n">
-        <v>98373</v>
+        <v>98327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876733</v>
+        <v>125876743</v>
       </c>
       <c r="B48" t="n">
-        <v>98323</v>
+        <v>98241</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,26 +6049,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723172</v>
+        <v>723221</v>
       </c>
       <c r="R48" t="n">
-        <v>6380881</v>
+        <v>6380864</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876743</v>
+        <v>125876814</v>
       </c>
       <c r="B49" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723221</v>
+        <v>723228</v>
       </c>
       <c r="R49" t="n">
-        <v>6380864</v>
+        <v>6380782</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876814</v>
+        <v>125876705</v>
       </c>
       <c r="B50" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723228</v>
+        <v>723064</v>
       </c>
       <c r="R50" t="n">
-        <v>6380782</v>
+        <v>6380825</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876705</v>
+        <v>125876728</v>
       </c>
       <c r="B51" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,26 +6397,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723064</v>
+        <v>723135</v>
       </c>
       <c r="R51" t="n">
-        <v>6380825</v>
+        <v>6380877</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107218</v>
+        <v>107231</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876661</v>
+        <v>125876761</v>
       </c>
       <c r="B53" t="n">
-        <v>109160</v>
+        <v>107231</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6624,26 +6624,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6651,21 +6651,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723022</v>
+        <v>723360</v>
       </c>
       <c r="R53" t="n">
-        <v>6380875</v>
+        <v>6380851</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,10 +6724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876714</v>
+        <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98323</v>
+        <v>98372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6735,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6769,7 +6764,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6778,10 +6773,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723098</v>
+        <v>722977</v>
       </c>
       <c r="R54" t="n">
-        <v>6380819</v>
+        <v>6380820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,37 +6840,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876681</v>
+        <v>125876786</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>107231</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6883,21 +6878,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>722977</v>
+        <v>723329</v>
       </c>
       <c r="R55" t="n">
-        <v>6380820</v>
+        <v>6380785</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6951,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876723</v>
+        <v>125876722</v>
       </c>
       <c r="B56" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6972,26 +6962,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723093</v>
+        <v>723061</v>
       </c>
       <c r="R56" t="n">
-        <v>6380849</v>
+        <v>6380859</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876736</v>
+        <v>125876826</v>
       </c>
       <c r="B57" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7088,26 +7078,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723172</v>
+        <v>723188</v>
       </c>
       <c r="R57" t="n">
-        <v>6380881</v>
+        <v>6380756</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7162,6 +7152,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7193,10 +7188,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876686</v>
+        <v>125876714</v>
       </c>
       <c r="B58" t="n">
-        <v>98237</v>
+        <v>98327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7204,26 +7199,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7233,7 +7228,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7242,10 +7237,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723006</v>
+        <v>723098</v>
       </c>
       <c r="R58" t="n">
-        <v>6380816</v>
+        <v>6380819</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7304,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876722</v>
+        <v>125876723</v>
       </c>
       <c r="B59" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7320,26 +7315,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7358,10 +7353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723061</v>
+        <v>723093</v>
       </c>
       <c r="R59" t="n">
-        <v>6380859</v>
+        <v>6380849</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,10 +7420,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876677</v>
+        <v>125876736</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,7 +7450,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7474,10 +7469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>722956</v>
+        <v>723172</v>
       </c>
       <c r="R60" t="n">
-        <v>6380853</v>
+        <v>6380881</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,10 +7536,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876739</v>
+        <v>125876686</v>
       </c>
       <c r="B61" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7571,7 +7566,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7590,10 +7585,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723173</v>
+        <v>723006</v>
       </c>
       <c r="R61" t="n">
-        <v>6380850</v>
+        <v>6380816</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7657,10 +7652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876738</v>
+        <v>125876677</v>
       </c>
       <c r="B62" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7687,7 +7682,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7706,10 +7701,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723157</v>
+        <v>722956</v>
       </c>
       <c r="R62" t="n">
-        <v>6380881</v>
+        <v>6380853</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7773,10 +7768,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876826</v>
+        <v>125876739</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7784,26 +7779,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7822,10 +7817,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723188</v>
+        <v>723173</v>
       </c>
       <c r="R63" t="n">
-        <v>6380756</v>
+        <v>6380850</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7858,11 +7853,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7894,37 +7884,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876761</v>
+        <v>125876738</v>
       </c>
       <c r="B64" t="n">
-        <v>107218</v>
+        <v>98241</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7932,16 +7922,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723360</v>
+        <v>723157</v>
       </c>
       <c r="R64" t="n">
-        <v>6380851</v>
+        <v>6380881</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8005,10 +8000,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876786</v>
+        <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>107218</v>
+        <v>109173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8016,26 +8011,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8043,16 +8038,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723329</v>
+        <v>723022</v>
       </c>
       <c r="R65" t="n">
-        <v>6380785</v>
+        <v>6380875</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8116,37 +8116,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125876735</v>
+        <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>109160</v>
+        <v>98372</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723172</v>
+        <v>723343</v>
       </c>
       <c r="R66" t="n">
-        <v>6380881</v>
+        <v>6380788</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8232,10 +8232,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876784</v>
+        <v>125876695</v>
       </c>
       <c r="B67" t="n">
-        <v>98368</v>
+        <v>98377</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8243,26 +8243,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723343</v>
+        <v>723040</v>
       </c>
       <c r="R67" t="n">
-        <v>6380788</v>
+        <v>6380808</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876695</v>
+        <v>125876793</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723040</v>
+        <v>723296</v>
       </c>
       <c r="R68" t="n">
-        <v>6380808</v>
+        <v>6380797</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876793</v>
+        <v>125876665</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>98372</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8475,26 +8475,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723296</v>
+        <v>723022</v>
       </c>
       <c r="R69" t="n">
-        <v>6380797</v>
+        <v>6380875</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876665</v>
+        <v>125876742</v>
       </c>
       <c r="B70" t="n">
-        <v>98368</v>
+        <v>98377</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R70" t="n">
-        <v>6380875</v>
+        <v>6380869</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8699,7 +8699,7 @@
         <v>125876785</v>
       </c>
       <c r="B71" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8812,27 +8812,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125876742</v>
+        <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>98373</v>
+        <v>109173</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723189</v>
+        <v>723172</v>
       </c>
       <c r="R72" t="n">
-        <v>6380869</v>
+        <v>6380881</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876757</v>
+        <v>125876921</v>
       </c>
       <c r="B73" t="n">
-        <v>103789</v>
+        <v>5492</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8939,21 +8939,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220164</v>
+        <v>101410</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8963,13 +8963,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723360</v>
+        <v>723364</v>
       </c>
       <c r="R73" t="n">
-        <v>6380851</v>
+        <v>6380813</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9001,6 +9001,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9009,11 +9014,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9030,10 +9030,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876810</v>
+        <v>125876910</v>
       </c>
       <c r="B74" t="n">
-        <v>98263</v>
+        <v>95952</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9041,36 +9041,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>2180</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9079,13 +9074,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723234</v>
+        <v>723027</v>
       </c>
       <c r="R74" t="n">
-        <v>6380772</v>
+        <v>6380801</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9125,11 +9120,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9146,57 +9136,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876910</v>
+        <v>125876757</v>
       </c>
       <c r="B75" t="n">
-        <v>95948</v>
+        <v>103802</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2180</v>
+        <v>220164</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723027</v>
+        <v>723360</v>
       </c>
       <c r="R75" t="n">
-        <v>6380801</v>
+        <v>6380851</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9236,6 +9217,11 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9252,48 +9238,62 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876921</v>
+        <v>125876716</v>
       </c>
       <c r="B76" t="n">
-        <v>5492</v>
+        <v>98377</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723364</v>
+        <v>723080</v>
       </c>
       <c r="R76" t="n">
-        <v>6380813</v>
+        <v>6380837</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Angripen tall.</t>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9338,6 +9338,11 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9354,10 +9359,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876741</v>
+        <v>125876828</v>
       </c>
       <c r="B77" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9365,26 +9370,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9399,14 +9404,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723189</v>
+        <v>723173</v>
       </c>
       <c r="R77" t="n">
-        <v>6380869</v>
+        <v>6380765</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9452,7 +9457,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9470,10 +9475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876658</v>
+        <v>125876741</v>
       </c>
       <c r="B78" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,7 +9505,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9519,10 +9524,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R78" t="n">
-        <v>6380859</v>
+        <v>6380869</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9586,10 +9591,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876717</v>
+        <v>125876658</v>
       </c>
       <c r="B79" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9616,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9635,10 +9640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723080</v>
+        <v>723022</v>
       </c>
       <c r="R79" t="n">
-        <v>6380837</v>
+        <v>6380859</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9671,11 +9676,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9707,10 +9707,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876716</v>
+        <v>125876717</v>
       </c>
       <c r="B80" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,26 +9718,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9762,7 +9762,7 @@
         <v>6380837</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>125876776</v>
       </c>
       <c r="B81" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>125876729</v>
       </c>
       <c r="B82" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876828</v>
+        <v>125876715</v>
       </c>
       <c r="B83" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10071,26 +10071,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723173</v>
+        <v>723098</v>
       </c>
       <c r="R83" t="n">
-        <v>6380765</v>
+        <v>6380819</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876715</v>
+        <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98237</v>
+        <v>98267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10187,26 +10187,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723098</v>
+        <v>723234</v>
       </c>
       <c r="R84" t="n">
-        <v>6380819</v>
+        <v>6380772</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876727</v>
+        <v>125876725</v>
       </c>
       <c r="B88" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10651,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10689,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723123</v>
+        <v>723122</v>
       </c>
       <c r="R88" t="n">
-        <v>6380868</v>
+        <v>6380858</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876754</v>
+        <v>125876727</v>
       </c>
       <c r="B89" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R89" t="n">
-        <v>6380853</v>
+        <v>6380868</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10841,11 +10841,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10877,10 +10872,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876666</v>
+        <v>125876754</v>
       </c>
       <c r="B90" t="n">
-        <v>98367</v>
+        <v>98377</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10888,26 +10883,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10926,13 +10921,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723022</v>
+        <v>723344</v>
       </c>
       <c r="R90" t="n">
-        <v>6380875</v>
+        <v>6380853</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10962,6 +10957,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10993,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876725</v>
+        <v>125876666</v>
       </c>
       <c r="B91" t="n">
-        <v>98237</v>
+        <v>98371</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723122</v>
+        <v>723022</v>
       </c>
       <c r="R91" t="n">
-        <v>6380858</v>
+        <v>6380875</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876744</v>
+        <v>125876781</v>
       </c>
       <c r="B92" t="n">
-        <v>98373</v>
+        <v>98267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723252</v>
+        <v>723343</v>
       </c>
       <c r="R92" t="n">
-        <v>6380854</v>
+        <v>6380811</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876683</v>
+        <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>722977</v>
+        <v>723252</v>
       </c>
       <c r="R93" t="n">
-        <v>6380820</v>
+        <v>6380854</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876781</v>
+        <v>125876683</v>
       </c>
       <c r="B94" t="n">
-        <v>98263</v>
+        <v>98241</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723343</v>
+        <v>722977</v>
       </c>
       <c r="R94" t="n">
-        <v>6380811</v>
+        <v>6380820</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B95" t="n">
-        <v>57649</v>
+        <v>107231</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11468,43 +11468,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R95" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11539,11 +11539,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,6 +11547,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11568,10 +11568,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876707</v>
+        <v>125876669</v>
       </c>
       <c r="B96" t="n">
-        <v>98237</v>
+        <v>98371</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11579,26 +11579,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723077</v>
+        <v>723014</v>
       </c>
       <c r="R96" t="n">
-        <v>6380813</v>
+        <v>6380862</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11684,10 +11684,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876669</v>
+        <v>125876719</v>
       </c>
       <c r="B97" t="n">
-        <v>98367</v>
+        <v>98377</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,21 +11695,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11733,13 +11733,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723014</v>
+        <v>723068</v>
       </c>
       <c r="R97" t="n">
-        <v>6380862</v>
+        <v>6380835</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11800,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876820</v>
+        <v>125876707</v>
       </c>
       <c r="B98" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,10 +11849,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723194</v>
+        <v>723077</v>
       </c>
       <c r="R98" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11916,10 +11916,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876772</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11965,10 +11965,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723364</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380813</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12001,11 +12001,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12037,10 +12032,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876697</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12067,7 +12062,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12086,10 +12081,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723031</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380827</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12122,6 +12117,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,10 +12153,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12280,26 +12280,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12318,13 +12318,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12385,10 +12385,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876945</v>
       </c>
       <c r="B103" t="n">
-        <v>107218</v>
+        <v>57653</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12396,43 +12396,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723296</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380797</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12467,6 +12467,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12475,11 +12480,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876699</v>
+        <v>125876777</v>
       </c>
       <c r="B107" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,13 +12893,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723026</v>
+        <v>723355</v>
       </c>
       <c r="R107" t="n">
-        <v>6380845</v>
+        <v>6380807</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876777</v>
+        <v>125876706</v>
       </c>
       <c r="B108" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723355</v>
+        <v>723064</v>
       </c>
       <c r="R108" t="n">
-        <v>6380807</v>
+        <v>6380825</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876706</v>
+        <v>125876702</v>
       </c>
       <c r="B109" t="n">
-        <v>98373</v>
+        <v>98371</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723064</v>
+        <v>723038</v>
       </c>
       <c r="R109" t="n">
-        <v>6380825</v>
+        <v>6380832</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876702</v>
+        <v>125876755</v>
       </c>
       <c r="B110" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723038</v>
+        <v>723344</v>
       </c>
       <c r="R110" t="n">
-        <v>6380832</v>
+        <v>6380853</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876755</v>
+        <v>125876699</v>
       </c>
       <c r="B111" t="n">
-        <v>98368</v>
+        <v>98241</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723344</v>
+        <v>723026</v>
       </c>
       <c r="R111" t="n">
-        <v>6380853</v>
+        <v>6380845</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13427,7 +13427,7 @@
         <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13656,37 +13656,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876765</v>
+        <v>125876811</v>
       </c>
       <c r="B114" t="n">
-        <v>98367</v>
+        <v>107231</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219862</v>
+        <v>220079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13694,21 +13694,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723369</v>
+        <v>723234</v>
       </c>
       <c r="R114" t="n">
-        <v>6380880</v>
+        <v>6380772</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13772,37 +13767,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876811</v>
+        <v>125876765</v>
       </c>
       <c r="B115" t="n">
-        <v>107218</v>
+        <v>98371</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13810,16 +13805,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723234</v>
+        <v>723369</v>
       </c>
       <c r="R115" t="n">
-        <v>6380772</v>
+        <v>6380880</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,45 +13883,59 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876819</v>
+        <v>125876676</v>
       </c>
       <c r="B116" t="n">
-        <v>109160</v>
+        <v>98372</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723194</v>
+        <v>722956</v>
       </c>
       <c r="R116" t="n">
-        <v>6380741</v>
+        <v>6380853</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13985,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876674</v>
+        <v>125876709</v>
       </c>
       <c r="B117" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13996,26 +14010,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14034,10 +14048,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>722924</v>
+        <v>723074</v>
       </c>
       <c r="R117" t="n">
-        <v>6380847</v>
+        <v>6380823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,10 +14115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876676</v>
+        <v>125876674</v>
       </c>
       <c r="B118" t="n">
-        <v>98368</v>
+        <v>98241</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14112,26 +14126,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14150,10 +14164,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722956</v>
+        <v>722924</v>
       </c>
       <c r="R118" t="n">
-        <v>6380853</v>
+        <v>6380847</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,10 +14231,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876709</v>
+        <v>125876823</v>
       </c>
       <c r="B119" t="n">
-        <v>98373</v>
+        <v>110440</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14228,16 +14242,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219864</v>
+        <v>219711</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14245,31 +14259,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723074</v>
+        <v>723189</v>
       </c>
       <c r="R119" t="n">
-        <v>6380823</v>
+        <v>6380746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876823</v>
+        <v>125876659</v>
       </c>
       <c r="B120" t="n">
-        <v>110427</v>
+        <v>98267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14344,34 +14344,48 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219711</v>
+        <v>223591</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723189</v>
+        <v>723022</v>
       </c>
       <c r="R120" t="n">
-        <v>6380746</v>
+        <v>6380869</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14435,59 +14449,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876659</v>
+        <v>125876819</v>
       </c>
       <c r="B121" t="n">
-        <v>98263</v>
+        <v>109173</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723022</v>
+        <v>723194</v>
       </c>
       <c r="R121" t="n">
-        <v>6380869</v>
+        <v>6380741</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14554,7 +14554,7 @@
         <v>125876667</v>
       </c>
       <c r="B122" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>125876718</v>
       </c>
       <c r="B123" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14783,37 +14783,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876792</v>
+        <v>125876710</v>
       </c>
       <c r="B124" t="n">
-        <v>107218</v>
+        <v>98383</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220079</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14827,10 +14827,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723296</v>
+        <v>723098</v>
       </c>
       <c r="R124" t="n">
-        <v>6380797</v>
+        <v>6380819</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,37 +14894,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876710</v>
+        <v>125876792</v>
       </c>
       <c r="B125" t="n">
-        <v>98379</v>
+        <v>107231</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219874</v>
+        <v>220079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14938,10 +14938,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723098</v>
+        <v>723296</v>
       </c>
       <c r="R125" t="n">
-        <v>6380819</v>
+        <v>6380797</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876690</v>
+        <v>125876767</v>
       </c>
       <c r="B126" t="n">
-        <v>98237</v>
+        <v>98377</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15016,21 +15016,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723004</v>
+        <v>723375</v>
       </c>
       <c r="R126" t="n">
-        <v>6380791</v>
+        <v>6380878</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,10 +15121,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876767</v>
+        <v>125876766</v>
       </c>
       <c r="B127" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15170,10 +15170,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723375</v>
+        <v>723369</v>
       </c>
       <c r="R127" t="n">
-        <v>6380878</v>
+        <v>6380880</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876763</v>
+        <v>125876690</v>
       </c>
       <c r="B128" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723370</v>
+        <v>723004</v>
       </c>
       <c r="R128" t="n">
-        <v>6380863</v>
+        <v>6380791</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,10 +15353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876766</v>
+        <v>125876763</v>
       </c>
       <c r="B129" t="n">
-        <v>98373</v>
+        <v>98241</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15364,26 +15364,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723369</v>
+        <v>723370</v>
       </c>
       <c r="R129" t="n">
-        <v>6380880</v>
+        <v>6380863</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003999</v>
+        <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>109160</v>
+        <v>98372</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723516</v>
+        <v>723483</v>
       </c>
       <c r="R132" t="n">
-        <v>6380880</v>
+        <v>6380826</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,10 +15817,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126003997</v>
+        <v>126004010</v>
       </c>
       <c r="B133" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723483</v>
+        <v>723469</v>
       </c>
       <c r="R133" t="n">
-        <v>6380826</v>
+        <v>6380865</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004010</v>
+        <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98368</v>
+        <v>98371</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723469</v>
+        <v>723496</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126004004</v>
+        <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>98367</v>
+        <v>109173</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723496</v>
+        <v>723516</v>
       </c>
       <c r="R135" t="n">
-        <v>6380865</v>
+        <v>6380880</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16745,45 +16745,59 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B141" t="n">
-        <v>103789</v>
+        <v>98241</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R141" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16818,11 +16832,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16834,7 +16843,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16852,59 +16861,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B142" t="n">
-        <v>98237</v>
+        <v>103802</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R142" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16939,6 +16934,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,62 +17548,48 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126004013</v>
+        <v>126004076</v>
       </c>
       <c r="B148" t="n">
-        <v>98373</v>
+        <v>5492</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219864</v>
+        <v>101410</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>723461</v>
+        <v>723369</v>
       </c>
       <c r="R148" t="n">
-        <v>6380878</v>
+        <v>6380814</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17633,6 +17619,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17664,10 +17655,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126003976</v>
+        <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>98263</v>
+        <v>98377</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17675,26 +17666,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17713,10 +17704,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>723349</v>
+        <v>723461</v>
       </c>
       <c r="R149" t="n">
-        <v>6380791</v>
+        <v>6380878</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -17780,48 +17771,62 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126004076</v>
+        <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>5492</v>
+        <v>98267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>101410</v>
+        <v>223591</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>723369</v>
+        <v>723349</v>
       </c>
       <c r="R150" t="n">
-        <v>6380814</v>
+        <v>6380791</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17851,11 +17856,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Tre tallar angripna.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>126003996</v>
       </c>
       <c r="B155" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>126004014</v>
       </c>
       <c r="B156" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110427</v>
+        <v>110440</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98327</v>
+        <v>98377</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,37 +6038,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876743</v>
+        <v>125876803</v>
       </c>
       <c r="B48" t="n">
-        <v>98241</v>
+        <v>107231</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6076,24 +6076,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723221</v>
+        <v>723244</v>
       </c>
       <c r="R48" t="n">
-        <v>6380864</v>
+        <v>6380753</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6149,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876814</v>
+        <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>98241</v>
+        <v>98327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,26 +6160,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6194,7 +6189,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723228</v>
+        <v>723172</v>
       </c>
       <c r="R49" t="n">
-        <v>6380782</v>
+        <v>6380881</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6270,7 +6265,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876705</v>
+        <v>125876743</v>
       </c>
       <c r="B50" t="n">
         <v>98241</v>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,13 +6314,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723064</v>
+        <v>723221</v>
       </c>
       <c r="R50" t="n">
-        <v>6380825</v>
+        <v>6380864</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6386,10 +6381,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876728</v>
+        <v>125876814</v>
       </c>
       <c r="B51" t="n">
-        <v>98377</v>
+        <v>98241</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,26 +6392,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,13 +6430,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723135</v>
+        <v>723228</v>
       </c>
       <c r="R51" t="n">
-        <v>6380877</v>
+        <v>6380782</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6502,37 +6497,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876803</v>
+        <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>107231</v>
+        <v>98241</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6540,16 +6535,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723244</v>
+        <v>723064</v>
       </c>
       <c r="R52" t="n">
-        <v>6380753</v>
+        <v>6380825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876724</v>
+        <v>125876727</v>
       </c>
       <c r="B87" t="n">
-        <v>98241</v>
+        <v>98377</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,26 +10535,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10576,10 +10576,10 @@
         <v>723123</v>
       </c>
       <c r="R87" t="n">
-        <v>6380848</v>
+        <v>6380868</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876725</v>
+        <v>125876754</v>
       </c>
       <c r="B88" t="n">
-        <v>98241</v>
+        <v>98377</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10651,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10689,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723122</v>
+        <v>723344</v>
       </c>
       <c r="R88" t="n">
-        <v>6380858</v>
+        <v>6380853</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10725,6 +10725,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10756,10 +10761,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876727</v>
+        <v>125876666</v>
       </c>
       <c r="B89" t="n">
-        <v>98377</v>
+        <v>98371</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10767,26 +10772,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10810,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723123</v>
+        <v>723022</v>
       </c>
       <c r="R89" t="n">
-        <v>6380868</v>
+        <v>6380875</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10872,10 +10877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876754</v>
+        <v>125876724</v>
       </c>
       <c r="B90" t="n">
-        <v>98377</v>
+        <v>98241</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10921,13 +10926,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R90" t="n">
-        <v>6380853</v>
+        <v>6380848</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10957,11 +10962,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10993,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876666</v>
+        <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98371</v>
+        <v>98241</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723022</v>
+        <v>723122</v>
       </c>
       <c r="R91" t="n">
-        <v>6380875</v>
+        <v>6380858</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -13424,37 +13424,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876664</v>
+        <v>125876811</v>
       </c>
       <c r="B112" t="n">
-        <v>98241</v>
+        <v>107231</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13462,21 +13462,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723022</v>
+        <v>723234</v>
       </c>
       <c r="R112" t="n">
-        <v>6380875</v>
+        <v>6380772</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,10 +13535,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876782</v>
+        <v>125876765</v>
       </c>
       <c r="B113" t="n">
-        <v>98241</v>
+        <v>98371</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13551,26 +13546,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13589,10 +13584,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723338</v>
+        <v>723369</v>
       </c>
       <c r="R113" t="n">
-        <v>6380799</v>
+        <v>6380880</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,37 +13651,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876811</v>
+        <v>125876664</v>
       </c>
       <c r="B114" t="n">
-        <v>107231</v>
+        <v>98241</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13694,16 +13689,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723234</v>
+        <v>723022</v>
       </c>
       <c r="R114" t="n">
-        <v>6380772</v>
+        <v>6380875</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,10 +13767,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B115" t="n">
-        <v>98371</v>
+        <v>98241</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13778,26 +13778,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R115" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>125876817</v>
       </c>
       <c r="B10" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125876749</v>
       </c>
       <c r="B11" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125876673</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>125876780</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>125876691</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>125876703</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876678</v>
       </c>
       <c r="B16" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>125876680</v>
       </c>
       <c r="B17" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876670</v>
+        <v>125876769</v>
       </c>
       <c r="B18" t="n">
-        <v>98372</v>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723014</v>
+        <v>723375</v>
       </c>
       <c r="R18" t="n">
-        <v>6380862</v>
+        <v>6380878</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876774</v>
+        <v>125876670</v>
       </c>
       <c r="B19" t="n">
-        <v>98371</v>
+        <v>98375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723342</v>
+        <v>723014</v>
       </c>
       <c r="R19" t="n">
-        <v>6380826</v>
+        <v>6380862</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876672</v>
+        <v>125876774</v>
       </c>
       <c r="B20" t="n">
-        <v>98372</v>
+        <v>98374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>722989</v>
+        <v>723342</v>
       </c>
       <c r="R20" t="n">
-        <v>6380861</v>
+        <v>6380826</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876769</v>
+        <v>125876696</v>
       </c>
       <c r="B21" t="n">
-        <v>98383</v>
+        <v>98244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723375</v>
+        <v>723042</v>
       </c>
       <c r="R21" t="n">
-        <v>6380878</v>
+        <v>6380816</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876696</v>
+        <v>125876672</v>
       </c>
       <c r="B22" t="n">
-        <v>98241</v>
+        <v>98375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,26 +3033,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723042</v>
+        <v>722989</v>
       </c>
       <c r="R22" t="n">
-        <v>6380816</v>
+        <v>6380861</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3141,7 +3141,7 @@
         <v>125876732</v>
       </c>
       <c r="B23" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>125876818</v>
       </c>
       <c r="B24" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125876794</v>
       </c>
       <c r="B25" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>125876768</v>
       </c>
       <c r="B26" t="n">
-        <v>107231</v>
+        <v>107234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>125876656</v>
       </c>
       <c r="B27" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>125876815</v>
       </c>
       <c r="B28" t="n">
-        <v>107231</v>
+        <v>107234</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>125876731</v>
       </c>
       <c r="B29" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>125876708</v>
       </c>
       <c r="B30" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125876805</v>
       </c>
       <c r="B33" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4419,37 +4419,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876813</v>
+        <v>125876663</v>
       </c>
       <c r="B34" t="n">
-        <v>107231</v>
+        <v>98270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4457,16 +4457,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723238</v>
+        <v>723022</v>
       </c>
       <c r="R34" t="n">
-        <v>6380770</v>
+        <v>6380875</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4530,10 +4535,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B35" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4541,26 +4546,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4579,13 +4584,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R35" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4646,10 +4651,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876698</v>
+        <v>125876752</v>
       </c>
       <c r="B36" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4657,26 +4662,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4695,10 +4700,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723026</v>
+        <v>723321</v>
       </c>
       <c r="R36" t="n">
-        <v>6380845</v>
+        <v>6380856</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4762,37 +4767,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876778</v>
+        <v>125876813</v>
       </c>
       <c r="B37" t="n">
-        <v>98241</v>
+        <v>107234</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4800,24 +4805,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723355</v>
+        <v>723238</v>
       </c>
       <c r="R37" t="n">
-        <v>6380807</v>
+        <v>6380770</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876752</v>
+        <v>125876682</v>
       </c>
       <c r="B38" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4889,26 +4889,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>722977</v>
       </c>
       <c r="R38" t="n">
-        <v>6380856</v>
+        <v>6380820</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876663</v>
+        <v>125876698</v>
       </c>
       <c r="B39" t="n">
-        <v>98267</v>
+        <v>98380</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,26 +5005,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723022</v>
+        <v>723026</v>
       </c>
       <c r="R39" t="n">
-        <v>6380875</v>
+        <v>6380845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876812</v>
+        <v>125876756</v>
       </c>
       <c r="B40" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,16 +5148,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723238</v>
+        <v>723344</v>
       </c>
       <c r="R40" t="n">
-        <v>6380770</v>
+        <v>6380853</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5221,10 +5226,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876671</v>
+        <v>125876812</v>
       </c>
       <c r="B41" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5251,7 +5256,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5259,21 +5264,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>722989</v>
+        <v>723238</v>
       </c>
       <c r="R41" t="n">
-        <v>6380861</v>
+        <v>6380770</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876762</v>
+        <v>125876671</v>
       </c>
       <c r="B42" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723370</v>
+        <v>722989</v>
       </c>
       <c r="R42" t="n">
-        <v>6380863</v>
+        <v>6380861</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876756</v>
+        <v>125876762</v>
       </c>
       <c r="B43" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723344</v>
+        <v>723370</v>
       </c>
       <c r="R43" t="n">
-        <v>6380853</v>
+        <v>6380863</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125876804</v>
+        <v>125876704</v>
       </c>
       <c r="B44" t="n">
-        <v>98372</v>
+        <v>98380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5580,26 +5580,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723050</v>
       </c>
       <c r="R44" t="n">
-        <v>6380753</v>
+        <v>6380829</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5654,6 +5654,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5685,10 +5690,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125876704</v>
+        <v>125876804</v>
       </c>
       <c r="B45" t="n">
-        <v>98377</v>
+        <v>98375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,26 +5701,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5734,10 +5739,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723050</v>
+        <v>723244</v>
       </c>
       <c r="R45" t="n">
-        <v>6380829</v>
+        <v>6380753</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5770,11 +5775,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5809,7 +5809,7 @@
         <v>125876711</v>
       </c>
       <c r="B46" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B47" t="n">
-        <v>98377</v>
+        <v>98330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,37 +6038,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876803</v>
+        <v>125876743</v>
       </c>
       <c r="B48" t="n">
-        <v>107231</v>
+        <v>98244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6076,19 +6076,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723244</v>
+        <v>723221</v>
       </c>
       <c r="R48" t="n">
-        <v>6380753</v>
+        <v>6380864</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6149,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876733</v>
+        <v>125876814</v>
       </c>
       <c r="B49" t="n">
-        <v>98327</v>
+        <v>98244</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,26 +6165,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6189,7 +6194,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723172</v>
+        <v>723228</v>
       </c>
       <c r="R49" t="n">
-        <v>6380881</v>
+        <v>6380782</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6265,10 +6270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876743</v>
+        <v>125876705</v>
       </c>
       <c r="B50" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6314,13 +6319,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723221</v>
+        <v>723064</v>
       </c>
       <c r="R50" t="n">
-        <v>6380864</v>
+        <v>6380825</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876814</v>
+        <v>125876728</v>
       </c>
       <c r="B51" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,26 +6397,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723228</v>
+        <v>723135</v>
       </c>
       <c r="R51" t="n">
-        <v>6380782</v>
+        <v>6380877</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,37 +6502,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876705</v>
+        <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>98241</v>
+        <v>107234</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6535,21 +6540,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723064</v>
+        <v>723244</v>
       </c>
       <c r="R52" t="n">
-        <v>6380825</v>
+        <v>6380753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,37 +6613,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876761</v>
+        <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>107231</v>
+        <v>98330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6651,16 +6651,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R53" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6727,7 +6732,7 @@
         <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6840,37 +6845,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876786</v>
+        <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>107231</v>
+        <v>98244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6878,16 +6883,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723329</v>
+        <v>723093</v>
       </c>
       <c r="R55" t="n">
-        <v>6380785</v>
+        <v>6380849</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6951,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876722</v>
+        <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6962,26 +6972,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7000,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723061</v>
+        <v>723172</v>
       </c>
       <c r="R56" t="n">
-        <v>6380859</v>
+        <v>6380881</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7067,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876826</v>
+        <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,26 +7088,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7116,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723188</v>
+        <v>723006</v>
       </c>
       <c r="R57" t="n">
-        <v>6380756</v>
+        <v>6380816</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7152,11 +7162,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7188,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876714</v>
+        <v>125876677</v>
       </c>
       <c r="B58" t="n">
-        <v>98327</v>
+        <v>98244</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7199,26 +7204,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7228,7 +7233,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7237,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723098</v>
+        <v>722956</v>
       </c>
       <c r="R58" t="n">
-        <v>6380819</v>
+        <v>6380853</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7304,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876723</v>
+        <v>125876739</v>
       </c>
       <c r="B59" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7334,7 +7339,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7353,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723093</v>
+        <v>723173</v>
       </c>
       <c r="R59" t="n">
-        <v>6380849</v>
+        <v>6380850</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7420,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876736</v>
+        <v>125876738</v>
       </c>
       <c r="B60" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7450,7 +7455,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7469,7 +7474,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723172</v>
+        <v>723157</v>
       </c>
       <c r="R60" t="n">
         <v>6380881</v>
@@ -7536,37 +7541,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876686</v>
+        <v>125876761</v>
       </c>
       <c r="B61" t="n">
-        <v>98241</v>
+        <v>107234</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7574,21 +7579,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723006</v>
+        <v>723360</v>
       </c>
       <c r="R61" t="n">
-        <v>6380816</v>
+        <v>6380851</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7652,37 +7652,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876677</v>
+        <v>125876786</v>
       </c>
       <c r="B62" t="n">
-        <v>98241</v>
+        <v>107234</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7690,21 +7690,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>722956</v>
+        <v>723329</v>
       </c>
       <c r="R62" t="n">
-        <v>6380853</v>
+        <v>6380785</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7768,10 +7763,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876739</v>
+        <v>125876722</v>
       </c>
       <c r="B63" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7779,26 +7774,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7817,10 +7812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723173</v>
+        <v>723061</v>
       </c>
       <c r="R63" t="n">
-        <v>6380850</v>
+        <v>6380859</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7884,10 +7879,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876738</v>
+        <v>125876826</v>
       </c>
       <c r="B64" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,26 +7890,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723157</v>
+        <v>723188</v>
       </c>
       <c r="R64" t="n">
-        <v>6380881</v>
+        <v>6380756</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7969,6 +7964,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8003,7 +8003,7 @@
         <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>125876784</v>
       </c>
       <c r="B66" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876695</v>
+        <v>125876665</v>
       </c>
       <c r="B67" t="n">
-        <v>98377</v>
+        <v>98375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8243,26 +8243,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723040</v>
+        <v>723022</v>
       </c>
       <c r="R67" t="n">
-        <v>6380808</v>
+        <v>6380875</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876793</v>
+        <v>125876785</v>
       </c>
       <c r="B68" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,26 +8359,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723296</v>
+        <v>723343</v>
       </c>
       <c r="R68" t="n">
-        <v>6380797</v>
+        <v>6380788</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876665</v>
+        <v>125876695</v>
       </c>
       <c r="B69" t="n">
-        <v>98372</v>
+        <v>98380</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8475,26 +8475,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723022</v>
+        <v>723040</v>
       </c>
       <c r="R69" t="n">
-        <v>6380875</v>
+        <v>6380808</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876742</v>
+        <v>125876793</v>
       </c>
       <c r="B70" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723189</v>
+        <v>723296</v>
       </c>
       <c r="R70" t="n">
-        <v>6380869</v>
+        <v>6380797</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125876785</v>
+        <v>125876742</v>
       </c>
       <c r="B71" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723343</v>
+        <v>723189</v>
       </c>
       <c r="R71" t="n">
-        <v>6380788</v>
+        <v>6380869</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>125876910</v>
       </c>
       <c r="B74" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>125876757</v>
       </c>
       <c r="B75" t="n">
-        <v>103802</v>
+        <v>103805</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876716</v>
+        <v>125876741</v>
       </c>
       <c r="B76" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9249,26 +9249,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9287,13 +9287,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723080</v>
+        <v>723189</v>
       </c>
       <c r="R76" t="n">
-        <v>6380837</v>
+        <v>6380869</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9323,11 +9323,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9359,10 +9354,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876828</v>
+        <v>125876658</v>
       </c>
       <c r="B77" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9370,26 +9365,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9404,14 +9399,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723173</v>
+        <v>723022</v>
       </c>
       <c r="R77" t="n">
-        <v>6380765</v>
+        <v>6380859</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9457,7 +9452,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9475,10 +9470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876741</v>
+        <v>125876717</v>
       </c>
       <c r="B78" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9505,7 +9500,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9524,10 +9519,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723189</v>
+        <v>723080</v>
       </c>
       <c r="R78" t="n">
-        <v>6380869</v>
+        <v>6380837</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9560,6 +9555,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9591,10 +9591,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876658</v>
+        <v>125876776</v>
       </c>
       <c r="B79" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9640,13 +9640,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723022</v>
+        <v>723342</v>
       </c>
       <c r="R79" t="n">
-        <v>6380859</v>
+        <v>6380826</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9707,10 +9707,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876717</v>
+        <v>125876729</v>
       </c>
       <c r="B80" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723080</v>
+        <v>723135</v>
       </c>
       <c r="R80" t="n">
-        <v>6380837</v>
+        <v>6380877</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9792,11 +9792,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9828,10 +9823,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876776</v>
+        <v>125876715</v>
       </c>
       <c r="B81" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9858,7 +9853,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9877,13 +9872,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723342</v>
+        <v>723098</v>
       </c>
       <c r="R81" t="n">
-        <v>6380826</v>
+        <v>6380819</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9944,10 +9939,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876729</v>
+        <v>125876716</v>
       </c>
       <c r="B82" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9955,26 +9950,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9993,13 +9988,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723135</v>
+        <v>723080</v>
       </c>
       <c r="R82" t="n">
-        <v>6380877</v>
+        <v>6380837</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10029,6 +10024,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10060,10 +10060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876715</v>
+        <v>125876828</v>
       </c>
       <c r="B83" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10071,26 +10071,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723098</v>
+        <v>723173</v>
       </c>
       <c r="R83" t="n">
-        <v>6380819</v>
+        <v>6380765</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10179,7 +10179,7 @@
         <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>125876684</v>
       </c>
       <c r="B85" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>125876783</v>
       </c>
       <c r="B86" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876727</v>
+        <v>125876724</v>
       </c>
       <c r="B87" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,26 +10535,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10576,10 +10576,10 @@
         <v>723123</v>
       </c>
       <c r="R87" t="n">
-        <v>6380868</v>
+        <v>6380848</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876754</v>
+        <v>125876666</v>
       </c>
       <c r="B88" t="n">
-        <v>98377</v>
+        <v>98374</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10651,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10689,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723344</v>
+        <v>723022</v>
       </c>
       <c r="R88" t="n">
-        <v>6380853</v>
+        <v>6380875</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10725,11 +10725,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10761,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876666</v>
+        <v>125876725</v>
       </c>
       <c r="B89" t="n">
-        <v>98371</v>
+        <v>98244</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10772,21 +10767,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10810,10 +10805,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723022</v>
+        <v>723122</v>
       </c>
       <c r="R89" t="n">
-        <v>6380875</v>
+        <v>6380858</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10877,10 +10872,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876724</v>
+        <v>125876727</v>
       </c>
       <c r="B90" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10888,26 +10883,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10929,10 +10924,10 @@
         <v>723123</v>
       </c>
       <c r="R90" t="n">
-        <v>6380848</v>
+        <v>6380868</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10993,10 +10988,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876725</v>
+        <v>125876754</v>
       </c>
       <c r="B91" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,26 +10999,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11042,13 +11037,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723122</v>
+        <v>723344</v>
       </c>
       <c r="R91" t="n">
-        <v>6380858</v>
+        <v>6380853</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11078,6 +11073,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876781</v>
+        <v>125876683</v>
       </c>
       <c r="B92" t="n">
-        <v>98267</v>
+        <v>98244</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,26 +11120,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723343</v>
+        <v>722977</v>
       </c>
       <c r="R92" t="n">
-        <v>6380811</v>
+        <v>6380820</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11228,7 +11228,7 @@
         <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876683</v>
+        <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98241</v>
+        <v>98270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,26 +11352,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R94" t="n">
-        <v>6380820</v>
+        <v>6380811</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11457,37 +11457,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876740</v>
+        <v>125876707</v>
       </c>
       <c r="B95" t="n">
-        <v>107231</v>
+        <v>98244</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11495,16 +11495,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723183</v>
+        <v>723077</v>
       </c>
       <c r="R95" t="n">
-        <v>6380860</v>
+        <v>6380813</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11571,7 +11576,7 @@
         <v>125876669</v>
       </c>
       <c r="B96" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11684,10 +11689,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876719</v>
+        <v>125876820</v>
       </c>
       <c r="B97" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11695,26 +11700,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11733,13 +11738,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723068</v>
+        <v>723194</v>
       </c>
       <c r="R97" t="n">
-        <v>6380835</v>
+        <v>6380741</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11800,10 +11805,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876707</v>
+        <v>125876772</v>
       </c>
       <c r="B98" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11830,7 +11835,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,7 +11854,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723077</v>
+        <v>723364</v>
       </c>
       <c r="R98" t="n">
         <v>6380813</v>
@@ -11885,6 +11890,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11916,10 +11926,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876820</v>
+        <v>125876697</v>
       </c>
       <c r="B99" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11946,7 +11956,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11965,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723194</v>
+        <v>723031</v>
       </c>
       <c r="R99" t="n">
-        <v>6380741</v>
+        <v>6380827</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12032,10 +12042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876772</v>
+        <v>125876788</v>
       </c>
       <c r="B100" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12062,7 +12072,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12081,10 +12091,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723364</v>
+        <v>723320</v>
       </c>
       <c r="R100" t="n">
-        <v>6380813</v>
+        <v>6380799</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12117,11 +12127,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,32 +12158,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876697</v>
+        <v>125876945</v>
       </c>
       <c r="B101" t="n">
-        <v>98241</v>
+        <v>57653</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12186,26 +12191,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723031</v>
+        <v>723296</v>
       </c>
       <c r="R101" t="n">
-        <v>6380827</v>
+        <v>6380797</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12240,6 +12240,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12248,11 +12253,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12269,37 +12269,37 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876788</v>
+        <v>125876740</v>
       </c>
       <c r="B102" t="n">
-        <v>98241</v>
+        <v>107234</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12307,21 +12307,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723320</v>
+        <v>723183</v>
       </c>
       <c r="R102" t="n">
-        <v>6380799</v>
+        <v>6380860</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12385,32 +12380,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876945</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>57653</v>
+        <v>98380</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12418,24 +12413,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12467,11 +12467,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +12475,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12499,7 +12499,7 @@
         <v>125876745</v>
       </c>
       <c r="B104" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>125876685</v>
       </c>
       <c r="B105" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>125876675</v>
       </c>
       <c r="B106" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876777</v>
+        <v>125876699</v>
       </c>
       <c r="B107" t="n">
-        <v>98377</v>
+        <v>98244</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12855,26 +12855,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,13 +12893,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723355</v>
+        <v>723026</v>
       </c>
       <c r="R107" t="n">
-        <v>6380807</v>
+        <v>6380845</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876706</v>
+        <v>125876702</v>
       </c>
       <c r="B108" t="n">
-        <v>98377</v>
+        <v>98374</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,10 +13009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723064</v>
+        <v>723038</v>
       </c>
       <c r="R108" t="n">
-        <v>6380825</v>
+        <v>6380832</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876702</v>
+        <v>125876755</v>
       </c>
       <c r="B109" t="n">
-        <v>98371</v>
+        <v>98375</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723038</v>
+        <v>723344</v>
       </c>
       <c r="R109" t="n">
-        <v>6380832</v>
+        <v>6380853</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876755</v>
+        <v>125876777</v>
       </c>
       <c r="B110" t="n">
-        <v>98372</v>
+        <v>98380</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723344</v>
+        <v>723355</v>
       </c>
       <c r="R110" t="n">
-        <v>6380853</v>
+        <v>6380807</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876699</v>
+        <v>125876706</v>
       </c>
       <c r="B111" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723026</v>
+        <v>723064</v>
       </c>
       <c r="R111" t="n">
-        <v>6380845</v>
+        <v>6380825</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13427,7 +13427,7 @@
         <v>125876811</v>
       </c>
       <c r="B112" t="n">
-        <v>107231</v>
+        <v>107234</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13535,10 +13535,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876765</v>
+        <v>125876782</v>
       </c>
       <c r="B113" t="n">
-        <v>98371</v>
+        <v>98244</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13546,26 +13546,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723369</v>
+        <v>723338</v>
       </c>
       <c r="R113" t="n">
-        <v>6380880</v>
+        <v>6380799</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13651,10 +13651,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876664</v>
+        <v>125876765</v>
       </c>
       <c r="B114" t="n">
-        <v>98241</v>
+        <v>98374</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13662,21 +13662,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13700,10 +13700,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723022</v>
+        <v>723369</v>
       </c>
       <c r="R114" t="n">
-        <v>6380875</v>
+        <v>6380880</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13767,10 +13767,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876782</v>
+        <v>125876664</v>
       </c>
       <c r="B115" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723338</v>
+        <v>723022</v>
       </c>
       <c r="R115" t="n">
-        <v>6380799</v>
+        <v>6380875</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B116" t="n">
-        <v>98372</v>
+        <v>98380</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R116" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876709</v>
+        <v>125876659</v>
       </c>
       <c r="B117" t="n">
-        <v>98377</v>
+        <v>98270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,26 +14010,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723074</v>
+        <v>723022</v>
       </c>
       <c r="R117" t="n">
-        <v>6380823</v>
+        <v>6380869</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14118,7 +14118,7 @@
         <v>125876674</v>
       </c>
       <c r="B118" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>125876823</v>
       </c>
       <c r="B119" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876659</v>
+        <v>125876676</v>
       </c>
       <c r="B120" t="n">
-        <v>98267</v>
+        <v>98375</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14344,26 +14344,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14382,10 +14382,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723022</v>
+        <v>722956</v>
       </c>
       <c r="R120" t="n">
-        <v>6380869</v>
+        <v>6380853</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14452,7 +14452,7 @@
         <v>125876819</v>
       </c>
       <c r="B121" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>125876667</v>
       </c>
       <c r="B122" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>125876718</v>
       </c>
       <c r="B123" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14783,10 +14783,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876710</v>
+        <v>125876690</v>
       </c>
       <c r="B124" t="n">
-        <v>98383</v>
+        <v>98244</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14794,26 +14794,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14821,16 +14821,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723098</v>
+        <v>723004</v>
       </c>
       <c r="R124" t="n">
-        <v>6380819</v>
+        <v>6380791</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,37 +14899,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876792</v>
+        <v>125876763</v>
       </c>
       <c r="B125" t="n">
-        <v>107231</v>
+        <v>98244</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14932,16 +14937,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723296</v>
+        <v>723370</v>
       </c>
       <c r="R125" t="n">
-        <v>6380797</v>
+        <v>6380863</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,10 +15015,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876767</v>
+        <v>125876710</v>
       </c>
       <c r="B126" t="n">
-        <v>98377</v>
+        <v>98386</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15016,26 +15026,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219864</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15043,21 +15053,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723375</v>
+        <v>723098</v>
       </c>
       <c r="R126" t="n">
-        <v>6380878</v>
+        <v>6380819</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,32 +15126,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876766</v>
+        <v>125876792</v>
       </c>
       <c r="B127" t="n">
-        <v>98377</v>
+        <v>107234</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -15159,21 +15164,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723369</v>
+        <v>723296</v>
       </c>
       <c r="R127" t="n">
-        <v>6380880</v>
+        <v>6380797</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876690</v>
+        <v>125876767</v>
       </c>
       <c r="B128" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15248,21 +15248,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723004</v>
+        <v>723375</v>
       </c>
       <c r="R128" t="n">
-        <v>6380791</v>
+        <v>6380878</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,10 +15353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876763</v>
+        <v>125876766</v>
       </c>
       <c r="B129" t="n">
-        <v>98241</v>
+        <v>98380</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15364,26 +15364,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723370</v>
+        <v>723369</v>
       </c>
       <c r="R129" t="n">
-        <v>6380863</v>
+        <v>6380880</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>126004010</v>
       </c>
       <c r="B133" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16745,59 +16745,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003986</v>
+        <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>98241</v>
+        <v>103805</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>723379</v>
+        <v>723461</v>
       </c>
       <c r="R141" t="n">
-        <v>6380799</v>
+        <v>6380842</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16832,6 +16818,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -16843,7 +16834,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16861,45 +16852,59 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003972</v>
+        <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>103802</v>
+        <v>98244</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>723461</v>
+        <v>723379</v>
       </c>
       <c r="R142" t="n">
-        <v>6380842</v>
+        <v>6380799</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16934,11 +16939,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126004013</v>
       </c>
       <c r="B149" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>126003976</v>
       </c>
       <c r="B150" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>126004012</v>
       </c>
       <c r="B151" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>126003987</v>
       </c>
       <c r="B152" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>126003988</v>
       </c>
       <c r="B153" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126004002</v>
+        <v>126003990</v>
       </c>
       <c r="B154" t="n">
-        <v>98372</v>
+        <v>99027</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723516</v>
+        <v>723426</v>
       </c>
       <c r="R154" t="n">
-        <v>6380880</v>
+        <v>6380811</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,6 +18322,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18333,7 +18338,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18351,10 +18356,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126003996</v>
+        <v>126004002</v>
       </c>
       <c r="B155" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18381,7 +18386,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18400,10 +18405,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723479</v>
+        <v>723516</v>
       </c>
       <c r="R155" t="n">
-        <v>6380833</v>
+        <v>6380880</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18467,10 +18472,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126004014</v>
+        <v>126003996</v>
       </c>
       <c r="B156" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18497,7 +18502,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18516,10 +18521,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723461</v>
+        <v>723479</v>
       </c>
       <c r="R156" t="n">
-        <v>6380878</v>
+        <v>6380833</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18583,47 +18588,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126003990</v>
+        <v>126004014</v>
       </c>
       <c r="B157" t="n">
-        <v>99024</v>
+        <v>98375</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18632,10 +18637,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723426</v>
+        <v>723461</v>
       </c>
       <c r="R157" t="n">
-        <v>6380811</v>
+        <v>6380878</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18670,11 +18675,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
         <v>126004000</v>
       </c>
       <c r="B158" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>126003973</v>
       </c>
       <c r="B159" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>126003983</v>
       </c>
       <c r="B160" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876806</v>
+        <v>125876712</v>
       </c>
       <c r="B31" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R31" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,11 +4146,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,10 +4177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876712</v>
+        <v>125876806</v>
       </c>
       <c r="B32" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4193,26 +4188,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R32" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,6 +4262,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876663</v>
+        <v>125876778</v>
       </c>
       <c r="B34" t="n">
-        <v>98270</v>
+        <v>98244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4468,13 +4468,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723022</v>
+        <v>723355</v>
       </c>
       <c r="R34" t="n">
-        <v>6380875</v>
+        <v>6380807</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876778</v>
+        <v>125876752</v>
       </c>
       <c r="B35" t="n">
         <v>98244</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723355</v>
+        <v>723321</v>
       </c>
       <c r="R35" t="n">
-        <v>6380807</v>
+        <v>6380856</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4651,37 +4651,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876752</v>
+        <v>125876813</v>
       </c>
       <c r="B36" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4689,21 +4689,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723321</v>
+        <v>723238</v>
       </c>
       <c r="R36" t="n">
-        <v>6380856</v>
+        <v>6380770</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4767,37 +4762,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876813</v>
+        <v>125876682</v>
       </c>
       <c r="B37" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4805,16 +4800,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723238</v>
+        <v>722977</v>
       </c>
       <c r="R37" t="n">
-        <v>6380770</v>
+        <v>6380820</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4878,7 +4878,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876682</v>
+        <v>125876698</v>
       </c>
       <c r="B38" t="n">
         <v>98380</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>722977</v>
+        <v>723026</v>
       </c>
       <c r="R38" t="n">
-        <v>6380820</v>
+        <v>6380845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125876698</v>
+        <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98380</v>
+        <v>98270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,26 +5005,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723026</v>
+        <v>723022</v>
       </c>
       <c r="R39" t="n">
-        <v>6380845</v>
+        <v>6380875</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876756</v>
+        <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,21 +5148,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723344</v>
+        <v>723238</v>
       </c>
       <c r="R40" t="n">
-        <v>6380853</v>
+        <v>6380770</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5226,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876812</v>
+        <v>125876671</v>
       </c>
       <c r="B41" t="n">
         <v>98380</v>
@@ -5256,7 +5251,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5264,16 +5259,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723238</v>
+        <v>722989</v>
       </c>
       <c r="R41" t="n">
-        <v>6380770</v>
+        <v>6380861</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876671</v>
+        <v>125876762</v>
       </c>
       <c r="B42" t="n">
         <v>98380</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>722989</v>
+        <v>723370</v>
       </c>
       <c r="R42" t="n">
-        <v>6380861</v>
+        <v>6380863</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876762</v>
+        <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723370</v>
+        <v>723344</v>
       </c>
       <c r="R43" t="n">
-        <v>6380863</v>
+        <v>6380853</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B47" t="n">
-        <v>98330</v>
+        <v>98380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R47" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,37 +6038,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876743</v>
+        <v>125876803</v>
       </c>
       <c r="B48" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6076,24 +6076,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723221</v>
+        <v>723244</v>
       </c>
       <c r="R48" t="n">
-        <v>6380864</v>
+        <v>6380753</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6149,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876814</v>
+        <v>125876733</v>
       </c>
       <c r="B49" t="n">
-        <v>98244</v>
+        <v>98330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,26 +6160,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6194,7 +6189,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723228</v>
+        <v>723172</v>
       </c>
       <c r="R49" t="n">
-        <v>6380782</v>
+        <v>6380881</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6270,7 +6265,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876705</v>
+        <v>125876743</v>
       </c>
       <c r="B50" t="n">
         <v>98244</v>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,13 +6314,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723064</v>
+        <v>723221</v>
       </c>
       <c r="R50" t="n">
-        <v>6380825</v>
+        <v>6380864</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6386,10 +6381,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876728</v>
+        <v>125876814</v>
       </c>
       <c r="B51" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,26 +6392,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,13 +6430,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723135</v>
+        <v>723228</v>
       </c>
       <c r="R51" t="n">
-        <v>6380877</v>
+        <v>6380782</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6502,37 +6497,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876803</v>
+        <v>125876705</v>
       </c>
       <c r="B52" t="n">
-        <v>107234</v>
+        <v>98244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6540,16 +6535,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723244</v>
+        <v>723064</v>
       </c>
       <c r="R52" t="n">
-        <v>6380753</v>
+        <v>6380825</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -8928,48 +8928,62 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876921</v>
+        <v>125876716</v>
       </c>
       <c r="B73" t="n">
-        <v>5492</v>
+        <v>98380</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723364</v>
+        <v>723080</v>
       </c>
       <c r="R73" t="n">
-        <v>6380813</v>
+        <v>6380837</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9003,7 +9017,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Angripen tall.</t>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9014,6 +9028,11 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9030,10 +9049,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876910</v>
+        <v>125876828</v>
       </c>
       <c r="B74" t="n">
-        <v>95955</v>
+        <v>98380</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9041,46 +9060,51 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723027</v>
+        <v>723173</v>
       </c>
       <c r="R74" t="n">
-        <v>6380801</v>
+        <v>6380765</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9120,6 +9144,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Alvar och torräng.</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9238,10 +9267,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876741</v>
+        <v>125876810</v>
       </c>
       <c r="B76" t="n">
-        <v>98244</v>
+        <v>98270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9249,26 +9278,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9278,7 +9307,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9287,13 +9316,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723189</v>
+        <v>723234</v>
       </c>
       <c r="R76" t="n">
-        <v>6380869</v>
+        <v>6380772</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9354,62 +9383,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876658</v>
+        <v>125876921</v>
       </c>
       <c r="B77" t="n">
-        <v>98244</v>
+        <v>5492</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219769</v>
+        <v>101410</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723022</v>
+        <v>723364</v>
       </c>
       <c r="R77" t="n">
-        <v>6380859</v>
+        <v>6380813</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9441,6 +9456,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9449,11 +9469,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9470,10 +9485,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876717</v>
+        <v>125876910</v>
       </c>
       <c r="B78" t="n">
-        <v>98244</v>
+        <v>95955</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9481,36 +9496,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219769</v>
+        <v>2180</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9519,13 +9529,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723080</v>
+        <v>723027</v>
       </c>
       <c r="R78" t="n">
-        <v>6380837</v>
+        <v>6380801</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9557,11 +9567,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9570,11 +9575,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9591,7 +9591,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876776</v>
+        <v>125876741</v>
       </c>
       <c r="B79" t="n">
         <v>98244</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9640,13 +9640,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723342</v>
+        <v>723189</v>
       </c>
       <c r="R79" t="n">
-        <v>6380826</v>
+        <v>6380869</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876729</v>
+        <v>125876658</v>
       </c>
       <c r="B80" t="n">
         <v>98244</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723135</v>
+        <v>723022</v>
       </c>
       <c r="R80" t="n">
-        <v>6380877</v>
+        <v>6380859</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9823,7 +9823,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876715</v>
+        <v>125876717</v>
       </c>
       <c r="B81" t="n">
         <v>98244</v>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723098</v>
+        <v>723080</v>
       </c>
       <c r="R81" t="n">
-        <v>6380819</v>
+        <v>6380837</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9908,6 +9908,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9939,10 +9944,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876716</v>
+        <v>125876776</v>
       </c>
       <c r="B82" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9950,26 +9955,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9988,13 +9993,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723080</v>
+        <v>723342</v>
       </c>
       <c r="R82" t="n">
-        <v>6380837</v>
+        <v>6380826</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10024,11 +10029,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10060,10 +10060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876828</v>
+        <v>125876729</v>
       </c>
       <c r="B83" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10071,26 +10071,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723173</v>
+        <v>723135</v>
       </c>
       <c r="R83" t="n">
-        <v>6380765</v>
+        <v>6380877</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876810</v>
+        <v>125876715</v>
       </c>
       <c r="B84" t="n">
-        <v>98270</v>
+        <v>98244</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10187,26 +10187,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723234</v>
+        <v>723098</v>
       </c>
       <c r="R84" t="n">
-        <v>6380772</v>
+        <v>6380819</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876683</v>
+        <v>125876781</v>
       </c>
       <c r="B92" t="n">
-        <v>98244</v>
+        <v>98270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,26 +11120,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R92" t="n">
-        <v>6380820</v>
+        <v>6380811</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876744</v>
+        <v>125876683</v>
       </c>
       <c r="B93" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723252</v>
+        <v>722977</v>
       </c>
       <c r="R93" t="n">
-        <v>6380854</v>
+        <v>6380820</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876781</v>
+        <v>125876744</v>
       </c>
       <c r="B94" t="n">
-        <v>98270</v>
+        <v>98380</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,21 +11352,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11390,13 +11390,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723343</v>
+        <v>723252</v>
       </c>
       <c r="R94" t="n">
-        <v>6380811</v>
+        <v>6380854</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876659</v>
+        <v>125876674</v>
       </c>
       <c r="B117" t="n">
-        <v>98270</v>
+        <v>98244</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,26 +14010,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723022</v>
+        <v>722924</v>
       </c>
       <c r="R117" t="n">
-        <v>6380869</v>
+        <v>6380847</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14115,10 +14115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876674</v>
+        <v>125876823</v>
       </c>
       <c r="B118" t="n">
-        <v>98244</v>
+        <v>110443</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14126,48 +14126,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722924</v>
+        <v>723189</v>
       </c>
       <c r="R118" t="n">
-        <v>6380847</v>
+        <v>6380746</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14231,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876823</v>
+        <v>125876676</v>
       </c>
       <c r="B119" t="n">
-        <v>110443</v>
+        <v>98375</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14242,34 +14228,48 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723189</v>
+        <v>722956</v>
       </c>
       <c r="R119" t="n">
-        <v>6380746</v>
+        <v>6380853</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,59 +14333,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876676</v>
+        <v>125876819</v>
       </c>
       <c r="B120" t="n">
-        <v>98375</v>
+        <v>109176</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>722956</v>
+        <v>723194</v>
       </c>
       <c r="R120" t="n">
-        <v>6380853</v>
+        <v>6380741</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14449,45 +14435,59 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125876819</v>
+        <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>109176</v>
+        <v>98270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>723194</v>
+        <v>723022</v>
       </c>
       <c r="R121" t="n">
-        <v>6380741</v>
+        <v>6380869</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003997</v>
+        <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>98375</v>
+        <v>109176</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723483</v>
+        <v>723516</v>
       </c>
       <c r="R132" t="n">
-        <v>6380826</v>
+        <v>6380880</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,7 +15817,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126004010</v>
+        <v>126003997</v>
       </c>
       <c r="B133" t="n">
         <v>98375</v>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723469</v>
+        <v>723483</v>
       </c>
       <c r="R133" t="n">
-        <v>6380865</v>
+        <v>6380826</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004004</v>
+        <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98374</v>
+        <v>98375</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723496</v>
+        <v>723469</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126003999</v>
+        <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>109176</v>
+        <v>98374</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723516</v>
+        <v>723496</v>
       </c>
       <c r="R135" t="n">
-        <v>6380880</v>
+        <v>6380865</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876817</v>
+        <v>125876673</v>
       </c>
       <c r="B10" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,26 +1641,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723210</v>
+        <v>722989</v>
       </c>
       <c r="R10" t="n">
-        <v>6380786</v>
+        <v>6380861</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876749</v>
+        <v>125876780</v>
       </c>
       <c r="B11" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,26 +1757,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723321</v>
+        <v>723343</v>
       </c>
       <c r="R11" t="n">
-        <v>6380856</v>
+        <v>6380811</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876673</v>
+        <v>125876691</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>722989</v>
+        <v>723017</v>
       </c>
       <c r="R12" t="n">
-        <v>6380861</v>
+        <v>6380808</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876780</v>
+        <v>125876703</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723343</v>
+        <v>723050</v>
       </c>
       <c r="R13" t="n">
-        <v>6380811</v>
+        <v>6380829</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876691</v>
+        <v>125876817</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723017</v>
+        <v>723210</v>
       </c>
       <c r="R14" t="n">
-        <v>6380808</v>
+        <v>6380786</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125876703</v>
+        <v>125876749</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723050</v>
+        <v>723321</v>
       </c>
       <c r="R15" t="n">
-        <v>6380829</v>
+        <v>6380856</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125876678</v>
+        <v>125876696</v>
       </c>
       <c r="B16" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>722965</v>
+        <v>723042</v>
       </c>
       <c r="R16" t="n">
-        <v>6380842</v>
+        <v>6380816</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125876680</v>
+        <v>125876732</v>
       </c>
       <c r="B17" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>722962</v>
+        <v>723148</v>
       </c>
       <c r="R17" t="n">
-        <v>6380832</v>
+        <v>6380883</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876769</v>
+        <v>125876818</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723375</v>
+        <v>723210</v>
       </c>
       <c r="R18" t="n">
-        <v>6380878</v>
+        <v>6380786</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2643,6 +2643,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876670</v>
+        <v>125876794</v>
       </c>
       <c r="B19" t="n">
-        <v>98375</v>
+        <v>98244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,26 +2690,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723014</v>
+        <v>723296</v>
       </c>
       <c r="R19" t="n">
-        <v>6380862</v>
+        <v>6380797</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2790,10 +2795,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876774</v>
+        <v>125876678</v>
       </c>
       <c r="B20" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,26 +2806,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2839,13 +2844,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723342</v>
+        <v>722965</v>
       </c>
       <c r="R20" t="n">
-        <v>6380826</v>
+        <v>6380842</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2906,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876696</v>
+        <v>125876680</v>
       </c>
       <c r="B21" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,26 +2922,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2955,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723042</v>
+        <v>722962</v>
       </c>
       <c r="R21" t="n">
-        <v>6380816</v>
+        <v>6380832</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3022,7 +3027,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876672</v>
+        <v>125876670</v>
       </c>
       <c r="B22" t="n">
         <v>98375</v>
@@ -3052,7 +3057,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>722989</v>
+        <v>723014</v>
       </c>
       <c r="R22" t="n">
-        <v>6380861</v>
+        <v>6380862</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125876732</v>
+        <v>125876774</v>
       </c>
       <c r="B23" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,26 +3154,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3187,13 +3192,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723148</v>
+        <v>723342</v>
       </c>
       <c r="R23" t="n">
-        <v>6380883</v>
+        <v>6380826</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876818</v>
+        <v>125876672</v>
       </c>
       <c r="B24" t="n">
-        <v>98244</v>
+        <v>98375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,26 +3270,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3303,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723210</v>
+        <v>722989</v>
       </c>
       <c r="R24" t="n">
-        <v>6380786</v>
+        <v>6380861</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3339,11 +3344,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125876794</v>
+        <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98244</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219769</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723296</v>
+        <v>723375</v>
       </c>
       <c r="R25" t="n">
-        <v>6380797</v>
+        <v>6380878</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3491,37 +3491,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125876768</v>
+        <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,16 +3529,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723375</v>
+        <v>723038</v>
       </c>
       <c r="R26" t="n">
-        <v>6380878</v>
+        <v>6380861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3602,7 +3607,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876656</v>
+        <v>125876731</v>
       </c>
       <c r="B27" t="n">
         <v>98380</v>
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723038</v>
+        <v>723148</v>
       </c>
       <c r="R27" t="n">
-        <v>6380861</v>
+        <v>6380883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3718,37 +3723,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876815</v>
+        <v>125876708</v>
       </c>
       <c r="B28" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3756,16 +3761,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723209</v>
+        <v>723077</v>
       </c>
       <c r="R28" t="n">
-        <v>6380775</v>
+        <v>6380813</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3829,37 +3839,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876731</v>
+        <v>125876768</v>
       </c>
       <c r="B29" t="n">
-        <v>98380</v>
+        <v>107234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3867,21 +3877,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723148</v>
+        <v>723375</v>
       </c>
       <c r="R29" t="n">
-        <v>6380883</v>
+        <v>6380878</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3945,37 +3950,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876708</v>
+        <v>125876815</v>
       </c>
       <c r="B30" t="n">
-        <v>98380</v>
+        <v>107234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3983,21 +3988,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723077</v>
+        <v>723209</v>
       </c>
       <c r="R30" t="n">
-        <v>6380813</v>
+        <v>6380775</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125876712</v>
+        <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,26 +4072,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R31" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4146,6 +4146,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876806</v>
+        <v>125876712</v>
       </c>
       <c r="B32" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,26 +4193,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R32" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4262,11 +4267,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876778</v>
+        <v>125876682</v>
       </c>
       <c r="B34" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4468,13 +4468,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723355</v>
+        <v>722977</v>
       </c>
       <c r="R34" t="n">
-        <v>6380807</v>
+        <v>6380820</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876752</v>
+        <v>125876698</v>
       </c>
       <c r="B35" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,26 +4546,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723321</v>
+        <v>723026</v>
       </c>
       <c r="R35" t="n">
-        <v>6380856</v>
+        <v>6380845</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4651,37 +4651,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876813</v>
+        <v>125876778</v>
       </c>
       <c r="B36" t="n">
-        <v>107234</v>
+        <v>98244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4689,19 +4689,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723238</v>
+        <v>723355</v>
       </c>
       <c r="R36" t="n">
-        <v>6380770</v>
+        <v>6380807</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4762,10 +4767,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876682</v>
+        <v>125876752</v>
       </c>
       <c r="B37" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,26 +4778,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4811,10 +4816,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>722977</v>
+        <v>723321</v>
       </c>
       <c r="R37" t="n">
-        <v>6380820</v>
+        <v>6380856</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4878,37 +4883,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876698</v>
+        <v>125876813</v>
       </c>
       <c r="B38" t="n">
-        <v>98380</v>
+        <v>107234</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4916,21 +4921,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723026</v>
+        <v>723238</v>
       </c>
       <c r="R38" t="n">
-        <v>6380845</v>
+        <v>6380770</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876812</v>
+        <v>125876756</v>
       </c>
       <c r="B40" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,16 +5148,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723238</v>
+        <v>723344</v>
       </c>
       <c r="R40" t="n">
-        <v>6380770</v>
+        <v>6380853</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5221,7 +5226,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876671</v>
+        <v>125876812</v>
       </c>
       <c r="B41" t="n">
         <v>98380</v>
@@ -5251,7 +5256,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5259,21 +5264,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>722989</v>
+        <v>723238</v>
       </c>
       <c r="R41" t="n">
-        <v>6380861</v>
+        <v>6380770</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876762</v>
+        <v>125876671</v>
       </c>
       <c r="B42" t="n">
         <v>98380</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723370</v>
+        <v>722989</v>
       </c>
       <c r="R42" t="n">
-        <v>6380863</v>
+        <v>6380861</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876756</v>
+        <v>125876762</v>
       </c>
       <c r="B43" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723344</v>
+        <v>723370</v>
       </c>
       <c r="R43" t="n">
-        <v>6380853</v>
+        <v>6380863</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125876704</v>
+        <v>125876804</v>
       </c>
       <c r="B44" t="n">
-        <v>98380</v>
+        <v>98375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5580,26 +5580,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723050</v>
+        <v>723244</v>
       </c>
       <c r="R44" t="n">
-        <v>6380829</v>
+        <v>6380753</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5654,11 +5654,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5690,10 +5685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125876804</v>
+        <v>125876704</v>
       </c>
       <c r="B45" t="n">
-        <v>98375</v>
+        <v>98380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5701,26 +5696,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723244</v>
+        <v>723050</v>
       </c>
       <c r="R45" t="n">
-        <v>6380753</v>
+        <v>6380829</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5775,6 +5770,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876728</v>
+        <v>125876743</v>
       </c>
       <c r="B47" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,26 +5933,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723135</v>
+        <v>723221</v>
       </c>
       <c r="R47" t="n">
-        <v>6380877</v>
+        <v>6380864</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,37 +6038,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876803</v>
+        <v>125876814</v>
       </c>
       <c r="B48" t="n">
-        <v>107234</v>
+        <v>98244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6076,16 +6076,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723244</v>
+        <v>723228</v>
       </c>
       <c r="R48" t="n">
-        <v>6380753</v>
+        <v>6380782</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6149,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876733</v>
+        <v>125876705</v>
       </c>
       <c r="B49" t="n">
-        <v>98330</v>
+        <v>98244</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,26 +6165,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6189,7 +6194,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723172</v>
+        <v>723064</v>
       </c>
       <c r="R49" t="n">
-        <v>6380881</v>
+        <v>6380825</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6265,37 +6270,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876743</v>
+        <v>125876803</v>
       </c>
       <c r="B50" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6303,24 +6308,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723221</v>
+        <v>723244</v>
       </c>
       <c r="R50" t="n">
-        <v>6380864</v>
+        <v>6380753</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876814</v>
+        <v>125876728</v>
       </c>
       <c r="B51" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,26 +6392,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723228</v>
+        <v>723135</v>
       </c>
       <c r="R51" t="n">
-        <v>6380782</v>
+        <v>6380877</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876705</v>
+        <v>125876733</v>
       </c>
       <c r="B52" t="n">
-        <v>98244</v>
+        <v>98330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6508,26 +6508,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723064</v>
+        <v>723172</v>
       </c>
       <c r="R52" t="n">
-        <v>6380825</v>
+        <v>6380881</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,32 +6613,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876714</v>
+        <v>125876661</v>
       </c>
       <c r="B53" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723098</v>
+        <v>723022</v>
       </c>
       <c r="R53" t="n">
-        <v>6380819</v>
+        <v>6380875</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876681</v>
+        <v>125876723</v>
       </c>
       <c r="B54" t="n">
-        <v>98375</v>
+        <v>98244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>722977</v>
+        <v>723093</v>
       </c>
       <c r="R54" t="n">
-        <v>6380820</v>
+        <v>6380849</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876723</v>
+        <v>125876736</v>
       </c>
       <c r="B55" t="n">
         <v>98244</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723093</v>
+        <v>723172</v>
       </c>
       <c r="R55" t="n">
-        <v>6380849</v>
+        <v>6380881</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876736</v>
+        <v>125876686</v>
       </c>
       <c r="B56" t="n">
         <v>98244</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723172</v>
+        <v>723006</v>
       </c>
       <c r="R56" t="n">
-        <v>6380881</v>
+        <v>6380816</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876686</v>
+        <v>125876677</v>
       </c>
       <c r="B57" t="n">
         <v>98244</v>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723006</v>
+        <v>722956</v>
       </c>
       <c r="R57" t="n">
-        <v>6380816</v>
+        <v>6380853</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,7 +7193,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876677</v>
+        <v>125876739</v>
       </c>
       <c r="B58" t="n">
         <v>98244</v>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>722956</v>
+        <v>723173</v>
       </c>
       <c r="R58" t="n">
-        <v>6380853</v>
+        <v>6380850</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,7 +7309,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876739</v>
+        <v>125876738</v>
       </c>
       <c r="B59" t="n">
         <v>98244</v>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723173</v>
+        <v>723157</v>
       </c>
       <c r="R59" t="n">
-        <v>6380850</v>
+        <v>6380881</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876738</v>
+        <v>125876714</v>
       </c>
       <c r="B60" t="n">
-        <v>98244</v>
+        <v>98330</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7436,26 +7436,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723157</v>
+        <v>723098</v>
       </c>
       <c r="R60" t="n">
-        <v>6380881</v>
+        <v>6380819</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,37 +7541,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876761</v>
+        <v>125876681</v>
       </c>
       <c r="B61" t="n">
-        <v>107234</v>
+        <v>98375</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7579,16 +7579,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723360</v>
+        <v>722977</v>
       </c>
       <c r="R61" t="n">
-        <v>6380851</v>
+        <v>6380820</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7652,37 +7657,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876786</v>
+        <v>125876722</v>
       </c>
       <c r="B62" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7690,16 +7695,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723329</v>
+        <v>723061</v>
       </c>
       <c r="R62" t="n">
-        <v>6380785</v>
+        <v>6380859</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7763,7 +7773,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876722</v>
+        <v>125876826</v>
       </c>
       <c r="B63" t="n">
         <v>98380</v>
@@ -7793,7 +7803,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7812,10 +7822,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723061</v>
+        <v>723188</v>
       </c>
       <c r="R63" t="n">
-        <v>6380859</v>
+        <v>6380756</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7848,6 +7858,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7879,37 +7894,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876826</v>
+        <v>125876761</v>
       </c>
       <c r="B64" t="n">
-        <v>98380</v>
+        <v>107234</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7917,21 +7932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723188</v>
+        <v>723360</v>
       </c>
       <c r="R64" t="n">
-        <v>6380756</v>
+        <v>6380851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7964,11 +7974,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8000,10 +8005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876661</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>109176</v>
+        <v>107234</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8011,26 +8016,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8038,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723022</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380875</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125876784</v>
+        <v>125876785</v>
       </c>
       <c r="B66" t="n">
-        <v>98375</v>
+        <v>98244</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8127,26 +8127,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8232,7 +8232,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125876665</v>
+        <v>125876784</v>
       </c>
       <c r="B67" t="n">
         <v>98375</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723022</v>
+        <v>723343</v>
       </c>
       <c r="R67" t="n">
-        <v>6380875</v>
+        <v>6380788</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876785</v>
+        <v>125876695</v>
       </c>
       <c r="B68" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,26 +8359,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723343</v>
+        <v>723040</v>
       </c>
       <c r="R68" t="n">
-        <v>6380788</v>
+        <v>6380808</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,7 +8464,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876695</v>
+        <v>125876793</v>
       </c>
       <c r="B69" t="n">
         <v>98380</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723040</v>
+        <v>723296</v>
       </c>
       <c r="R69" t="n">
-        <v>6380808</v>
+        <v>6380797</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876793</v>
+        <v>125876665</v>
       </c>
       <c r="B70" t="n">
-        <v>98380</v>
+        <v>98375</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723296</v>
+        <v>723022</v>
       </c>
       <c r="R70" t="n">
-        <v>6380797</v>
+        <v>6380875</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876716</v>
+        <v>125876910</v>
       </c>
       <c r="B73" t="n">
-        <v>98380</v>
+        <v>95955</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8939,36 +8939,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8977,13 +8972,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723080</v>
+        <v>723027</v>
       </c>
       <c r="R73" t="n">
-        <v>6380837</v>
+        <v>6380801</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9015,11 +9010,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9028,11 +9018,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9049,59 +9034,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876828</v>
+        <v>125876757</v>
       </c>
       <c r="B74" t="n">
-        <v>98380</v>
+        <v>103805</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219864</v>
+        <v>220164</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723173</v>
+        <v>723360</v>
       </c>
       <c r="R74" t="n">
-        <v>6380765</v>
+        <v>6380851</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9147,7 +9118,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9165,10 +9136,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876757</v>
+        <v>125876921</v>
       </c>
       <c r="B75" t="n">
-        <v>103805</v>
+        <v>5492</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9176,21 +9147,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220164</v>
+        <v>101410</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9200,13 +9171,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723360</v>
+        <v>723364</v>
       </c>
       <c r="R75" t="n">
-        <v>6380851</v>
+        <v>6380813</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9238,6 +9209,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9246,11 +9222,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9267,10 +9238,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876810</v>
+        <v>125876741</v>
       </c>
       <c r="B76" t="n">
-        <v>98270</v>
+        <v>98244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9278,26 +9249,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>219769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9307,7 +9278,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9316,13 +9287,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723234</v>
+        <v>723189</v>
       </c>
       <c r="R76" t="n">
-        <v>6380772</v>
+        <v>6380869</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9383,48 +9354,62 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876921</v>
+        <v>125876658</v>
       </c>
       <c r="B77" t="n">
-        <v>5492</v>
+        <v>98244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101410</v>
+        <v>219769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723364</v>
+        <v>723022</v>
       </c>
       <c r="R77" t="n">
-        <v>6380813</v>
+        <v>6380859</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9456,11 +9441,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9469,6 +9449,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9485,10 +9470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876910</v>
+        <v>125876717</v>
       </c>
       <c r="B78" t="n">
-        <v>95955</v>
+        <v>98244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9496,31 +9481,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2180</v>
+        <v>219769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9529,13 +9519,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723027</v>
+        <v>723080</v>
       </c>
       <c r="R78" t="n">
-        <v>6380801</v>
+        <v>6380837</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9567,6 +9557,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9575,6 +9570,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9591,7 +9591,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876741</v>
+        <v>125876776</v>
       </c>
       <c r="B79" t="n">
         <v>98244</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9640,13 +9640,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723189</v>
+        <v>723342</v>
       </c>
       <c r="R79" t="n">
-        <v>6380869</v>
+        <v>6380826</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876658</v>
+        <v>125876729</v>
       </c>
       <c r="B80" t="n">
         <v>98244</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723022</v>
+        <v>723135</v>
       </c>
       <c r="R80" t="n">
-        <v>6380859</v>
+        <v>6380877</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9823,7 +9823,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876717</v>
+        <v>125876715</v>
       </c>
       <c r="B81" t="n">
         <v>98244</v>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723080</v>
+        <v>723098</v>
       </c>
       <c r="R81" t="n">
-        <v>6380837</v>
+        <v>6380819</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9908,11 +9908,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9944,10 +9939,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876776</v>
+        <v>125876716</v>
       </c>
       <c r="B82" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9955,26 +9950,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9993,13 +9988,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723342</v>
+        <v>723080</v>
       </c>
       <c r="R82" t="n">
-        <v>6380826</v>
+        <v>6380837</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10029,6 +10024,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10060,10 +10060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876729</v>
+        <v>125876828</v>
       </c>
       <c r="B83" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10071,26 +10071,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723135</v>
+        <v>723173</v>
       </c>
       <c r="R83" t="n">
-        <v>6380877</v>
+        <v>6380765</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876715</v>
+        <v>125876810</v>
       </c>
       <c r="B84" t="n">
-        <v>98244</v>
+        <v>98270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10187,26 +10187,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723098</v>
+        <v>723234</v>
       </c>
       <c r="R84" t="n">
-        <v>6380819</v>
+        <v>6380772</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10640,10 +10640,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876666</v>
+        <v>125876725</v>
       </c>
       <c r="B88" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,21 +10651,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723022</v>
+        <v>723122</v>
       </c>
       <c r="R88" t="n">
-        <v>6380875</v>
+        <v>6380858</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876725</v>
+        <v>125876727</v>
       </c>
       <c r="B89" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10767,26 +10767,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10805,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723122</v>
+        <v>723123</v>
       </c>
       <c r="R89" t="n">
-        <v>6380858</v>
+        <v>6380868</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876727</v>
+        <v>125876754</v>
       </c>
       <c r="B90" t="n">
         <v>98380</v>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10921,13 +10921,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723123</v>
+        <v>723344</v>
       </c>
       <c r="R90" t="n">
-        <v>6380868</v>
+        <v>6380853</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10957,6 +10957,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10988,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876754</v>
+        <v>125876666</v>
       </c>
       <c r="B91" t="n">
-        <v>98380</v>
+        <v>98374</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10999,26 +11004,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11037,13 +11042,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723344</v>
+        <v>723022</v>
       </c>
       <c r="R91" t="n">
-        <v>6380853</v>
+        <v>6380875</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11073,11 +11078,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11573,10 +11573,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876669</v>
+        <v>125876820</v>
       </c>
       <c r="B96" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11584,26 +11584,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723014</v>
+        <v>723194</v>
       </c>
       <c r="R96" t="n">
-        <v>6380862</v>
+        <v>6380741</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876820</v>
+        <v>125876772</v>
       </c>
       <c r="B97" t="n">
         <v>98244</v>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11738,10 +11738,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723194</v>
+        <v>723364</v>
       </c>
       <c r="R97" t="n">
-        <v>6380741</v>
+        <v>6380813</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11774,6 +11774,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11805,7 +11810,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876772</v>
+        <v>125876697</v>
       </c>
       <c r="B98" t="n">
         <v>98244</v>
@@ -11835,7 +11840,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11854,10 +11859,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723364</v>
+        <v>723031</v>
       </c>
       <c r="R98" t="n">
-        <v>6380813</v>
+        <v>6380827</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11890,11 +11895,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11926,7 +11926,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876697</v>
+        <v>125876788</v>
       </c>
       <c r="B99" t="n">
         <v>98244</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723031</v>
+        <v>723320</v>
       </c>
       <c r="R99" t="n">
-        <v>6380827</v>
+        <v>6380799</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12042,10 +12042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876788</v>
+        <v>125876669</v>
       </c>
       <c r="B100" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12053,26 +12053,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723320</v>
+        <v>723014</v>
       </c>
       <c r="R100" t="n">
-        <v>6380799</v>
+        <v>6380862</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12158,32 +12158,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876945</v>
+        <v>125876719</v>
       </c>
       <c r="B101" t="n">
-        <v>57653</v>
+        <v>98380</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12191,24 +12191,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R101" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12240,11 +12245,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12253,6 +12253,11 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12380,32 +12385,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876719</v>
+        <v>125876945</v>
       </c>
       <c r="B103" t="n">
-        <v>98380</v>
+        <v>57653</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219864</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12413,29 +12418,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723068</v>
+        <v>723296</v>
       </c>
       <c r="R103" t="n">
-        <v>6380835</v>
+        <v>6380797</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12467,6 +12467,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12475,11 +12480,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876702</v>
+        <v>125876777</v>
       </c>
       <c r="B108" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723038</v>
+        <v>723355</v>
       </c>
       <c r="R108" t="n">
-        <v>6380832</v>
+        <v>6380807</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876755</v>
+        <v>125876706</v>
       </c>
       <c r="B109" t="n">
-        <v>98375</v>
+        <v>98380</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723344</v>
+        <v>723064</v>
       </c>
       <c r="R109" t="n">
-        <v>6380853</v>
+        <v>6380825</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876777</v>
+        <v>125876702</v>
       </c>
       <c r="B110" t="n">
-        <v>98380</v>
+        <v>98374</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,13 +13241,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723355</v>
+        <v>723038</v>
       </c>
       <c r="R110" t="n">
-        <v>6380807</v>
+        <v>6380832</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876706</v>
+        <v>125876755</v>
       </c>
       <c r="B111" t="n">
-        <v>98380</v>
+        <v>98375</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723064</v>
+        <v>723344</v>
       </c>
       <c r="R111" t="n">
-        <v>6380825</v>
+        <v>6380853</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13424,37 +13424,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876811</v>
+        <v>125876664</v>
       </c>
       <c r="B112" t="n">
-        <v>107234</v>
+        <v>98244</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13462,16 +13462,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723234</v>
+        <v>723022</v>
       </c>
       <c r="R112" t="n">
-        <v>6380772</v>
+        <v>6380875</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13767,37 +13772,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876664</v>
+        <v>125876811</v>
       </c>
       <c r="B115" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13805,21 +13810,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723022</v>
+        <v>723234</v>
       </c>
       <c r="R115" t="n">
-        <v>6380875</v>
+        <v>6380772</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876709</v>
+        <v>125876676</v>
       </c>
       <c r="B116" t="n">
-        <v>98380</v>
+        <v>98375</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723074</v>
+        <v>722956</v>
       </c>
       <c r="R116" t="n">
-        <v>6380823</v>
+        <v>6380853</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876674</v>
+        <v>125876709</v>
       </c>
       <c r="B117" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14010,26 +14010,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>722924</v>
+        <v>723074</v>
       </c>
       <c r="R117" t="n">
-        <v>6380847</v>
+        <v>6380823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14115,27 +14115,27 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876823</v>
+        <v>125876819</v>
       </c>
       <c r="B118" t="n">
-        <v>110443</v>
+        <v>109176</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219711</v>
+        <v>220299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -14150,10 +14150,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>723189</v>
+        <v>723194</v>
       </c>
       <c r="R118" t="n">
-        <v>6380746</v>
+        <v>6380741</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876676</v>
+        <v>125876674</v>
       </c>
       <c r="B119" t="n">
-        <v>98375</v>
+        <v>98244</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14228,26 +14228,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>722956</v>
+        <v>722924</v>
       </c>
       <c r="R119" t="n">
-        <v>6380853</v>
+        <v>6380847</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,27 +14333,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876819</v>
+        <v>125876823</v>
       </c>
       <c r="B120" t="n">
-        <v>109176</v>
+        <v>110443</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723194</v>
+        <v>723189</v>
       </c>
       <c r="R120" t="n">
-        <v>6380741</v>
+        <v>6380746</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14551,32 +14551,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876667</v>
+        <v>125876710</v>
       </c>
       <c r="B122" t="n">
-        <v>109176</v>
+        <v>98386</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -14589,21 +14589,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723014</v>
+        <v>723098</v>
       </c>
       <c r="R122" t="n">
-        <v>6380862</v>
+        <v>6380819</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14667,27 +14662,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876718</v>
+        <v>125876767</v>
       </c>
       <c r="B123" t="n">
-        <v>109176</v>
+        <v>98380</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14697,7 +14692,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14716,10 +14711,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723068</v>
+        <v>723375</v>
       </c>
       <c r="R123" t="n">
-        <v>6380835</v>
+        <v>6380878</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14783,10 +14778,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876690</v>
+        <v>125876766</v>
       </c>
       <c r="B124" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14794,26 +14789,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14832,10 +14827,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723004</v>
+        <v>723369</v>
       </c>
       <c r="R124" t="n">
-        <v>6380791</v>
+        <v>6380880</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14899,37 +14894,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876763</v>
+        <v>125876792</v>
       </c>
       <c r="B125" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14937,21 +14932,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723370</v>
+        <v>723296</v>
       </c>
       <c r="R125" t="n">
-        <v>6380863</v>
+        <v>6380797</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15015,32 +15005,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876710</v>
+        <v>125876667</v>
       </c>
       <c r="B126" t="n">
-        <v>98386</v>
+        <v>109176</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -15053,16 +15043,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723098</v>
+        <v>723014</v>
       </c>
       <c r="R126" t="n">
-        <v>6380819</v>
+        <v>6380862</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15126,10 +15121,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876792</v>
+        <v>125876718</v>
       </c>
       <c r="B127" t="n">
-        <v>107234</v>
+        <v>109176</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15137,26 +15132,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15164,16 +15159,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723296</v>
+        <v>723068</v>
       </c>
       <c r="R127" t="n">
-        <v>6380797</v>
+        <v>6380835</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876767</v>
+        <v>125876690</v>
       </c>
       <c r="B128" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15248,21 +15248,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723375</v>
+        <v>723004</v>
       </c>
       <c r="R128" t="n">
-        <v>6380878</v>
+        <v>6380791</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,10 +15353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876766</v>
+        <v>125876763</v>
       </c>
       <c r="B129" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15364,26 +15364,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723369</v>
+        <v>723370</v>
       </c>
       <c r="R129" t="n">
-        <v>6380880</v>
+        <v>6380863</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003999</v>
+        <v>126003997</v>
       </c>
       <c r="B132" t="n">
-        <v>109176</v>
+        <v>98375</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723516</v>
+        <v>723483</v>
       </c>
       <c r="R132" t="n">
-        <v>6380880</v>
+        <v>6380826</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,7 +15817,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126003997</v>
+        <v>126004010</v>
       </c>
       <c r="B133" t="n">
         <v>98375</v>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723483</v>
+        <v>723469</v>
       </c>
       <c r="R133" t="n">
-        <v>6380826</v>
+        <v>6380865</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004010</v>
+        <v>126004004</v>
       </c>
       <c r="B134" t="n">
-        <v>98375</v>
+        <v>98374</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723469</v>
+        <v>723496</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126004004</v>
+        <v>126003999</v>
       </c>
       <c r="B135" t="n">
-        <v>98374</v>
+        <v>109176</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723496</v>
+        <v>723516</v>
       </c>
       <c r="R135" t="n">
-        <v>6380865</v>
+        <v>6380880</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16281,10 +16281,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126003974</v>
+        <v>126003993</v>
       </c>
       <c r="B137" t="n">
-        <v>98380</v>
+        <v>98375</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16292,26 +16292,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16330,10 +16330,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>723349</v>
+        <v>723470</v>
       </c>
       <c r="R137" t="n">
-        <v>6380791</v>
+        <v>6380822</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16397,7 +16397,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126003993</v>
+        <v>126003995</v>
       </c>
       <c r="B138" t="n">
         <v>98375</v>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>723470</v>
       </c>
       <c r="R138" t="n">
-        <v>6380822</v>
+        <v>6380826</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16513,10 +16513,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126003995</v>
+        <v>126003978</v>
       </c>
       <c r="B139" t="n">
-        <v>98375</v>
+        <v>98244</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16524,26 +16524,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16562,10 +16562,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>723470</v>
+        <v>723349</v>
       </c>
       <c r="R139" t="n">
-        <v>6380826</v>
+        <v>6380791</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16629,10 +16629,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126003978</v>
+        <v>126003974</v>
       </c>
       <c r="B140" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16640,26 +16640,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17200,10 +17200,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126003998</v>
+        <v>126003971</v>
       </c>
       <c r="B145" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17211,26 +17211,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>723508</v>
+        <v>723257</v>
       </c>
       <c r="R145" t="n">
-        <v>6380857</v>
+        <v>6380842</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17316,10 +17316,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126003971</v>
+        <v>126003998</v>
       </c>
       <c r="B146" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17327,26 +17327,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>723257</v>
+        <v>723508</v>
       </c>
       <c r="R146" t="n">
-        <v>6380842</v>
+        <v>6380857</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876756</v>
+        <v>125876812</v>
       </c>
       <c r="B40" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,21 +5148,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723344</v>
+        <v>723238</v>
       </c>
       <c r="R40" t="n">
-        <v>6380853</v>
+        <v>6380770</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5226,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125876812</v>
+        <v>125876671</v>
       </c>
       <c r="B41" t="n">
         <v>98380</v>
@@ -5256,7 +5251,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5264,16 +5259,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723238</v>
+        <v>722989</v>
       </c>
       <c r="R41" t="n">
-        <v>6380770</v>
+        <v>6380861</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125876671</v>
+        <v>125876762</v>
       </c>
       <c r="B42" t="n">
         <v>98380</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>722989</v>
+        <v>723370</v>
       </c>
       <c r="R42" t="n">
-        <v>6380861</v>
+        <v>6380863</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876762</v>
+        <v>125876756</v>
       </c>
       <c r="B43" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5464,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723370</v>
+        <v>723344</v>
       </c>
       <c r="R43" t="n">
-        <v>6380863</v>
+        <v>6380853</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6270,32 +6270,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876803</v>
+        <v>125876728</v>
       </c>
       <c r="B50" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6308,19 +6308,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723244</v>
+        <v>723135</v>
       </c>
       <c r="R50" t="n">
-        <v>6380753</v>
+        <v>6380877</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6381,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876728</v>
+        <v>125876733</v>
       </c>
       <c r="B51" t="n">
-        <v>98380</v>
+        <v>98330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,21 +6397,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6421,7 +6426,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6430,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723135</v>
+        <v>723172</v>
       </c>
       <c r="R51" t="n">
-        <v>6380877</v>
+        <v>6380881</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,32 +6502,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125876733</v>
+        <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>98330</v>
+        <v>107234</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6535,21 +6540,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723172</v>
+        <v>723244</v>
       </c>
       <c r="R52" t="n">
-        <v>6380881</v>
+        <v>6380753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6613,37 +6613,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876661</v>
+        <v>125876723</v>
       </c>
       <c r="B53" t="n">
-        <v>109176</v>
+        <v>98244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723022</v>
+        <v>723093</v>
       </c>
       <c r="R53" t="n">
-        <v>6380875</v>
+        <v>6380849</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876723</v>
+        <v>125876736</v>
       </c>
       <c r="B54" t="n">
         <v>98244</v>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723093</v>
+        <v>723172</v>
       </c>
       <c r="R54" t="n">
-        <v>6380849</v>
+        <v>6380881</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876736</v>
+        <v>125876686</v>
       </c>
       <c r="B55" t="n">
         <v>98244</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723172</v>
+        <v>723006</v>
       </c>
       <c r="R55" t="n">
-        <v>6380881</v>
+        <v>6380816</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876686</v>
+        <v>125876677</v>
       </c>
       <c r="B56" t="n">
         <v>98244</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723006</v>
+        <v>722956</v>
       </c>
       <c r="R56" t="n">
-        <v>6380816</v>
+        <v>6380853</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876677</v>
+        <v>125876739</v>
       </c>
       <c r="B57" t="n">
         <v>98244</v>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>722956</v>
+        <v>723173</v>
       </c>
       <c r="R57" t="n">
-        <v>6380853</v>
+        <v>6380850</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,7 +7193,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876739</v>
+        <v>125876738</v>
       </c>
       <c r="B58" t="n">
         <v>98244</v>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723173</v>
+        <v>723157</v>
       </c>
       <c r="R58" t="n">
-        <v>6380850</v>
+        <v>6380881</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876738</v>
+        <v>125876714</v>
       </c>
       <c r="B59" t="n">
-        <v>98244</v>
+        <v>98330</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7320,26 +7320,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723157</v>
+        <v>723098</v>
       </c>
       <c r="R59" t="n">
-        <v>6380881</v>
+        <v>6380819</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876714</v>
+        <v>125876681</v>
       </c>
       <c r="B60" t="n">
-        <v>98330</v>
+        <v>98375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7436,26 +7436,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723098</v>
+        <v>722977</v>
       </c>
       <c r="R60" t="n">
-        <v>6380819</v>
+        <v>6380820</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876681</v>
+        <v>125876722</v>
       </c>
       <c r="B61" t="n">
-        <v>98375</v>
+        <v>98380</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7552,26 +7552,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>722977</v>
+        <v>723061</v>
       </c>
       <c r="R61" t="n">
-        <v>6380820</v>
+        <v>6380859</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876722</v>
+        <v>125876826</v>
       </c>
       <c r="B62" t="n">
         <v>98380</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723061</v>
+        <v>723188</v>
       </c>
       <c r="R62" t="n">
-        <v>6380859</v>
+        <v>6380756</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7742,6 +7742,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7773,37 +7778,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876826</v>
+        <v>125876761</v>
       </c>
       <c r="B63" t="n">
-        <v>98380</v>
+        <v>107234</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7811,21 +7816,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723188</v>
+        <v>723360</v>
       </c>
       <c r="R63" t="n">
-        <v>6380756</v>
+        <v>6380851</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7858,11 +7858,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7894,7 +7889,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876761</v>
+        <v>125876786</v>
       </c>
       <c r="B64" t="n">
         <v>107234</v>
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723360</v>
+        <v>723329</v>
       </c>
       <c r="R64" t="n">
-        <v>6380851</v>
+        <v>6380785</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8005,10 +8000,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876786</v>
+        <v>125876661</v>
       </c>
       <c r="B65" t="n">
-        <v>107234</v>
+        <v>109176</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8016,26 +8011,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8043,16 +8038,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723329</v>
+        <v>723022</v>
       </c>
       <c r="R65" t="n">
-        <v>6380785</v>
+        <v>6380875</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -9034,45 +9034,59 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876757</v>
+        <v>125876741</v>
       </c>
       <c r="B74" t="n">
-        <v>103805</v>
+        <v>98244</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723360</v>
+        <v>723189</v>
       </c>
       <c r="R74" t="n">
-        <v>6380851</v>
+        <v>6380869</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9136,48 +9150,62 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876921</v>
+        <v>125876658</v>
       </c>
       <c r="B75" t="n">
-        <v>5492</v>
+        <v>98244</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>101410</v>
+        <v>219769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723364</v>
+        <v>723022</v>
       </c>
       <c r="R75" t="n">
-        <v>6380813</v>
+        <v>6380859</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9209,11 +9237,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Angripen tall.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9222,6 +9245,11 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9238,7 +9266,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876741</v>
+        <v>125876717</v>
       </c>
       <c r="B76" t="n">
         <v>98244</v>
@@ -9268,7 +9296,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9287,10 +9315,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723189</v>
+        <v>723080</v>
       </c>
       <c r="R76" t="n">
-        <v>6380869</v>
+        <v>6380837</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9323,6 +9351,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9354,7 +9387,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876658</v>
+        <v>125876776</v>
       </c>
       <c r="B77" t="n">
         <v>98244</v>
@@ -9384,7 +9417,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9403,13 +9436,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723022</v>
+        <v>723342</v>
       </c>
       <c r="R77" t="n">
-        <v>6380859</v>
+        <v>6380826</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9470,7 +9503,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876717</v>
+        <v>125876729</v>
       </c>
       <c r="B78" t="n">
         <v>98244</v>
@@ -9519,10 +9552,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723080</v>
+        <v>723135</v>
       </c>
       <c r="R78" t="n">
-        <v>6380837</v>
+        <v>6380877</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9555,11 +9588,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9591,7 +9619,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876776</v>
+        <v>125876715</v>
       </c>
       <c r="B79" t="n">
         <v>98244</v>
@@ -9621,7 +9649,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9640,13 +9668,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723342</v>
+        <v>723098</v>
       </c>
       <c r="R79" t="n">
-        <v>6380826</v>
+        <v>6380819</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9707,10 +9735,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876729</v>
+        <v>125876716</v>
       </c>
       <c r="B80" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,26 +9746,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9756,13 +9784,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723135</v>
+        <v>723080</v>
       </c>
       <c r="R80" t="n">
-        <v>6380877</v>
+        <v>6380837</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9792,6 +9820,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9823,10 +9856,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876715</v>
+        <v>125876828</v>
       </c>
       <c r="B81" t="n">
-        <v>98244</v>
+        <v>98380</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9834,26 +9867,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9868,14 +9901,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723098</v>
+        <v>723173</v>
       </c>
       <c r="R81" t="n">
-        <v>6380819</v>
+        <v>6380765</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9921,7 +9954,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9939,62 +9972,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876716</v>
+        <v>125876757</v>
       </c>
       <c r="B82" t="n">
-        <v>98380</v>
+        <v>103805</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219864</v>
+        <v>220164</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723080</v>
+        <v>723360</v>
       </c>
       <c r="R82" t="n">
-        <v>6380837</v>
+        <v>6380851</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10024,11 +10043,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10060,10 +10074,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876828</v>
+        <v>125876810</v>
       </c>
       <c r="B83" t="n">
-        <v>98380</v>
+        <v>98270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10071,26 +10085,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10100,22 +10114,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723173</v>
+        <v>723234</v>
       </c>
       <c r="R83" t="n">
-        <v>6380765</v>
+        <v>6380772</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10158,7 +10172,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10176,62 +10190,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876810</v>
+        <v>125876921</v>
       </c>
       <c r="B84" t="n">
-        <v>98270</v>
+        <v>5492</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>101410</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723234</v>
+        <v>723364</v>
       </c>
       <c r="R84" t="n">
-        <v>6380772</v>
+        <v>6380813</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10263,6 +10263,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10271,11 +10276,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876781</v>
+        <v>125876744</v>
       </c>
       <c r="B92" t="n">
-        <v>98270</v>
+        <v>98380</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723343</v>
+        <v>723252</v>
       </c>
       <c r="R92" t="n">
-        <v>6380811</v>
+        <v>6380854</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11341,10 +11341,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125876744</v>
+        <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98380</v>
+        <v>98270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11352,21 +11352,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219864</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11390,13 +11390,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723252</v>
+        <v>723343</v>
       </c>
       <c r="R94" t="n">
-        <v>6380854</v>
+        <v>6380811</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11689,59 +11689,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876772</v>
+        <v>125876945</v>
       </c>
       <c r="B97" t="n">
-        <v>98244</v>
+        <v>57653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723364</v>
+        <v>723296</v>
       </c>
       <c r="R97" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11778,7 +11773,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fler plantor mot S-SO.</t>
+          <t>Födosökshack i murken tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11789,11 +11784,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11810,7 +11800,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876697</v>
+        <v>125876772</v>
       </c>
       <c r="B98" t="n">
         <v>98244</v>
@@ -11840,7 +11830,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11859,10 +11849,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723031</v>
+        <v>723364</v>
       </c>
       <c r="R98" t="n">
-        <v>6380827</v>
+        <v>6380813</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11895,6 +11885,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11926,7 +11921,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876788</v>
+        <v>125876697</v>
       </c>
       <c r="B99" t="n">
         <v>98244</v>
@@ -11956,7 +11951,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723320</v>
+        <v>723031</v>
       </c>
       <c r="R99" t="n">
-        <v>6380799</v>
+        <v>6380827</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12042,10 +12037,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876669</v>
+        <v>125876788</v>
       </c>
       <c r="B100" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12053,26 +12048,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12091,10 +12086,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723014</v>
+        <v>723320</v>
       </c>
       <c r="R100" t="n">
-        <v>6380862</v>
+        <v>6380799</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12158,10 +12153,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876719</v>
+        <v>125876669</v>
       </c>
       <c r="B101" t="n">
-        <v>98380</v>
+        <v>98374</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12169,21 +12164,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12207,13 +12202,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723068</v>
+        <v>723014</v>
       </c>
       <c r="R101" t="n">
-        <v>6380835</v>
+        <v>6380862</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12274,37 +12269,37 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B102" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12312,19 +12307,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R102" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12385,10 +12385,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876945</v>
+        <v>125876740</v>
       </c>
       <c r="B103" t="n">
-        <v>57653</v>
+        <v>107234</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12396,43 +12396,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723296</v>
+        <v>723183</v>
       </c>
       <c r="R103" t="n">
-        <v>6380797</v>
+        <v>6380860</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12467,11 +12467,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +12475,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13424,10 +13424,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125876664</v>
+        <v>125876765</v>
       </c>
       <c r="B112" t="n">
-        <v>98244</v>
+        <v>98374</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,21 +13435,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>723022</v>
+        <v>723369</v>
       </c>
       <c r="R112" t="n">
-        <v>6380875</v>
+        <v>6380880</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13540,37 +13540,37 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125876782</v>
+        <v>125876811</v>
       </c>
       <c r="B113" t="n">
-        <v>98244</v>
+        <v>107234</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13578,21 +13578,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>723338</v>
+        <v>723234</v>
       </c>
       <c r="R113" t="n">
-        <v>6380799</v>
+        <v>6380772</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13656,10 +13651,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125876765</v>
+        <v>125876664</v>
       </c>
       <c r="B114" t="n">
-        <v>98374</v>
+        <v>98244</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13667,21 +13662,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13705,10 +13700,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>723369</v>
+        <v>723022</v>
       </c>
       <c r="R114" t="n">
-        <v>6380880</v>
+        <v>6380875</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13772,37 +13767,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125876811</v>
+        <v>125876782</v>
       </c>
       <c r="B115" t="n">
-        <v>107234</v>
+        <v>98244</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220079</v>
+        <v>219769</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13810,16 +13805,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>723234</v>
+        <v>723338</v>
       </c>
       <c r="R115" t="n">
-        <v>6380772</v>
+        <v>6380799</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876676</v>
+        <v>125876709</v>
       </c>
       <c r="B116" t="n">
-        <v>98375</v>
+        <v>98380</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>722956</v>
+        <v>723074</v>
       </c>
       <c r="R116" t="n">
-        <v>6380853</v>
+        <v>6380823</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,27 +13999,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876709</v>
+        <v>125876819</v>
       </c>
       <c r="B117" t="n">
-        <v>98380</v>
+        <v>109176</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14027,31 +14027,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723074</v>
+        <v>723194</v>
       </c>
       <c r="R117" t="n">
-        <v>6380823</v>
+        <v>6380741</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14115,45 +14101,59 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876819</v>
+        <v>125876674</v>
       </c>
       <c r="B118" t="n">
-        <v>109176</v>
+        <v>98244</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220299</v>
+        <v>219769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>723194</v>
+        <v>722924</v>
       </c>
       <c r="R118" t="n">
-        <v>6380741</v>
+        <v>6380847</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876674</v>
+        <v>125876823</v>
       </c>
       <c r="B119" t="n">
-        <v>98244</v>
+        <v>110443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14228,48 +14228,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>722924</v>
+        <v>723189</v>
       </c>
       <c r="R119" t="n">
-        <v>6380847</v>
+        <v>6380746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14333,10 +14319,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876823</v>
+        <v>125876676</v>
       </c>
       <c r="B120" t="n">
-        <v>110443</v>
+        <v>98375</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14344,34 +14330,48 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>723189</v>
+        <v>722956</v>
       </c>
       <c r="R120" t="n">
-        <v>6380746</v>
+        <v>6380853</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14551,10 +14551,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125876710</v>
+        <v>125876690</v>
       </c>
       <c r="B122" t="n">
-        <v>98386</v>
+        <v>98244</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14562,26 +14562,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>219769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14589,16 +14589,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>723098</v>
+        <v>723004</v>
       </c>
       <c r="R122" t="n">
-        <v>6380819</v>
+        <v>6380791</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14662,10 +14667,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125876767</v>
+        <v>125876763</v>
       </c>
       <c r="B123" t="n">
-        <v>98380</v>
+        <v>98244</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14673,26 +14678,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14711,10 +14716,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>723375</v>
+        <v>723370</v>
       </c>
       <c r="R123" t="n">
-        <v>6380878</v>
+        <v>6380863</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14778,10 +14783,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125876766</v>
+        <v>125876710</v>
       </c>
       <c r="B124" t="n">
-        <v>98380</v>
+        <v>98386</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14789,26 +14794,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219864</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14816,21 +14821,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>723369</v>
+        <v>723098</v>
       </c>
       <c r="R124" t="n">
-        <v>6380880</v>
+        <v>6380819</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14894,37 +14894,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876792</v>
+        <v>125876767</v>
       </c>
       <c r="B125" t="n">
-        <v>107234</v>
+        <v>98380</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14932,16 +14932,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723296</v>
+        <v>723375</v>
       </c>
       <c r="R125" t="n">
-        <v>6380797</v>
+        <v>6380878</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15005,27 +15010,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876667</v>
+        <v>125876766</v>
       </c>
       <c r="B126" t="n">
-        <v>109176</v>
+        <v>98380</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -15035,7 +15040,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15054,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723014</v>
+        <v>723369</v>
       </c>
       <c r="R126" t="n">
-        <v>6380862</v>
+        <v>6380880</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15121,10 +15126,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125876718</v>
+        <v>125876792</v>
       </c>
       <c r="B127" t="n">
-        <v>109176</v>
+        <v>107234</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15132,26 +15137,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15159,21 +15164,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>723068</v>
+        <v>723296</v>
       </c>
       <c r="R127" t="n">
-        <v>6380835</v>
+        <v>6380797</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15237,37 +15237,37 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125876690</v>
+        <v>125876667</v>
       </c>
       <c r="B128" t="n">
-        <v>98244</v>
+        <v>109176</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>723004</v>
+        <v>723014</v>
       </c>
       <c r="R128" t="n">
-        <v>6380791</v>
+        <v>6380862</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15353,32 +15353,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125876763</v>
+        <v>125876718</v>
       </c>
       <c r="B129" t="n">
-        <v>98244</v>
+        <v>109176</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219769</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>723370</v>
+        <v>723068</v>
       </c>
       <c r="R129" t="n">
-        <v>6380863</v>
+        <v>6380835</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -18235,32 +18235,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126003990</v>
+        <v>126004002</v>
       </c>
       <c r="B154" t="n">
-        <v>99027</v>
+        <v>98375</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222322</v>
+        <v>219847</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18284,10 +18284,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>723426</v>
+        <v>723516</v>
       </c>
       <c r="R154" t="n">
-        <v>6380811</v>
+        <v>6380880</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18322,11 +18322,6 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Mindre agmyr 10 x 10 m även mot N.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18338,7 +18333,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Agmyrkant.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18356,7 +18351,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126004002</v>
+        <v>126003996</v>
       </c>
       <c r="B155" t="n">
         <v>98375</v>
@@ -18386,7 +18381,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18405,10 +18400,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>723516</v>
+        <v>723479</v>
       </c>
       <c r="R155" t="n">
-        <v>6380880</v>
+        <v>6380833</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18472,7 +18467,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126003996</v>
+        <v>126004014</v>
       </c>
       <c r="B156" t="n">
         <v>98375</v>
@@ -18502,7 +18497,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18521,10 +18516,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>723479</v>
+        <v>723461</v>
       </c>
       <c r="R156" t="n">
-        <v>6380833</v>
+        <v>6380878</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18588,47 +18583,47 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126004014</v>
+        <v>126003990</v>
       </c>
       <c r="B157" t="n">
-        <v>98375</v>
+        <v>99027</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -18637,10 +18632,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>723461</v>
+        <v>723426</v>
       </c>
       <c r="R157" t="n">
-        <v>6380878</v>
+        <v>6380811</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18675,6 +18670,11 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Mindre agmyr 10 x 10 m även mot N.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Agmyrkant.</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>

--- a/artfynd/A 24575-2025 artfynd.xlsx
+++ b/artfynd/A 24575-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>125876679</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>125876692</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>125876827</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>125876721</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125876694</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876673</v>
+        <v>125876749</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722989</v>
+        <v>723321</v>
       </c>
       <c r="R10" t="n">
-        <v>6380861</v>
+        <v>6380856</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876780</v>
+        <v>125876673</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723343</v>
+        <v>722989</v>
       </c>
       <c r="R11" t="n">
-        <v>6380811</v>
+        <v>6380861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876691</v>
+        <v>125876780</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723017</v>
+        <v>723343</v>
       </c>
       <c r="R12" t="n">
-        <v>6380808</v>
+        <v>6380811</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876703</v>
+        <v>125876691</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723050</v>
+        <v>723017</v>
       </c>
       <c r="R13" t="n">
-        <v>6380829</v>
+        <v>6380808</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876817</v>
+        <v>125876703</v>
       </c>
       <c r="B14" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,26 +2105,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723210</v>
+        <v>723050</v>
       </c>
       <c r="R14" t="n">
-        <v>6380786</v>
+        <v>6380829</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125876749</v>
+        <v>125876817</v>
       </c>
       <c r="B15" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723321</v>
+        <v>723210</v>
       </c>
       <c r="R15" t="n">
-        <v>6380856</v>
+        <v>6380786</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>125876696</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125876732</v>
+        <v>125876672</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723148</v>
+        <v>722989</v>
       </c>
       <c r="R17" t="n">
-        <v>6380883</v>
+        <v>6380861</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125876818</v>
+        <v>125876732</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723210</v>
+        <v>723148</v>
       </c>
       <c r="R18" t="n">
-        <v>6380786</v>
+        <v>6380883</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2643,11 +2643,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125876794</v>
+        <v>125876818</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2704,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723296</v>
+        <v>723210</v>
       </c>
       <c r="R19" t="n">
-        <v>6380797</v>
+        <v>6380786</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2764,6 +2759,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inom 20 m, dessutom spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125876678</v>
+        <v>125876794</v>
       </c>
       <c r="B20" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>722965</v>
+        <v>723296</v>
       </c>
       <c r="R20" t="n">
-        <v>6380842</v>
+        <v>6380797</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125876680</v>
+        <v>125876670</v>
       </c>
       <c r="B21" t="n">
-        <v>98380</v>
+        <v>98384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,26 +2922,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>722962</v>
+        <v>723014</v>
       </c>
       <c r="R21" t="n">
-        <v>6380832</v>
+        <v>6380862</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125876670</v>
+        <v>125876678</v>
       </c>
       <c r="B22" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,26 +3038,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723014</v>
+        <v>722965</v>
       </c>
       <c r="R22" t="n">
-        <v>6380862</v>
+        <v>6380842</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3146,7 +3146,7 @@
         <v>125876774</v>
       </c>
       <c r="B23" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125876672</v>
+        <v>125876680</v>
       </c>
       <c r="B24" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,26 +3270,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>722989</v>
+        <v>722962</v>
       </c>
       <c r="R24" t="n">
-        <v>6380861</v>
+        <v>6380832</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3378,7 +3378,7 @@
         <v>125876769</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>125876656</v>
       </c>
       <c r="B26" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3607,37 +3607,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125876731</v>
+        <v>125876815</v>
       </c>
       <c r="B27" t="n">
-        <v>98380</v>
+        <v>107243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3645,21 +3645,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723148</v>
+        <v>723209</v>
       </c>
       <c r="R27" t="n">
-        <v>6380883</v>
+        <v>6380775</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3723,10 +3718,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125876708</v>
+        <v>125876731</v>
       </c>
       <c r="B28" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3772,10 +3767,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723077</v>
+        <v>723148</v>
       </c>
       <c r="R28" t="n">
-        <v>6380813</v>
+        <v>6380883</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3839,37 +3834,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125876768</v>
+        <v>125876708</v>
       </c>
       <c r="B29" t="n">
-        <v>107234</v>
+        <v>98389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3877,16 +3872,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723375</v>
+        <v>723077</v>
       </c>
       <c r="R29" t="n">
-        <v>6380878</v>
+        <v>6380813</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125876815</v>
+        <v>125876768</v>
       </c>
       <c r="B30" t="n">
-        <v>107234</v>
+        <v>107243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723209</v>
+        <v>723375</v>
       </c>
       <c r="R30" t="n">
-        <v>6380775</v>
+        <v>6380878</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>125876806</v>
       </c>
       <c r="B31" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125876712</v>
+        <v>125876805</v>
       </c>
       <c r="B32" t="n">
-        <v>98374</v>
+        <v>98389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4193,26 +4193,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723098</v>
+        <v>723244</v>
       </c>
       <c r="R32" t="n">
-        <v>6380819</v>
+        <v>6380753</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4267,6 +4267,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,10 +4303,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125876805</v>
+        <v>125876712</v>
       </c>
       <c r="B33" t="n">
-        <v>98380</v>
+        <v>98383</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4309,26 +4314,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R33" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4383,11 +4388,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125876682</v>
+        <v>125876778</v>
       </c>
       <c r="B34" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4468,13 +4468,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>722977</v>
+        <v>723355</v>
       </c>
       <c r="R34" t="n">
-        <v>6380820</v>
+        <v>6380807</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125876698</v>
+        <v>125876752</v>
       </c>
       <c r="B35" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,26 +4546,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723026</v>
+        <v>723321</v>
       </c>
       <c r="R35" t="n">
-        <v>6380845</v>
+        <v>6380856</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125876778</v>
+        <v>125876682</v>
       </c>
       <c r="B36" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,26 +4662,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723355</v>
+        <v>722977</v>
       </c>
       <c r="R36" t="n">
-        <v>6380807</v>
+        <v>6380820</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4767,37 +4767,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125876752</v>
+        <v>125876813</v>
       </c>
       <c r="B37" t="n">
-        <v>98244</v>
+        <v>107243</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4805,21 +4805,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723238</v>
       </c>
       <c r="R37" t="n">
-        <v>6380856</v>
+        <v>6380770</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4883,37 +4878,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125876813</v>
+        <v>125876698</v>
       </c>
       <c r="B38" t="n">
-        <v>107234</v>
+        <v>98389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4921,16 +4916,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723238</v>
+        <v>723026</v>
       </c>
       <c r="R38" t="n">
-        <v>6380770</v>
+        <v>6380845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4997,7 +4997,7 @@
         <v>125876663</v>
       </c>
       <c r="B39" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125876812</v>
+        <v>125876756</v>
       </c>
       <c r="B40" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5148,16 +5148,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723238</v>
+        <v>723344</v>
       </c>
       <c r="R40" t="n">
-        <v>6380770</v>
+        <v>6380853</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5224,7 +5229,7 @@
         <v>125876671</v>
       </c>
       <c r="B41" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5345,7 @@
         <v>125876762</v>
       </c>
       <c r="B42" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5453,10 +5458,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125876756</v>
+        <v>125876812</v>
       </c>
       <c r="B43" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,26 +5469,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5491,21 +5496,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723344</v>
+        <v>723238</v>
       </c>
       <c r="R43" t="n">
-        <v>6380853</v>
+        <v>6380770</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125876804</v>
+        <v>125876711</v>
       </c>
       <c r="B44" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723098</v>
       </c>
       <c r="R44" t="n">
-        <v>6380753</v>
+        <v>6380819</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125876704</v>
+        <v>125876804</v>
       </c>
       <c r="B45" t="n">
-        <v>98380</v>
+        <v>98384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,26 +5696,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723050</v>
+        <v>723244</v>
       </c>
       <c r="R45" t="n">
-        <v>6380829</v>
+        <v>6380753</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5770,11 +5770,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5806,10 +5801,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125876711</v>
+        <v>125876704</v>
       </c>
       <c r="B46" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,26 +5812,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723098</v>
+        <v>723050</v>
       </c>
       <c r="R46" t="n">
-        <v>6380819</v>
+        <v>6380829</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5891,6 +5886,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5922,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125876743</v>
+        <v>125876733</v>
       </c>
       <c r="B47" t="n">
-        <v>98244</v>
+        <v>98339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5933,26 +5933,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5971,13 +5971,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723221</v>
+        <v>723172</v>
       </c>
       <c r="R47" t="n">
-        <v>6380864</v>
+        <v>6380881</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125876814</v>
+        <v>125876743</v>
       </c>
       <c r="B48" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723228</v>
+        <v>723221</v>
       </c>
       <c r="R48" t="n">
-        <v>6380782</v>
+        <v>6380864</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125876705</v>
+        <v>125876814</v>
       </c>
       <c r="B49" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723064</v>
+        <v>723228</v>
       </c>
       <c r="R49" t="n">
-        <v>6380825</v>
+        <v>6380782</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125876728</v>
+        <v>125876705</v>
       </c>
       <c r="B50" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6281,26 +6281,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723135</v>
+        <v>723064</v>
       </c>
       <c r="R50" t="n">
-        <v>6380877</v>
+        <v>6380825</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125876733</v>
+        <v>125876728</v>
       </c>
       <c r="B51" t="n">
-        <v>98330</v>
+        <v>98389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6397,21 +6397,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723172</v>
+        <v>723135</v>
       </c>
       <c r="R51" t="n">
-        <v>6380881</v>
+        <v>6380877</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>125876803</v>
       </c>
       <c r="B52" t="n">
-        <v>107234</v>
+        <v>107243</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125876723</v>
+        <v>125876714</v>
       </c>
       <c r="B53" t="n">
-        <v>98244</v>
+        <v>98339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6624,26 +6624,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723093</v>
+        <v>723098</v>
       </c>
       <c r="R53" t="n">
-        <v>6380849</v>
+        <v>6380819</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125876736</v>
+        <v>125876681</v>
       </c>
       <c r="B54" t="n">
-        <v>98244</v>
+        <v>98384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723172</v>
+        <v>722977</v>
       </c>
       <c r="R54" t="n">
-        <v>6380881</v>
+        <v>6380820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125876686</v>
+        <v>125876723</v>
       </c>
       <c r="B55" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723006</v>
+        <v>723093</v>
       </c>
       <c r="R55" t="n">
-        <v>6380816</v>
+        <v>6380849</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125876677</v>
+        <v>125876736</v>
       </c>
       <c r="B56" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>722956</v>
+        <v>723172</v>
       </c>
       <c r="R56" t="n">
-        <v>6380853</v>
+        <v>6380881</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125876739</v>
+        <v>125876686</v>
       </c>
       <c r="B57" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723173</v>
+        <v>723006</v>
       </c>
       <c r="R57" t="n">
-        <v>6380850</v>
+        <v>6380816</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125876738</v>
+        <v>125876677</v>
       </c>
       <c r="B58" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723157</v>
+        <v>722956</v>
       </c>
       <c r="R58" t="n">
-        <v>6380881</v>
+        <v>6380853</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125876714</v>
+        <v>125876739</v>
       </c>
       <c r="B59" t="n">
-        <v>98330</v>
+        <v>98253</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7320,26 +7320,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723098</v>
+        <v>723173</v>
       </c>
       <c r="R59" t="n">
-        <v>6380819</v>
+        <v>6380850</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125876681</v>
+        <v>125876738</v>
       </c>
       <c r="B60" t="n">
-        <v>98375</v>
+        <v>98253</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7436,26 +7436,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219847</v>
+        <v>219769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>722977</v>
+        <v>723157</v>
       </c>
       <c r="R60" t="n">
-        <v>6380820</v>
+        <v>6380881</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7541,27 +7541,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125876722</v>
+        <v>125876661</v>
       </c>
       <c r="B61" t="n">
-        <v>98380</v>
+        <v>109185</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723061</v>
+        <v>723022</v>
       </c>
       <c r="R61" t="n">
-        <v>6380859</v>
+        <v>6380875</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7657,37 +7657,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125876826</v>
+        <v>125876761</v>
       </c>
       <c r="B62" t="n">
-        <v>98380</v>
+        <v>107243</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7695,21 +7695,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723188</v>
+        <v>723360</v>
       </c>
       <c r="R62" t="n">
-        <v>6380756</v>
+        <v>6380851</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7742,11 +7737,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,37 +7768,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125876761</v>
+        <v>125876722</v>
       </c>
       <c r="B63" t="n">
-        <v>107234</v>
+        <v>98389</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7816,16 +7806,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723360</v>
+        <v>723061</v>
       </c>
       <c r="R63" t="n">
-        <v>6380851</v>
+        <v>6380859</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7889,37 +7884,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125876786</v>
+        <v>125876826</v>
       </c>
       <c r="B64" t="n">
-        <v>107234</v>
+        <v>98389</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7927,16 +7922,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723329</v>
+        <v>723188</v>
       </c>
       <c r="R64" t="n">
-        <v>6380785</v>
+        <v>6380756</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7969,6 +7969,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8000,10 +8005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125876661</v>
+        <v>125876786</v>
       </c>
       <c r="B65" t="n">
-        <v>109176</v>
+        <v>107243</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8011,26 +8016,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8038,21 +8043,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723022</v>
+        <v>723329</v>
       </c>
       <c r="R65" t="n">
-        <v>6380875</v>
+        <v>6380785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8119,7 +8119,7 @@
         <v>125876785</v>
       </c>
       <c r="B66" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>125876784</v>
       </c>
       <c r="B67" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125876695</v>
+        <v>125876665</v>
       </c>
       <c r="B68" t="n">
-        <v>98380</v>
+        <v>98384</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,26 +8359,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219864</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723040</v>
+        <v>723022</v>
       </c>
       <c r="R68" t="n">
-        <v>6380808</v>
+        <v>6380875</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125876793</v>
+        <v>125876695</v>
       </c>
       <c r="B69" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723296</v>
+        <v>723040</v>
       </c>
       <c r="R69" t="n">
-        <v>6380797</v>
+        <v>6380808</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125876665</v>
+        <v>125876742</v>
       </c>
       <c r="B70" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723022</v>
+        <v>723189</v>
       </c>
       <c r="R70" t="n">
-        <v>6380875</v>
+        <v>6380869</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125876742</v>
+        <v>125876793</v>
       </c>
       <c r="B71" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723189</v>
+        <v>723296</v>
       </c>
       <c r="R71" t="n">
-        <v>6380869</v>
+        <v>6380797</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8815,7 +8815,7 @@
         <v>125876735</v>
       </c>
       <c r="B72" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8928,54 +8928,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125876910</v>
+        <v>125876921</v>
       </c>
       <c r="B73" t="n">
-        <v>95955</v>
+        <v>5492</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723027</v>
+        <v>723364</v>
       </c>
       <c r="R73" t="n">
-        <v>6380801</v>
+        <v>6380813</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9008,6 +8999,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Angripen tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9034,10 +9030,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125876741</v>
+        <v>125876910</v>
       </c>
       <c r="B74" t="n">
-        <v>98244</v>
+        <v>95964</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9045,36 +9041,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219769</v>
+        <v>2180</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9083,13 +9074,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723189</v>
+        <v>723027</v>
       </c>
       <c r="R74" t="n">
-        <v>6380869</v>
+        <v>6380801</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9129,11 +9120,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9150,59 +9136,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125876658</v>
+        <v>125876757</v>
       </c>
       <c r="B75" t="n">
-        <v>98244</v>
+        <v>103814</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219769</v>
+        <v>220164</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723022</v>
+        <v>723360</v>
       </c>
       <c r="R75" t="n">
-        <v>6380859</v>
+        <v>6380851</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9266,10 +9238,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125876717</v>
+        <v>125876810</v>
       </c>
       <c r="B76" t="n">
-        <v>98244</v>
+        <v>98279</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9277,21 +9249,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219769</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9306,7 +9278,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9315,13 +9287,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723080</v>
+        <v>723234</v>
       </c>
       <c r="R76" t="n">
-        <v>6380837</v>
+        <v>6380772</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9351,11 +9323,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9387,10 +9354,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125876776</v>
+        <v>125876741</v>
       </c>
       <c r="B77" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9417,7 +9384,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9436,13 +9403,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723342</v>
+        <v>723189</v>
       </c>
       <c r="R77" t="n">
-        <v>6380826</v>
+        <v>6380869</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9503,10 +9470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125876729</v>
+        <v>125876658</v>
       </c>
       <c r="B78" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9533,7 +9500,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9552,10 +9519,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723135</v>
+        <v>723022</v>
       </c>
       <c r="R78" t="n">
-        <v>6380877</v>
+        <v>6380859</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9619,10 +9586,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125876715</v>
+        <v>125876717</v>
       </c>
       <c r="B79" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9649,7 +9616,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9668,10 +9635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723098</v>
+        <v>723080</v>
       </c>
       <c r="R79" t="n">
-        <v>6380819</v>
+        <v>6380837</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9704,6 +9671,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9735,10 +9707,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125876716</v>
+        <v>125876776</v>
       </c>
       <c r="B80" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9746,26 +9718,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9784,13 +9756,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723080</v>
+        <v>723342</v>
       </c>
       <c r="R80" t="n">
-        <v>6380837</v>
+        <v>6380826</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9820,11 +9792,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9856,10 +9823,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125876828</v>
+        <v>125876729</v>
       </c>
       <c r="B81" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,26 +9834,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9901,14 +9868,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723173</v>
+        <v>723135</v>
       </c>
       <c r="R81" t="n">
-        <v>6380765</v>
+        <v>6380877</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9954,7 +9921,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvar och torräng.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9972,45 +9939,59 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125876757</v>
+        <v>125876715</v>
       </c>
       <c r="B82" t="n">
-        <v>103805</v>
+        <v>98253</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220164</v>
+        <v>219769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723360</v>
+        <v>723098</v>
       </c>
       <c r="R82" t="n">
-        <v>6380851</v>
+        <v>6380819</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10074,10 +10055,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125876810</v>
+        <v>125876828</v>
       </c>
       <c r="B83" t="n">
-        <v>98270</v>
+        <v>98389</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10085,26 +10066,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>219864</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10114,22 +10095,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723234</v>
+        <v>723173</v>
       </c>
       <c r="R83" t="n">
-        <v>6380772</v>
+        <v>6380765</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10172,7 +10153,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Alvar och torräng.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10190,48 +10171,62 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125876921</v>
+        <v>125876716</v>
       </c>
       <c r="B84" t="n">
-        <v>5492</v>
+        <v>98389</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101410</v>
+        <v>219864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723364</v>
+        <v>723080</v>
       </c>
       <c r="R84" t="n">
-        <v>6380813</v>
+        <v>6380837</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10265,7 +10260,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Angripen tall.</t>
+          <t>Stensträng? Just O.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10276,6 +10271,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10292,10 +10292,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125876684</v>
+        <v>125876783</v>
       </c>
       <c r="B85" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>722988</v>
+        <v>723343</v>
       </c>
       <c r="R85" t="n">
-        <v>6380785</v>
+        <v>6380788</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10408,10 +10408,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125876783</v>
+        <v>125876684</v>
       </c>
       <c r="B86" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723343</v>
+        <v>722988</v>
       </c>
       <c r="R86" t="n">
-        <v>6380788</v>
+        <v>6380785</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125876724</v>
+        <v>125876754</v>
       </c>
       <c r="B87" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10535,21 +10535,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723123</v>
+        <v>723344</v>
       </c>
       <c r="R87" t="n">
-        <v>6380848</v>
+        <v>6380853</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10609,6 +10609,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10640,10 +10645,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125876725</v>
+        <v>125876727</v>
       </c>
       <c r="B88" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10651,26 +10656,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10689,13 +10694,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723122</v>
+        <v>723123</v>
       </c>
       <c r="R88" t="n">
-        <v>6380858</v>
+        <v>6380868</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10756,10 +10761,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125876727</v>
+        <v>125876666</v>
       </c>
       <c r="B89" t="n">
-        <v>98380</v>
+        <v>98383</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10767,26 +10772,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10805,13 +10810,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723123</v>
+        <v>723022</v>
       </c>
       <c r="R89" t="n">
-        <v>6380868</v>
+        <v>6380875</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10872,10 +10877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125876754</v>
+        <v>125876724</v>
       </c>
       <c r="B90" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10883,21 +10888,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10921,13 +10926,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723344</v>
+        <v>723123</v>
       </c>
       <c r="R90" t="n">
-        <v>6380853</v>
+        <v>6380848</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10957,11 +10962,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10993,10 +10993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125876666</v>
+        <v>125876725</v>
       </c>
       <c r="B91" t="n">
-        <v>98374</v>
+        <v>98253</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723022</v>
+        <v>723122</v>
       </c>
       <c r="R91" t="n">
-        <v>6380875</v>
+        <v>6380858</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125876744</v>
+        <v>125876683</v>
       </c>
       <c r="B92" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11120,26 +11120,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723252</v>
+        <v>722977</v>
       </c>
       <c r="R92" t="n">
-        <v>6380854</v>
+        <v>6380820</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125876683</v>
+        <v>125876744</v>
       </c>
       <c r="B93" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11236,26 +11236,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>722977</v>
+        <v>723252</v>
       </c>
       <c r="R93" t="n">
-        <v>6380820</v>
+        <v>6380854</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>125876781</v>
       </c>
       <c r="B94" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11457,59 +11457,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125876707</v>
+        <v>125876945</v>
       </c>
       <c r="B95" t="n">
-        <v>98244</v>
+        <v>57654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219769</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
+          <t>Bjärs 1:2., Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723077</v>
+        <v>723296</v>
       </c>
       <c r="R95" t="n">
-        <v>6380813</v>
+        <v>6380797</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11544,6 +11539,11 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack i murken tall.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11552,11 +11552,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11573,37 +11568,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125876820</v>
+        <v>125876740</v>
       </c>
       <c r="B96" t="n">
-        <v>98244</v>
+        <v>107243</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219769</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11611,21 +11606,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723194</v>
+        <v>723183</v>
       </c>
       <c r="R96" t="n">
-        <v>6380741</v>
+        <v>6380860</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11689,32 +11679,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125876945</v>
+        <v>125876669</v>
       </c>
       <c r="B97" t="n">
-        <v>57653</v>
+        <v>98383</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11722,21 +11712,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bjärs 1:2., Gtl</t>
+          <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>723296</v>
+        <v>723014</v>
       </c>
       <c r="R97" t="n">
-        <v>6380797</v>
+        <v>6380862</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11771,11 +11766,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Födosökshack i murken tall.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11784,6 +11774,11 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11800,10 +11795,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125876772</v>
+        <v>125876707</v>
       </c>
       <c r="B98" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11830,7 +11825,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11849,7 +11844,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>723364</v>
+        <v>723077</v>
       </c>
       <c r="R98" t="n">
         <v>6380813</v>
@@ -11885,11 +11880,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11921,10 +11911,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125876697</v>
+        <v>125876820</v>
       </c>
       <c r="B99" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11951,7 +11941,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11970,10 +11960,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>723031</v>
+        <v>723194</v>
       </c>
       <c r="R99" t="n">
-        <v>6380827</v>
+        <v>6380741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12037,10 +12027,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125876788</v>
+        <v>125876772</v>
       </c>
       <c r="B100" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12067,7 +12057,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12086,10 +12076,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>723320</v>
+        <v>723364</v>
       </c>
       <c r="R100" t="n">
-        <v>6380799</v>
+        <v>6380813</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12122,6 +12112,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Fler plantor mot S-SO.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12153,10 +12148,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125876669</v>
+        <v>125876697</v>
       </c>
       <c r="B101" t="n">
-        <v>98374</v>
+        <v>98253</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12164,21 +12159,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>723014</v>
+        <v>723031</v>
       </c>
       <c r="R101" t="n">
-        <v>6380862</v>
+        <v>6380827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12269,10 +12264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125876719</v>
+        <v>125876788</v>
       </c>
       <c r="B102" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12280,26 +12275,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12318,13 +12313,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>723068</v>
+        <v>723320</v>
       </c>
       <c r="R102" t="n">
-        <v>6380835</v>
+        <v>6380799</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12385,37 +12380,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125876740</v>
+        <v>125876719</v>
       </c>
       <c r="B103" t="n">
-        <v>107234</v>
+        <v>98389</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12423,19 +12418,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>723183</v>
+        <v>723068</v>
       </c>
       <c r="R103" t="n">
-        <v>6380860</v>
+        <v>6380835</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12496,10 +12496,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125876745</v>
+        <v>125876755</v>
       </c>
       <c r="B104" t="n">
-        <v>98244</v>
+        <v>98384</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12507,26 +12507,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>723252</v>
+        <v>723344</v>
       </c>
       <c r="R104" t="n">
-        <v>6380854</v>
+        <v>6380853</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125876685</v>
+        <v>125876745</v>
       </c>
       <c r="B105" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>722988</v>
+        <v>723252</v>
       </c>
       <c r="R105" t="n">
-        <v>6380785</v>
+        <v>6380854</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125876675</v>
+        <v>125876685</v>
       </c>
       <c r="B106" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>722934</v>
+        <v>722988</v>
       </c>
       <c r="R106" t="n">
-        <v>6380847</v>
+        <v>6380785</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125876699</v>
+        <v>125876675</v>
       </c>
       <c r="B107" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12893,13 +12893,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>723026</v>
+        <v>722934</v>
       </c>
       <c r="R107" t="n">
-        <v>6380845</v>
+        <v>6380847</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125876777</v>
+        <v>125876699</v>
       </c>
       <c r="B108" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12971,26 +12971,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>723355</v>
+        <v>723026</v>
       </c>
       <c r="R108" t="n">
-        <v>6380807</v>
+        <v>6380845</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125876706</v>
+        <v>125876702</v>
       </c>
       <c r="B109" t="n">
-        <v>98380</v>
+        <v>98383</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13087,26 +13087,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>723064</v>
+        <v>723038</v>
       </c>
       <c r="R109" t="n">
-        <v>6380825</v>
+        <v>6380832</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125876702</v>
+        <v>125876706</v>
       </c>
       <c r="B110" t="n">
-        <v>98374</v>
+        <v>98389</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>723038</v>
+        <v>723064</v>
       </c>
       <c r="R110" t="n">
-        <v>6380832</v>
+        <v>6380825</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13308,10 +13308,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125876755</v>
+        <v>125876777</v>
       </c>
       <c r="B111" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13319,26 +13319,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13357,13 +13357,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>723344</v>
+        <v>723355</v>
       </c>
       <c r="R111" t="n">
-        <v>6380853</v>
+        <v>6380807</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>125876765</v>
       </c>
       <c r="B112" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>125876811</v>
       </c>
       <c r="B113" t="n">
-        <v>107234</v>
+        <v>107243</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>125876664</v>
       </c>
       <c r="B114" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>125876782</v>
       </c>
       <c r="B115" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125876709</v>
+        <v>125876674</v>
       </c>
       <c r="B116" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13894,26 +13894,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>723074</v>
+        <v>722924</v>
       </c>
       <c r="R116" t="n">
-        <v>6380823</v>
+        <v>6380847</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13999,27 +13999,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125876819</v>
+        <v>125876823</v>
       </c>
       <c r="B117" t="n">
-        <v>109176</v>
+        <v>110452</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>723194</v>
+        <v>723189</v>
       </c>
       <c r="R117" t="n">
-        <v>6380741</v>
+        <v>6380746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125876674</v>
+        <v>125876709</v>
       </c>
       <c r="B118" t="n">
-        <v>98244</v>
+        <v>98389</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14112,26 +14112,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219769</v>
+        <v>219864</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14150,10 +14150,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>722924</v>
+        <v>723074</v>
       </c>
       <c r="R118" t="n">
-        <v>6380847</v>
+        <v>6380823</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14217,10 +14217,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125876823</v>
+        <v>125876676</v>
       </c>
       <c r="B119" t="n">
-        <v>110443</v>
+        <v>98384</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14228,34 +14228,48 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>723189</v>
+        <v>722956</v>
       </c>
       <c r="R119" t="n">
-        <v>6380746</v>
+        <v>6380853</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14319,59 +14333,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125876676</v>
+        <v>125876819</v>
       </c>
       <c r="B120" t="n">
-        <v>98375</v>
+        <v>109185</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Bjärs 1:4, avverkningsanmälan A 24575-2025., Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>722956</v>
+        <v>723194</v>
       </c>
       <c r="R120" t="n">
-        <v>6380853</v>
+        <v>6380741</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14438,7 +14438,7 @@
         <v>125876659</v>
       </c>
       <c r="B121" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>125876690</v>
       </c>
       <c r="B122" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>125876763</v>
       </c>
       <c r="B123" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>125876710</v>
       </c>
       <c r="B124" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14894,10 +14894,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125876767</v>
+        <v>125876766</v>
       </c>
       <c r="B125" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14943,10 +14943,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>723375</v>
+        <v>723369</v>
       </c>
       <c r="R125" t="n">
-        <v>6380878</v>
+        <v>6380880</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15010,10 +15010,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125876766</v>
+        <v>125876767</v>
       </c>
       <c r="B126" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>723369</v>
+        <v>723375</v>
       </c>
       <c r="R126" t="n">
-        <v>6380880</v>
+        <v>6380878</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15129,7 +15129,7 @@
         <v>125876792</v>
       </c>
       <c r="B127" t="n">
-        <v>107234</v>
+        <v>107243</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>125876667</v>
       </c>
       <c r="B128" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>125876718</v>
       </c>
       <c r="B129" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>126004016</v>
       </c>
       <c r="B130" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>126003980</v>
       </c>
       <c r="B131" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15701,37 +15701,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126003997</v>
+        <v>126003999</v>
       </c>
       <c r="B132" t="n">
-        <v>98375</v>
+        <v>109185</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>723483</v>
+        <v>723516</v>
       </c>
       <c r="R132" t="n">
-        <v>6380826</v>
+        <v>6380880</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15817,10 +15817,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126004010</v>
+        <v>126003997</v>
       </c>
       <c r="B133" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>723469</v>
+        <v>723483</v>
       </c>
       <c r="R133" t="n">
-        <v>6380865</v>
+        <v>6380826</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15933,10 +15933,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126004004</v>
+        <v>126004010</v>
       </c>
       <c r="B134" t="n">
-        <v>98374</v>
+        <v>98384</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15944,26 +15944,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>723496</v>
+        <v>723469</v>
       </c>
       <c r="R134" t="n">
         <v>6380865</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16049,37 +16049,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126003999</v>
+        <v>126004004</v>
       </c>
       <c r="B135" t="n">
-        <v>109176</v>
+        <v>98383</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>723516</v>
+        <v>723496</v>
       </c>
       <c r="R135" t="n">
-        <v>6380880</v>
+        <v>6380865</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog av ängstyp med kontinuitet. Rkt med döda träd av gran och tall. Kjolgranar och grova tallar.</t>
+          <t>Kalkbarrskog av ängstyp med kontinuitet. Fuktmark, träd på socklar.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16168,7 +16168,7 @@
         <v>126003992</v>
       </c>
       <c r="B136" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16281,10 +16281,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126003993</v>
+        <v>126003974</v>
       </c>
       <c r="B137" t="n">
-        <v>98375</v>
+        <v>98389</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16292,26 +16292,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16330,10 +16330,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>723470</v>
+        <v>723349</v>
       </c>
       <c r="R137" t="n">
-        <v>6380822</v>
+        <v>6380791</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16397,10 +16397,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126003995</v>
+        <v>126003993</v>
       </c>
       <c r="B138" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>723470</v>
       </c>
       <c r="R138" t="n">
-        <v>6380826</v>
+        <v>6380822</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -16513,10 +16513,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126003978</v>
+        <v>126003995</v>
       </c>
       <c r="B139" t="n">
-        <v>98244</v>
+        <v>98384</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16524,26 +16524,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219769</v>
+        <v>219847</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16562,10 +16562,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>723349</v>
+        <v>723470</v>
       </c>
       <c r="R139" t="n">
-        <v>6380791</v>
+        <v>6380826</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -16629,10 +16629,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126003974</v>
+        <v>126003978</v>
       </c>
       <c r="B140" t="n">
-        <v>98380</v>
+        <v>98253</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16640,26 +16640,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219864</v>
+        <v>219769</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16748,7 +16748,7 @@
         <v>126003972</v>
       </c>
       <c r="B141" t="n">
-        <v>103805</v>
+        <v>103814</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>126003986</v>
       </c>
       <c r="B142" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>126003970</v>
       </c>
       <c r="B143" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>126004003</v>
       </c>
       <c r="B144" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17200,10 +17200,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126003971</v>
+        <v>126003998</v>
       </c>
       <c r="B145" t="n">
-        <v>98244</v>
+        <v>98383</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17211,26 +17211,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219769</v>
+        <v>219862</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>723257</v>
+        <v>723508</v>
       </c>
       <c r="R145" t="n">
-        <v>6380842</v>
+        <v>6380857</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17316,10 +17316,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126003998</v>
+        <v>126003971</v>
       </c>
       <c r="B146" t="n">
-        <v>98374</v>
+        <v>98253</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17327,26 +17327,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219862</v>
+        <v>219769</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>723508</v>
+        <v>723257</v>
       </c>
       <c r="R146" t="n">
-        <v>6380857</v>
+        <v>6380842</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17435,7 +17435,7 @@
         <v>126003989</v>
       </c>
       <c r="B147" t="n">
-        <v>98244</v>
+        <v>98253</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17548,48 +17548,62 @@
     </row>
     <row r="148">
       <c r="A148" t="n">